--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -7545,12 +7545,12 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>@duartejr_</t>
+          <t>@duartejr70</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/duartejr_</t>
+          <t>https://instagram.com/duartejr70</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CIDADANIA</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -22152,7 +22152,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -9706,108 +9706,100 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>74383</v>
+        <v>204491</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Giacobo</t>
+          <t>Gilberto Abramo</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>FERNANDO LÚCIO GIACOBO</t>
+          <t>GILBERTO APARECIDO ABRAMO</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>dep.giacobo@camara.leg.br</t>
+          <t>dep.gilbertoabramo@camara.leg.br</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>@fernandogiacobo</t>
+          <t>@gilbertoabramo_</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/fernandogiacobo</t>
+          <t>https://instagram.com/gilbertoabramo_</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74383</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204491</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>204491</v>
+        <v>74270</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Gilberto Abramo</t>
+          <t>Gilberto Nascimento</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>GILBERTO APARECIDO ABRAMO</t>
+          <t>GILBERTO NASCIMENTO SILVA</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>dep.gilbertoabramo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>@gilbertoabramo_</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/gilbertoabramo_</t>
-        </is>
-      </c>
+          <t>dep.gilbertonascimento@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204491</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74270</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>74270</v>
+        <v>220529</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Gilberto Nascimento</t>
+          <t>Gilson Daniel</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>GILBERTO NASCIMENTO SILVA</t>
+          <t>GILSON DANIEL BATISTA</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -9817,131 +9809,139 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>dep.gilbertonascimento@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr"/>
+          <t>dep.gilsondaniel@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>@gilsondaniel1919</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/gilsondaniel1919</t>
+        </is>
+      </c>
       <c r="I213" s="2" t="inlineStr"/>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74270</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220529</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>220529</v>
+        <v>204365</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Gilson Daniel</t>
+          <t>Gilson Marques</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>GILSON DANIEL BATISTA</t>
+          <t>GILSON MARQUES VIEIRA</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>dep.gilsondaniel@camara.leg.br</t>
+          <t>dep.gilsonmarques@camara.leg.br</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>@gilsondaniel1919</t>
+          <t>@gilson.marques.novo</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gilsondaniel1919</t>
-        </is>
-      </c>
-      <c r="I214" s="2" t="inlineStr"/>
+          <t>https://instagram.com/gilson.marques.novo</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/gilsonmarquesnovo</t>
+        </is>
+      </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220529</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204365</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>204365</v>
+        <v>220526</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Gilson Marques</t>
+          <t>Gilvan da Federal</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>GILSON MARQUES VIEIRA</t>
+          <t>GILVAN AGUIAR COSTA</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>dep.gilsonmarques@camara.leg.br</t>
+          <t>dep.gilvandafederal@camara.leg.br</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>@gilson.marques.novo</t>
+          <t>@gilvandafederal</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gilson.marques.novo</t>
-        </is>
-      </c>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/gilsonmarquesnovo</t>
-        </is>
-      </c>
+          <t>https://instagram.com/gilvandafederal</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr"/>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204365</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220526</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>220526</v>
+        <v>160673</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Gilvan da Federal</t>
+          <t>Giovani Cherini</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>GILVAN AGUIAR COSTA</t>
+          <t>GIOVANI CHERINI</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9951,58 +9951,50 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>dep.gilvandafederal@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>@gilvandafederal</t>
-        </is>
-      </c>
-      <c r="H216" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/gilvandafederal</t>
-        </is>
-      </c>
+          <t>dep.giovanicherini@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
       <c r="I216" s="2" t="inlineStr"/>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220526</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160673</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>160673</v>
+        <v>204419</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Giovani Cherini</t>
+          <t>Glaustin da Fokus</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>GIOVANI CHERINI</t>
+          <t>GLAUSKSTON BATISTA RIOS</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>dep.giovanicherini@camara.leg.br</t>
+          <t>dep.glaustindafokus@camara.leg.br</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr"/>
@@ -10010,321 +10002,321 @@
       <c r="I217" s="2" t="inlineStr"/>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160673</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204419</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>204419</v>
+        <v>107283</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Glaustin da Fokus</t>
+          <t>Gleisi Hoffmann</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>GLAUSKSTON BATISTA RIOS</t>
+          <t>GLEISI HELENA HOFFMANN</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>dep.glaustindafokus@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr"/>
-      <c r="I218" s="2" t="inlineStr"/>
+          <t>dep.gleisihoffmann@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>@gleisihoffmann</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/gleisihoffmann</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/GleisiHoffmannPT</t>
+        </is>
+      </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204419</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/107283</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>107283</v>
+        <v>198197</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Gleisi Hoffmann</t>
+          <t>Greyce Elias</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>GLEISI HELENA HOFFMANN</t>
+          <t>GREYCE DE QUEIROZ ELIAS</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>dep.gleisihoffmann@camara.leg.br</t>
+          <t>dep.greyceelias@camara.leg.br</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>@gleisihoffmann</t>
+          <t>@greyceelias</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gleisihoffmann</t>
+          <t>https://instagram.com/greyceelias</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/GleisiHoffmannPT</t>
+          <t>https://youtube.com/channel/UCcSZxLiSfO1dFmAryUnxPHg</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/107283</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/198197</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>198197</v>
+        <v>204531</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Greyce Elias</t>
+          <t>Guilherme Derrite</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>GREYCE DE QUEIROZ ELIAS</t>
+          <t>GUILHERME MURARO DERRITE</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>dep.greyceelias@camara.leg.br</t>
+          <t>dep.guilhermederrite@camara.leg.br</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>@greyceelias</t>
+          <t>@capitaoderrite</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/greyceelias</t>
+          <t>https://instagram.com/capitaoderrite</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCcSZxLiSfO1dFmAryUnxPHg</t>
+          <t>https://youtube.com/channel/UCZHZxgmwC2c5tz3_Jn-gGOw</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/198197</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204531</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>204531</v>
+        <v>220664</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Derrite</t>
+          <t>Guilherme Uchoa</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>GUILHERME MURARO DERRITE</t>
+          <t>GUILHERME A. UCHOA CAVALCANTI PESSOA DE MELO JUNIOR</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>dep.guilhermederrite@camara.leg.br</t>
+          <t>dep.guilhermeuchoa@camara.leg.br</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>@capitaoderrite</t>
+          <t>@GUILHERMEUCHOAJR</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/capitaoderrite</t>
-        </is>
-      </c>
-      <c r="I221" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCZHZxgmwC2c5tz3_Jn-gGOw</t>
-        </is>
-      </c>
+          <t>https://instagram.com/GUILHERMEUCHOAJR</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr"/>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204531</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220664</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>220664</v>
+        <v>220568</v>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Uchoa</t>
+          <t>Gustavo Gayer</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>GUILHERME A. UCHOA CAVALCANTI PESSOA DE MELO JUNIOR</t>
+          <t>GUSTAVO GAYER MACHADO DE ARAUJO</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>dep.guilhermeuchoa@camara.leg.br</t>
+          <t>dep.gustavogayer@camara.leg.br</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>@GUILHERMEUCHOAJR</t>
+          <t>@gusgayer</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/GUILHERMEUCHOAJR</t>
-        </is>
-      </c>
-      <c r="I222" s="2" t="inlineStr"/>
+          <t>https://instagram.com/gusgayer</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/GustavoGayer</t>
+        </is>
+      </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220664</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220568</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>220568</v>
+        <v>204408</v>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Gayer</t>
+          <t>Gustinho Ribeiro</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>GUSTAVO GAYER MACHADO DE ARAUJO</t>
+          <t>LUIZ AUGUSTO CARVALHO RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>dep.gustavogayer@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G223" s="2" t="inlineStr">
-        <is>
-          <t>@gusgayer</t>
-        </is>
-      </c>
-      <c r="H223" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/gusgayer</t>
-        </is>
-      </c>
-      <c r="I223" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/GustavoGayer</t>
-        </is>
-      </c>
+          <t>dep.gustinhoribeiro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr"/>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220568</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204408</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>204408</v>
+        <v>204456</v>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Gustinho Ribeiro</t>
+          <t>Gutemberg Reis</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>LUIZ AUGUSTO CARVALHO RIBEIRO FILHO</t>
+          <t>GUTEMBERG REIS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>dep.gustinhoribeiro@camara.leg.br</t>
+          <t>dep.gutembergreis@camara.leg.br</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr"/>
@@ -10332,195 +10324,203 @@
       <c r="I224" s="2" t="inlineStr"/>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204408</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204456</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>204456</v>
+        <v>178964</v>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Gutemberg Reis</t>
+          <t>Heitor Schuch</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>GUTEMBERG REIS DE OLIVEIRA</t>
+          <t>HEITOR JOSE SCHUCH</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>dep.gutembergreis@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr"/>
+          <t>dep.heitorschuch@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>@heitorschuch</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/heitorschuch</t>
+        </is>
+      </c>
       <c r="I225" s="2" t="inlineStr"/>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204456</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178964</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>178964</v>
+        <v>178873</v>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Heitor Schuch</t>
+          <t>Helder Salomão</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>HEITOR JOSE SCHUCH</t>
+          <t>HELDER IGNACIO SALOMAO</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>dep.heitorschuch@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>@heitorschuch</t>
-        </is>
-      </c>
-      <c r="H226" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/heitorschuch</t>
-        </is>
-      </c>
+          <t>dep.heldersalomao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr"/>
       <c r="I226" s="2" t="inlineStr"/>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178964</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178873</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>178873</v>
+        <v>220537</v>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Helder Salomão</t>
+          <t>Helena Lima</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>HELDER IGNACIO SALOMAO</t>
+          <t>MARIA HELENA TEIXEIRA LIMA</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>dep.heldersalomao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr"/>
+          <t>dep.helenalima@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>@helenadaasatur</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/helenadaasatur</t>
+        </is>
+      </c>
       <c r="I227" s="2" t="inlineStr"/>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178873</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220537</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>220537</v>
+        <v>204444</v>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Helena Lima</t>
+          <t>Helio Lopes</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>MARIA HELENA TEIXEIRA LIMA</t>
+          <t>HELIO FERNANDO BARBOSA LOPES</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>dep.helenalima@camara.leg.br</t>
+          <t>dep.heliolopes@camara.leg.br</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>@helenadaasatur</t>
+          <t>@depheliolopes</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/helenadaasatur</t>
+          <t>https://instagram.com/depheliolopes</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr"/>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220537</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204444</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>204444</v>
+        <v>234788</v>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Helio Lopes</t>
+          <t>Heloísa Helena</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>HELIO FERNANDO BARBOSA LOPES</t>
+          <t>HELOÍSA HELENA LIMA DE MORAES CARVALHO</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REDE</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -10530,122 +10530,126 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>dep.heliolopes@camara.leg.br</t>
+          <t>dep.heloisahelena@camara.leg.br</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>@depheliolopes</t>
+          <t>@_heloisa_helena</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/depheliolopes</t>
+          <t>https://instagram.com/_heloisa_helena</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr"/>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204444</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/234788</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>234788</v>
+        <v>220672</v>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Heloísa Helena</t>
+          <t>Henderson Pinto</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>HELOÍSA HELENA LIMA DE MORAES CARVALHO</t>
+          <t>HENDERSON LIRA PINTO</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>REDE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>dep.heloisahelena@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>@_heloisa_helena</t>
-        </is>
-      </c>
-      <c r="H230" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/_heloisa_helena</t>
-        </is>
-      </c>
+          <t>dep.hendersonpinto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
       <c r="I230" s="2" t="inlineStr"/>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/234788</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220672</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>220672</v>
+        <v>204539</v>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Henderson Pinto</t>
+          <t>Hercílio Coelho Diniz</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>HENDERSON LIRA PINTO</t>
+          <t>HERCÍLIO ARAÚJO DINIZ FILHO</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>dep.hendersonpinto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr"/>
-      <c r="I231" s="2" t="inlineStr"/>
+          <t>dep.herciliocoelhodiniz@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>@herciliocoelhodinizoficial</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/herciliocoelhodinizoficial</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/HercílioCoelhoDinizOficial</t>
+        </is>
+      </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220672</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204539</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>204539</v>
+        <v>178884</v>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Hercílio Coelho Diniz</t>
+          <t>Hildo Rocha</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>HERCÍLIO ARAÚJO DINIZ FILHO</t>
+          <t>HILDO AUGUSTO DA ROCHA NETO</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -10655,131 +10659,119 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>dep.herciliocoelhodiniz@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>@herciliocoelhodinizoficial</t>
-        </is>
-      </c>
-      <c r="H232" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/herciliocoelhodinizoficial</t>
-        </is>
-      </c>
-      <c r="I232" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/HercílioCoelhoDinizOficial</t>
-        </is>
-      </c>
+          <t>dep.hildorocha@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr"/>
+      <c r="I232" s="2" t="inlineStr"/>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204539</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178884</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>178884</v>
+        <v>141450</v>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Hildo Rocha</t>
+          <t>Hugo Leal</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>HILDO AUGUSTO DA ROCHA NETO</t>
+          <t>HUGO LEAL MELO DA SILVA</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>dep.hildorocha@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr"/>
+          <t>dep.hugoleal@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>@dephugoleal</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dephugoleal</t>
+        </is>
+      </c>
       <c r="I233" s="2" t="inlineStr"/>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178884</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141450</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>141450</v>
+        <v>160674</v>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Hugo Leal</t>
+          <t>Hugo Motta</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>HUGO LEAL MELO DA SILVA</t>
+          <t>HUGO MOTTA WANDERLEY DA NÓBREGA</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>dep.hugoleal@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>@dephugoleal</t>
-        </is>
-      </c>
-      <c r="H234" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/dephugoleal</t>
-        </is>
-      </c>
+          <t>dep.hugomotta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr"/>
       <c r="I234" s="2" t="inlineStr"/>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141450</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160674</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>160674</v>
+        <v>220563</v>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Hugo Motta</t>
+          <t>Icaro de Valmir</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>HUGO MOTTA WANDERLEY DA NÓBREGA</t>
+          <t>ICARO BARBOSA COSTA</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -10789,132 +10781,140 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>dep.hugomotta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr"/>
+          <t>dep.icarodevalmir@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>@icarodevalmir</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/icarodevalmir</t>
+        </is>
+      </c>
       <c r="I235" s="2" t="inlineStr"/>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160674</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220563</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>220563</v>
+        <v>204533</v>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Icaro de Valmir</t>
+          <t>Idilvan Alencar</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>ICARO BARBOSA COSTA</t>
+          <t>ANTONIO IDILVAN DE LIMA ALENCAR</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>dep.icarodevalmir@camara.leg.br</t>
+          <t>dep.idilvanalencar@camara.leg.br</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>@icarodevalmir</t>
+          <t>@idilvanalencar</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/icarodevalmir</t>
+          <t>https://instagram.com/idilvanalencar</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr"/>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220563</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204533</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>204533</v>
+        <v>204508</v>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Idilvan Alencar</t>
+          <t>Igor Timo</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO IDILVAN DE LIMA ALENCAR</t>
+          <t>IGOR TARCIANO TIMO</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>dep.idilvanalencar@camara.leg.br</t>
+          <t>dep.igortimo@camara.leg.br</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>@idilvanalencar</t>
+          <t>@oficialigortimo</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/idilvanalencar</t>
+          <t>https://instagram.com/oficialigortimo</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204508</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>204508</v>
+        <v>235620</v>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Igor Timo</t>
+          <t>Ilacir Bicalho</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>IGOR TARCIANO TIMO</t>
+          <t>ILACIR BICALHO DE BARROS</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -10924,53 +10924,45 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>dep.igortimo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>@oficialigortimo</t>
-        </is>
-      </c>
-      <c r="H238" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/oficialigortimo</t>
-        </is>
-      </c>
+          <t>dep.ilacirbicalho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr"/>
       <c r="I238" s="2" t="inlineStr"/>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204508</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235620</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>235620</v>
+        <v>74295</v>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Ilacir Bicalho</t>
+          <t>Inácio Arruda</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>ILACIR BICALHO DE BARROS</t>
+          <t>INÁCIO FRANCISCO DE ASSIS NUNES ARRUDA</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>dep.ilacirbicalho@camara.leg.br</t>
+          <t>dep.inacioarruda@camara.leg.br</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr"/>
@@ -10978,137 +10970,137 @@
       <c r="I239" s="2" t="inlineStr"/>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235620</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74295</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>74295</v>
+        <v>98615</v>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Inácio Arruda</t>
+          <t>Ismael</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>INÁCIO FRANCISCO DE ASSIS NUNES ARRUDA</t>
+          <t>ISMAEL DOS SANTOS</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>dep.inacioarruda@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr"/>
+          <t>dep.ismael@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>@deputadoismael</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadoismael</t>
+        </is>
+      </c>
       <c r="I240" s="2" t="inlineStr"/>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74295</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/98615</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>98615</v>
+        <v>204436</v>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Ismael</t>
+          <t>Isnaldo Bulhões Jr.</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>ISMAEL DOS SANTOS</t>
+          <t>ISNALDO BULHOES BARROS JUNIOR</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>dep.ismael@camara.leg.br</t>
+          <t>dep.isnaldobulhoesjr@camara.leg.br</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>@deputadoismael</t>
+          <t>@isnaldobulhoes</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadoismael</t>
+          <t>https://instagram.com/isnaldobulhoes</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr"/>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/98615</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204436</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>204436</v>
+        <v>225846</v>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Isnaldo Bulhões Jr.</t>
+          <t>Itamar Paim</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>ISNALDO BULHOES BARROS JUNIOR</t>
+          <t>ITAMAR PAIM PRUCH</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>dep.isnaldobulhoesjr@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>@isnaldobulhoes</t>
-        </is>
-      </c>
-      <c r="H242" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/isnaldobulhoes</t>
-        </is>
-      </c>
+          <t>dep.itamarpaim@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr"/>
       <c r="I242" s="2" t="inlineStr"/>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204436</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/225846</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>PRD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
@@ -22446,7 +22446,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J517"/>
+  <dimension ref="A1:J516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16812,572 +16812,564 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>74159</v>
+        <v>204498</v>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Odair Cunha</t>
+          <t>Olival Marques</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>ODAIR JOSÉ DA CUNHA</t>
+          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>dep.odaircunha@camara.leg.br</t>
+          <t>dep.olivalmarques@camara.leg.br</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>@odaircunhamg</t>
+          <t>@OlivalMarques</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/odaircunhamg</t>
+          <t>https://instagram.com/OlivalMarques</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr"/>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74159</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>204498</v>
+        <v>178987</v>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Olival Marques</t>
+          <t>Orlando Silva</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
+          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>dep.olivalmarques@camara.leg.br</t>
+          <t>dep.orlandosilva@camara.leg.br</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>@OlivalMarques</t>
+          <t>@orlandosilvasp</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/OlivalMarques</t>
+          <t>https://instagram.com/orlandosilvasp</t>
         </is>
       </c>
       <c r="I373" s="2" t="inlineStr"/>
       <c r="J373" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>178987</v>
+        <v>73692</v>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Orlando Silva</t>
+          <t>Osmar Terra</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
+          <t>OSMAR GASPARINI TERRA</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>dep.orlandosilva@camara.leg.br</t>
+          <t>dep.osmarterra@camara.leg.br</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>@orlandosilvasp</t>
+          <t>@terra.osmar</t>
         </is>
       </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/orlandosilvasp</t>
-        </is>
-      </c>
-      <c r="I374" s="2" t="inlineStr"/>
+          <t>https://instagram.com/terra.osmar</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
+        </is>
+      </c>
       <c r="J374" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>73692</v>
+        <v>204441</v>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Osmar Terra</t>
+          <t>Otoni de Paula</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>OSMAR GASPARINI TERRA</t>
+          <t>OTONI MOURA DE PAULO JUNIOR</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>dep.osmarterra@camara.leg.br</t>
+          <t>dep.otonidepaula@camara.leg.br</t>
         </is>
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>@terra.osmar</t>
+          <t>@otonidepaulaoficial</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/terra.osmar</t>
-        </is>
-      </c>
-      <c r="I375" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/otonidepaulaoficial</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr"/>
       <c r="J375" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>204441</v>
+        <v>220706</v>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Otoni de Paula</t>
+          <t>Padovani</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>OTONI MOURA DE PAULO JUNIOR</t>
+          <t>NELSON FERNANDO PADOVANI</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>dep.otonidepaula@camara.leg.br</t>
+          <t>dep.padovani@camara.leg.br</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>@otonidepaulaoficial</t>
+          <t>@nelsinhopadovani</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/otonidepaulaoficial</t>
+          <t>https://instagram.com/nelsinhopadovani</t>
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr"/>
       <c r="J376" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220706</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>220706</v>
+        <v>160556</v>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Padovani</t>
+          <t>Padre João</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>NELSON FERNANDO PADOVANI</t>
+          <t>JOÃO CARLOS SIQUEIRA</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>dep.padovani@camara.leg.br</t>
+          <t>dep.padrejoao@camara.leg.br</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>@nelsinhopadovani</t>
+          <t>@dep_padrejoao</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelsinhopadovani</t>
-        </is>
-      </c>
-      <c r="I377" s="2" t="inlineStr"/>
+          <t>https://instagram.com/dep_padrejoao</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
+        </is>
+      </c>
       <c r="J377" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220706</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>160556</v>
+        <v>180214</v>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Padre João</t>
+          <t>Pastor Diniz</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>JOÃO CARLOS SIQUEIRA</t>
+          <t>RAIMUNDO DINIZ ARAÚJO</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>dep.padrejoao@camara.leg.br</t>
+          <t>dep.pastordiniz@camara.leg.br</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>@dep_padrejoao</t>
+          <t>@pastordiniz.ad</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep_padrejoao</t>
-        </is>
-      </c>
-      <c r="I378" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
-        </is>
-      </c>
+          <t>https://instagram.com/pastordiniz.ad</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr"/>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>180214</v>
+        <v>160642</v>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Pastor Diniz</t>
+          <t>Pastor Eurico</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO DINIZ ARAÚJO</t>
+          <t>FRANCISCO EURICO DA SILVA</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>dep.pastordiniz@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G379" s="2" t="inlineStr">
-        <is>
-          <t>@pastordiniz.ad</t>
-        </is>
-      </c>
-      <c r="H379" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pastordiniz.ad</t>
-        </is>
-      </c>
+          <t>dep.pastoreurico@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr"/>
+      <c r="H379" s="2" t="inlineStr"/>
       <c r="I379" s="2" t="inlineStr"/>
       <c r="J379" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>160642</v>
+        <v>204570</v>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Pastor Eurico</t>
+          <t>Pastor Gil</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EURICO DA SILVA</t>
+          <t>GILDENEMIR DE LIMA SOUSA</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>dep.pastoreurico@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G380" s="2" t="inlineStr"/>
-      <c r="H380" s="2" t="inlineStr"/>
+          <t>dep.pastorgil@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>@deputadogildenemyr</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadogildenemyr</t>
+        </is>
+      </c>
       <c r="I380" s="2" t="inlineStr"/>
       <c r="J380" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>204570</v>
+        <v>220615</v>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Pastor Gil</t>
+          <t>Pastor Henrique Vieira</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>GILDENEMIR DE LIMA SOUSA</t>
+          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorgil@camara.leg.br</t>
+          <t>dep.pastorhenriquevieira@camara.leg.br</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>@deputadogildenemyr</t>
+          <t>@pastorhenriquevieira</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadogildenemyr</t>
-        </is>
-      </c>
-      <c r="I381" s="2" t="inlineStr"/>
+          <t>https://instagram.com/pastorhenriquevieira</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PastorHenriqueVieira</t>
+        </is>
+      </c>
       <c r="J381" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>220615</v>
+        <v>204553</v>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>Pastor Henrique Vieira</t>
+          <t>Pastor Sargento Isidório</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
+          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorhenriquevieira@camara.leg.br</t>
+          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>@pastorhenriquevieira</t>
+          <t>@pastorsargentoisidorio</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastorhenriquevieira</t>
-        </is>
-      </c>
-      <c r="I382" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/PastorHenriqueVieira</t>
-        </is>
-      </c>
+          <t>https://instagram.com/pastorsargentoisidorio</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr"/>
       <c r="J382" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>204553</v>
+        <v>74160</v>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>Pastor Sargento Isidório</t>
+          <t>Patrus Ananias</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
+          <t>PATRUS ANANIAS DE SOUZA</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>@pastorsargentoisidorio</t>
-        </is>
-      </c>
-      <c r="H383" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pastorsargentoisidorio</t>
-        </is>
-      </c>
+          <t>dep.patrusananias@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr"/>
+      <c r="H383" s="2" t="inlineStr"/>
       <c r="I383" s="2" t="inlineStr"/>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>74160</v>
+        <v>171617</v>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>Patrus Ananias</t>
+          <t>Paulão</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS DE SOUZA</t>
+          <t>PAULO FERNANDO DOS SANTOS</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
@@ -17387,12 +17379,12 @@
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>dep.patrusananias@camara.leg.br</t>
+          <t>dep.paulao@camara.leg.br</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr"/>
@@ -17400,37 +17392,37 @@
       <c r="I384" s="2" t="inlineStr"/>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171617</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>171617</v>
+        <v>141518</v>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Paulão</t>
+          <t>Paulinho da Força</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>PAULO FERNANDO DOS SANTOS</t>
+          <t>PAULO PEREIRA DA SILVA</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>dep.paulao@camara.leg.br</t>
+          <t>dep.paulinhodaforca@camara.leg.br</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr"/>
@@ -17438,37 +17430,37 @@
       <c r="I385" s="2" t="inlineStr"/>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171617</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>141518</v>
+        <v>141516</v>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Paulinho da Força</t>
+          <t>Paulo Abi-Ackel</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>PAULO PEREIRA DA SILVA</t>
+          <t>PAULO ABI-ACKEL</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>dep.paulinhodaforca@camara.leg.br</t>
+          <t>dep.pauloabiackel@camara.leg.br</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr"/>
@@ -17476,213 +17468,213 @@
       <c r="I386" s="2" t="inlineStr"/>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>141516</v>
+        <v>220650</v>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Paulo Abi-Ackel</t>
+          <t>Paulo Alexandre Barbosa</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>PAULO ABI-ACKEL</t>
+          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloabiackel@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G387" s="2" t="inlineStr"/>
-      <c r="H387" s="2" t="inlineStr"/>
+          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>@pauloalexandrebarbosa</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pauloalexandrebarbosa</t>
+        </is>
+      </c>
       <c r="I387" s="2" t="inlineStr"/>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>220650</v>
+        <v>178860</v>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>Paulo Alexandre Barbosa</t>
+          <t>Paulo Azi</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
+          <t>PAULO VELLOSO DANTAS AZI</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
+          <t>dep.pauloazi@camara.leg.br</t>
         </is>
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>@pauloalexandrebarbosa</t>
+          <t>@PauloAziofcial</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pauloalexandrebarbosa</t>
+          <t>https://instagram.com/PauloAziofcial</t>
         </is>
       </c>
       <c r="I388" s="2" t="inlineStr"/>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>178860</v>
+        <v>160517</v>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>Paulo Azi</t>
+          <t>Paulo Folletto</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>PAULO VELLOSO DANTAS AZI</t>
+          <t>PAULO ROBERTO FOLLETTO</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloazi@camara.leg.br</t>
+          <t>dep.paulofolletto@camara.leg.br</t>
         </is>
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>@PauloAziofcial</t>
+          <t>@paulo.folletto</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/PauloAziofcial</t>
+          <t>https://instagram.com/paulo.folletto</t>
         </is>
       </c>
       <c r="I389" s="2" t="inlineStr"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>160517</v>
+        <v>160558</v>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>Paulo Folletto</t>
+          <t>Paulo Freire Costa</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FOLLETTO</t>
+          <t>PAULO ROBERTO FREIRE DA COSTA</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofolletto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G390" s="2" t="inlineStr">
-        <is>
-          <t>@paulo.folletto</t>
-        </is>
-      </c>
-      <c r="H390" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/paulo.folletto</t>
-        </is>
-      </c>
+          <t>dep.paulofreirecosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr"/>
+      <c r="H390" s="2" t="inlineStr"/>
       <c r="I390" s="2" t="inlineStr"/>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>160558</v>
+        <v>204492</v>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>Paulo Freire Costa</t>
+          <t>Paulo Guedes</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FREIRE DA COSTA</t>
+          <t>PAULO JOSE CARLOS GUEDES</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofreirecosta@camara.leg.br</t>
+          <t>dep.pauloguedes@camara.leg.br</t>
         </is>
       </c>
       <c r="G391" s="2" t="inlineStr"/>
@@ -17690,22 +17682,22 @@
       <c r="I391" s="2" t="inlineStr"/>
       <c r="J391" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>204492</v>
+        <v>233592</v>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>Paulo Guedes</t>
+          <t>Paulo Lemos</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>PAULO JOSE CARLOS GUEDES</t>
+          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -17715,100 +17707,100 @@
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloguedes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G392" s="2" t="inlineStr"/>
-      <c r="H392" s="2" t="inlineStr"/>
-      <c r="I392" s="2" t="inlineStr"/>
+          <t>dep.paulolemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>@paulolemosap</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/paulolemosap</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
+        </is>
+      </c>
       <c r="J392" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>233592</v>
+        <v>220685</v>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>Paulo Lemos</t>
+          <t>Paulo Litro</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
+          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G393" s="2" t="inlineStr">
-        <is>
-          <t>@paulolemosap</t>
-        </is>
-      </c>
-      <c r="H393" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/paulolemosap</t>
-        </is>
-      </c>
-      <c r="I393" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
-        </is>
-      </c>
+          <t>dep.paulolitro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr"/>
+      <c r="H393" s="2" t="inlineStr"/>
+      <c r="I393" s="2" t="inlineStr"/>
       <c r="J393" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>220685</v>
+        <v>74574</v>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>Paulo Litro</t>
+          <t>Paulo Magalhães</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
+          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolitro@camara.leg.br</t>
+          <t>dep.paulomagalhaes@camara.leg.br</t>
         </is>
       </c>
       <c r="G394" s="2" t="inlineStr"/>
@@ -17816,37 +17808,37 @@
       <c r="I394" s="2" t="inlineStr"/>
       <c r="J394" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>74574</v>
+        <v>128760</v>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>Paulo Magalhães</t>
+          <t>Paulo Marinho Jr</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
+          <t>PAULO CELSO FONSECA MARINHO JÚNIOR</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>dep.paulomagalhaes@camara.leg.br</t>
+          <t>dep.paulomarinhojr@camara.leg.br</t>
         </is>
       </c>
       <c r="G395" s="2" t="inlineStr"/>
@@ -17854,37 +17846,37 @@
       <c r="I395" s="2" t="inlineStr"/>
       <c r="J395" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/128760</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>128760</v>
+        <v>74400</v>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>Paulo Marinho Jr</t>
+          <t>Paulo Pimenta</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>PAULO CELSO FONSECA MARINHO JÚNIOR</t>
+          <t>PAULO ROBERTO SEVERO PIMENTA</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>dep.paulomarinhojr@camara.leg.br</t>
+          <t>dep.paulopimenta@camara.leg.br</t>
         </is>
       </c>
       <c r="G396" s="2" t="inlineStr"/>
@@ -17892,22 +17884,22 @@
       <c r="I396" s="2" t="inlineStr"/>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/128760</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>74400</v>
+        <v>141488</v>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>Paulo Pimenta</t>
+          <t>Paulo Teixeira</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO SEVERO PIMENTA</t>
+          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
@@ -17917,272 +17909,272 @@
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>dep.paulopimenta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G397" s="2" t="inlineStr"/>
-      <c r="H397" s="2" t="inlineStr"/>
+          <t>dep.pauloteixeira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>@pauloteixeira13</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pauloteixeira13</t>
+        </is>
+      </c>
       <c r="I397" s="2" t="inlineStr"/>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>141488</v>
+        <v>220630</v>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Paulo Teixeira</t>
+          <t>Pedro Aihara</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
+          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloteixeira@camara.leg.br</t>
+          <t>dep.pedroaihara@camara.leg.br</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>@pauloteixeira13</t>
+          <t>@pedroaihara</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pauloteixeira13</t>
+          <t>https://instagram.com/pedroaihara</t>
         </is>
       </c>
       <c r="I398" s="2" t="inlineStr"/>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>220630</v>
+        <v>220667</v>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>Pedro Aihara</t>
+          <t>Pedro Campos</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
+          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>dep.pedroaihara@camara.leg.br</t>
+          <t>dep.pedrocampos@camara.leg.br</t>
         </is>
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>@pedroaihara</t>
+          <t>@pedrocampospe</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedroaihara</t>
+          <t>https://instagram.com/pedrocampospe</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr"/>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>220667</v>
+        <v>122974</v>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Pedro Campos</t>
+          <t>Pedro Lucas Fernandes</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
+          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrocampos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G400" s="2" t="inlineStr">
-        <is>
-          <t>@pedrocampospe</t>
-        </is>
-      </c>
-      <c r="H400" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrocampospe</t>
-        </is>
-      </c>
+          <t>dep.pedrolucasfernandes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr"/>
+      <c r="H400" s="2" t="inlineStr"/>
       <c r="I400" s="2" t="inlineStr"/>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>122974</v>
+        <v>204395</v>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lucas Fernandes</t>
+          <t>Pedro Lupion</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
+          <t>PEDRO DEBONI LUPION MELLO</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolucasfernandes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G401" s="2" t="inlineStr"/>
-      <c r="H401" s="2" t="inlineStr"/>
+          <t>dep.pedrolupion@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>@pedrolupion</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrolupion</t>
+        </is>
+      </c>
       <c r="I401" s="2" t="inlineStr"/>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>204395</v>
+        <v>122158</v>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lupion</t>
+          <t>Pedro Paulo</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DEBONI LUPION MELLO</t>
+          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolupion@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G402" s="2" t="inlineStr">
-        <is>
-          <t>@pedrolupion</t>
-        </is>
-      </c>
-      <c r="H402" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrolupion</t>
-        </is>
-      </c>
+          <t>dep.pedropaulo@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr"/>
+      <c r="H402" s="2" t="inlineStr"/>
       <c r="I402" s="2" t="inlineStr"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>122158</v>
+        <v>160604</v>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Pedro Paulo</t>
+          <t>Pedro Uczai</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
+          <t>PEDRO FRANCISCO UCZAI</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>dep.pedropaulo@camara.leg.br</t>
+          <t>dep.pedrouczai@camara.leg.br</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr"/>
@@ -18190,37 +18182,37 @@
       <c r="I403" s="2" t="inlineStr"/>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>160604</v>
+        <v>204406</v>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Pedro Uczai</t>
+          <t>Pedro Westphalen</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>PEDRO FRANCISCO UCZAI</t>
+          <t>PEDRO BANDARRA WESTPHALEN</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrouczai@camara.leg.br</t>
+          <t>dep.pedrowestphalen@camara.leg.br</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr"/>
@@ -18228,612 +18220,612 @@
       <c r="I404" s="2" t="inlineStr"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>204406</v>
+        <v>161440</v>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Pedro Westphalen</t>
+          <t>Pezenti</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>PEDRO BANDARRA WESTPHALEN</t>
+          <t>RAFAEL PEZENTI</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrowestphalen@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G405" s="2" t="inlineStr"/>
-      <c r="H405" s="2" t="inlineStr"/>
+          <t>dep.pezenti@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>@deputadopezenti</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadopezenti</t>
+        </is>
+      </c>
       <c r="I405" s="2" t="inlineStr"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>161440</v>
+        <v>204524</v>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Pezenti</t>
+          <t>Pinheirinho</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL PEZENTI</t>
+          <t>ANTÔNIO PINHEIRO NETO</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>dep.pezenti@camara.leg.br</t>
+          <t>dep.pinheirinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>@deputadopezenti</t>
+          <t>@pinheirinhomg</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadopezenti</t>
-        </is>
-      </c>
-      <c r="I406" s="2" t="inlineStr"/>
+          <t>https://instagram.com/pinheirinhomg</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
+        </is>
+      </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>204524</v>
+        <v>73486</v>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>Pinheirinho</t>
+          <t>Pompeo de Mattos</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>ANTÔNIO PINHEIRO NETO</t>
+          <t>DARCI POMPEO DE MATTOS</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>dep.pinheirinho@camara.leg.br</t>
+          <t>dep.pompeodemattos@camara.leg.br</t>
         </is>
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>@pinheirinhomg</t>
+          <t>@pompeodemattospdt</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pinheirinhomg</t>
+          <t>https://instagram.com/pompeodemattospdt</t>
         </is>
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
+          <t>https://youtube.com/PompeodeMattos</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>73486</v>
+        <v>160601</v>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Pompeo de Mattos</t>
+          <t>Pr. Marco Feliciano</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>DARCI POMPEO DE MATTOS</t>
+          <t>MARCO ANTÔNIO FELICIANO</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>dep.pompeodemattos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G408" s="2" t="inlineStr">
-        <is>
-          <t>@pompeodemattospdt</t>
-        </is>
-      </c>
-      <c r="H408" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pompeodemattospdt</t>
-        </is>
-      </c>
-      <c r="I408" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/PompeodeMattos</t>
-        </is>
-      </c>
+          <t>dep.pr.marcofeliciano@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr"/>
+      <c r="H408" s="2" t="inlineStr"/>
+      <c r="I408" s="2" t="inlineStr"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>160601</v>
+        <v>220533</v>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Pr. Marco Feliciano</t>
+          <t>Prof. Reginaldo Veras</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>MARCO ANTÔNIO FELICIANO</t>
+          <t>Reginaldo Veras Coelho</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>dep.pr.marcofeliciano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G409" s="2" t="inlineStr"/>
-      <c r="H409" s="2" t="inlineStr"/>
-      <c r="I409" s="2" t="inlineStr"/>
+          <t>dep.prof.reginaldoveras@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>@reginaldo.veras</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/reginaldo.veras</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/Reginaldoveras12</t>
+        </is>
+      </c>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>220533</v>
+        <v>204390</v>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Prof. Reginaldo Veras</t>
+          <t>Professor Alcides</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Veras Coelho</t>
+          <t>ALCIDES RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>dep.prof.reginaldoveras@camara.leg.br</t>
+          <t>dep.professoralcides@camara.leg.br</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>@reginaldo.veras</t>
+          <t>@professoralcidesoficial</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/reginaldo.veras</t>
+          <t>https://instagram.com/professoralcidesoficial</t>
         </is>
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/Reginaldoveras12</t>
+          <t>https://youtube.com/DeputadoProfessorAlcides</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>204390</v>
+        <v>221338</v>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Professor Alcides</t>
+          <t>Professora Luciene Cavalcante</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>ALCIDES RIBEIRO FILHO</t>
+          <t>LUCIENE CAVALCANTE DA SILVA</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralcides@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G411" s="2" t="inlineStr">
-        <is>
-          <t>@professoralcidesoficial</t>
-        </is>
-      </c>
-      <c r="H411" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/professoralcidesoficial</t>
-        </is>
-      </c>
-      <c r="I411" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/DeputadoProfessorAlcides</t>
-        </is>
-      </c>
+          <t>dep.professoralucienecavalcante@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr"/>
+      <c r="H411" s="2" t="inlineStr"/>
+      <c r="I411" s="2" t="inlineStr"/>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>221338</v>
+        <v>160641</v>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Professora Luciene Cavalcante</t>
+          <t>Professora Marcivania</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>LUCIENE CAVALCANTE DA SILVA</t>
+          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralucienecavalcante@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G412" s="2" t="inlineStr"/>
-      <c r="H412" s="2" t="inlineStr"/>
+          <t>dep.professoramarcivania@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>@profmarcivania</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/profmarcivania</t>
+        </is>
+      </c>
       <c r="I412" s="2" t="inlineStr"/>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>160641</v>
+        <v>220586</v>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Professora Marcivania</t>
+          <t>Rafael Brito</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
+          <t>RAFAEL DE GOES BRITO</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>dep.professoramarcivania@camara.leg.br</t>
+          <t>dep.rafaelbrito@camara.leg.br</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>@profmarcivania</t>
+          <t>@rafaelbrito15</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/profmarcivania</t>
-        </is>
-      </c>
-      <c r="I413" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
+        </is>
+      </c>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>220586</v>
+        <v>233594</v>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Rafael Brito</t>
+          <t>Rafael Fera</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL DE GOES BRITO</t>
+          <t>RAFAEL BENTO PEREIRA</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelbrito@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="H414" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="I414" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
-        </is>
-      </c>
+          <t>dep.rafaelfera@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr"/>
+      <c r="H414" s="2" t="inlineStr"/>
+      <c r="I414" s="2" t="inlineStr"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>233594</v>
+        <v>220532</v>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Rafael Fera</t>
+          <t>Rafael Prudente</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL BENTO PEREIRA</t>
+          <t>RAFAEL CAVALCANTI PRUDENTE</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelfera@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G415" s="2" t="inlineStr"/>
-      <c r="H415" s="2" t="inlineStr"/>
-      <c r="I415" s="2" t="inlineStr"/>
+          <t>dep.rafaelprudente@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RafaelPrudente</t>
+        </is>
+      </c>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>220532</v>
+        <v>220626</v>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Rafael Prudente</t>
+          <t>Rafael Simoes</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL CAVALCANTI PRUDENTE</t>
+          <t>RAFAEL TADEU SIMÕES</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelprudente@camara.leg.br</t>
+          <t>dep.rafaelsimoes@camara.leg.br</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>@rafaelprudentedep</t>
+          <t>@rafaelsimoesmg</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="I416" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RafaelPrudente</t>
-        </is>
-      </c>
+          <t>https://instagram.com/rafaelsimoesmg</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr"/>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>220626</v>
+        <v>204567</v>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Rafael Simoes</t>
+          <t>Raimundo Costa</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL TADEU SIMÕES</t>
+          <t>RAIMUNDO MAGALHÃES COSTA</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelsimoes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G417" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelsimoesmg</t>
-        </is>
-      </c>
-      <c r="H417" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelsimoesmg</t>
-        </is>
-      </c>
+          <t>dep.raimundocosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr"/>
+      <c r="H417" s="2" t="inlineStr"/>
       <c r="I417" s="2" t="inlineStr"/>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>204567</v>
+        <v>74084</v>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Costa</t>
+          <t>Raimundo Santos</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO MAGALHÃES COSTA</t>
+          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
@@ -18843,85 +18835,89 @@
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundocosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G418" s="2" t="inlineStr"/>
-      <c r="H418" s="2" t="inlineStr"/>
-      <c r="I418" s="2" t="inlineStr"/>
+          <t>dep.raimundosantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>@depraimundosantos</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depraimundosantos</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
+        </is>
+      </c>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>74084</v>
+        <v>74161</v>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Santos</t>
+          <t>Reginaldo Lopes</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
+          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundosantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G419" s="2" t="inlineStr">
-        <is>
-          <t>@depraimundosantos</t>
-        </is>
-      </c>
-      <c r="H419" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depraimundosantos</t>
-        </is>
-      </c>
+          <t>dep.reginaldolopes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr"/>
+      <c r="H419" s="2" t="inlineStr"/>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
+          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>74161</v>
+        <v>220606</v>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Lopes</t>
+          <t>Reimont</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
+          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
@@ -18931,54 +18927,50 @@
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>dep.reginaldolopes@camara.leg.br</t>
+          <t>dep.reimont@camara.leg.br</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr"/>
       <c r="H420" s="2" t="inlineStr"/>
-      <c r="I420" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
-        </is>
-      </c>
+      <c r="I420" s="2" t="inlineStr"/>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>220606</v>
+        <v>178989</v>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>Reimont</t>
+          <t>Renata Abreu</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
+          <t>RENATA HELLMEISTER DE ABREU</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>dep.reimont@camara.leg.br</t>
+          <t>dep.renataabreu@camara.leg.br</t>
         </is>
       </c>
       <c r="G421" s="2" t="inlineStr"/>
@@ -18986,645 +18978,645 @@
       <c r="I421" s="2" t="inlineStr"/>
       <c r="J421" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178989</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>178989</v>
+        <v>153423</v>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>Renata Abreu</t>
+          <t>Renilce Nicodemos</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>RENATA HELLMEISTER DE ABREU</t>
+          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>dep.renataabreu@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G422" s="2" t="inlineStr"/>
-      <c r="H422" s="2" t="inlineStr"/>
+          <t>dep.renilcenicodemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>@renilcenicodemoss</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/renilcenicodemoss</t>
+        </is>
+      </c>
       <c r="I422" s="2" t="inlineStr"/>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178989</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>153423</v>
+        <v>73801</v>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>Renilce Nicodemos</t>
+          <t>Renildo Calheiros</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
+          <t>RENILDO VASCONCELOS CALHEIROS</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>dep.renilcenicodemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G423" s="2" t="inlineStr">
-        <is>
-          <t>@renilcenicodemoss</t>
-        </is>
-      </c>
-      <c r="H423" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/renilcenicodemoss</t>
-        </is>
-      </c>
+          <t>dep.renildocalheiros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr"/>
+      <c r="H423" s="2" t="inlineStr"/>
       <c r="I423" s="2" t="inlineStr"/>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>73801</v>
+        <v>175765</v>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>Renildo Calheiros</t>
+          <t>Ribamar Silva</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>RENILDO VASCONCELOS CALHEIROS</t>
+          <t>RIBAMAR ANTONIO DA SILVA</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>dep.renildocalheiros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G424" s="2" t="inlineStr"/>
-      <c r="H424" s="2" t="inlineStr"/>
+          <t>dep.ribamarsilva@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>@ribamarsilvaoficial</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ribamarsilvaoficial</t>
+        </is>
+      </c>
       <c r="I424" s="2" t="inlineStr"/>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>175765</v>
+        <v>235088</v>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>Ribamar Silva</t>
+          <t>Ribeiro Neto</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>RIBAMAR ANTONIO DA SILVA</t>
+          <t>AIRES DO ESPIRITO SANTO RIBEIRO NETO</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>dep.ribamarsilva@camara.leg.br</t>
+          <t>dep.ribeironeto@camara.leg.br</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>@ribamarsilvaoficial</t>
+          <t>@ribeironeto.ma</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ribamarsilvaoficial</t>
+          <t>https://instagram.com/ribeironeto.ma</t>
         </is>
       </c>
       <c r="I425" s="2" t="inlineStr"/>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235088</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>235088</v>
+        <v>221329</v>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>Ribeiro Neto</t>
+          <t>Ricardo Abrão</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>AIRES DO ESPIRITO SANTO RIBEIRO NETO</t>
+          <t>RICARDO MARTINS DAVID</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>dep.ribeironeto@camara.leg.br</t>
+          <t>dep.ricardoabrao@camara.leg.br</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>@ribeironeto.ma</t>
+          <t>@ricardoabraooficial</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ribeironeto.ma</t>
+          <t>https://instagram.com/ricardoabraooficial</t>
         </is>
       </c>
       <c r="I426" s="2" t="inlineStr"/>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235088</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>221329</v>
+        <v>220543</v>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Abrão</t>
+          <t>Ricardo Ayres</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MARTINS DAVID</t>
+          <t>RICARDO AYRES DE CARVALHO</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoabrao@camara.leg.br</t>
+          <t>dep.ricardoayres@camara.leg.br</t>
         </is>
       </c>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>@ricardoabraooficial</t>
+          <t>@ricardoayres_to</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardoabraooficial</t>
+          <t>https://instagram.com/ricardoayres_to</t>
         </is>
       </c>
       <c r="I427" s="2" t="inlineStr"/>
       <c r="J427" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>220543</v>
+        <v>73788</v>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Ayres</t>
+          <t>Ricardo Barros</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>RICARDO AYRES DE CARVALHO</t>
+          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoayres@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G428" s="2" t="inlineStr">
-        <is>
-          <t>@ricardoayres_to</t>
-        </is>
-      </c>
-      <c r="H428" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ricardoayres_to</t>
-        </is>
-      </c>
+          <t>dep.ricardobarros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr"/>
+      <c r="H428" s="2" t="inlineStr"/>
       <c r="I428" s="2" t="inlineStr"/>
       <c r="J428" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>73788</v>
+        <v>204362</v>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Barros</t>
+          <t>Ricardo Guidi</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
+          <t>RICARDO ZANATTA GUIDI</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardobarros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G429" s="2" t="inlineStr"/>
-      <c r="H429" s="2" t="inlineStr"/>
+          <t>dep.ricardoguidi@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>@ricardozguidi</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ricardozguidi</t>
+        </is>
+      </c>
       <c r="I429" s="2" t="inlineStr"/>
       <c r="J429" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>204362</v>
+        <v>220694</v>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Guidi</t>
+          <t>Ricardo Maia</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>RICARDO ZANATTA GUIDI</t>
+          <t>RICARDO MAIA CHAVES DE SOUZA</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoguidi@camara.leg.br</t>
+          <t>dep.ricardomaia@camara.leg.br</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>@ricardozguidi</t>
+          <t>@ricardomaia.dabahia</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardozguidi</t>
-        </is>
-      </c>
-      <c r="I430" s="2" t="inlineStr"/>
+          <t>https://instagram.com/ricardomaia.dabahia</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/ricardomaiadabahia5610</t>
+        </is>
+      </c>
       <c r="J430" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>220694</v>
+        <v>220633</v>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Maia</t>
+          <t>Ricardo Salles</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MAIA CHAVES DE SOUZA</t>
+          <t>RICARDO DE AQUINO SALLES</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardomaia@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G431" s="2" t="inlineStr">
-        <is>
-          <t>@ricardomaia.dabahia</t>
-        </is>
-      </c>
-      <c r="H431" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ricardomaia.dabahia</t>
-        </is>
-      </c>
-      <c r="I431" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/ricardomaiadabahia5610</t>
-        </is>
-      </c>
+          <t>dep.ricardosalles@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr"/>
+      <c r="H431" s="2" t="inlineStr"/>
+      <c r="I431" s="2" t="inlineStr"/>
       <c r="J431" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>220633</v>
+        <v>204489</v>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Salles</t>
+          <t>Robério Monteiro</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DE AQUINO SALLES</t>
+          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardosalles@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G432" s="2" t="inlineStr"/>
-      <c r="H432" s="2" t="inlineStr"/>
+          <t>dep.roberiomonteiro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>@dep.roberiomonteiro</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dep.roberiomonteiro</t>
+        </is>
+      </c>
       <c r="I432" s="2" t="inlineStr"/>
       <c r="J432" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>204489</v>
+        <v>220693</v>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>Robério Monteiro</t>
+          <t>Roberta Roma</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
+          <t>Roberta de Araujo Costa Roma</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>dep.roberiomonteiro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G433" s="2" t="inlineStr">
-        <is>
-          <t>@dep.roberiomonteiro</t>
-        </is>
-      </c>
-      <c r="H433" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/dep.roberiomonteiro</t>
-        </is>
-      </c>
+          <t>dep.robertaroma@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr"/>
+      <c r="H433" s="2" t="inlineStr"/>
       <c r="I433" s="2" t="inlineStr"/>
       <c r="J433" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>220693</v>
+        <v>220588</v>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>Roberta Roma</t>
+          <t>Roberto Duarte</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>Roberta de Araujo Costa Roma</t>
+          <t>ROBERTO DUARTE JUNIOR</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>dep.robertaroma@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G434" s="2" t="inlineStr"/>
-      <c r="H434" s="2" t="inlineStr"/>
+          <t>dep.robertoduarte@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>@rdnarede</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rdnarede</t>
+        </is>
+      </c>
       <c r="I434" s="2" t="inlineStr"/>
       <c r="J434" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>220588</v>
+        <v>220613</v>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>Roberto Duarte</t>
+          <t>Roberto Monteiro Pai</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO DUARTE JUNIOR</t>
+          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>dep.robertoduarte@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G435" s="2" t="inlineStr">
-        <is>
-          <t>@rdnarede</t>
-        </is>
-      </c>
-      <c r="H435" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rdnarede</t>
-        </is>
-      </c>
+          <t>dep.robertomonteiropai@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr"/>
+      <c r="H435" s="2" t="inlineStr"/>
       <c r="I435" s="2" t="inlineStr"/>
       <c r="J435" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>220613</v>
+        <v>220624</v>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>Roberto Monteiro Pai</t>
+          <t>Robinson Faria</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
+          <t>ROBINSON MESQUITA DE FARIA</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>dep.robertomonteiropai@camara.leg.br</t>
+          <t>dep.robinsonfaria@camara.leg.br</t>
         </is>
       </c>
       <c r="G436" s="2" t="inlineStr"/>
@@ -19632,60 +19624,72 @@
       <c r="I436" s="2" t="inlineStr"/>
       <c r="J436" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>220624</v>
+        <v>220546</v>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>Robinson Faria</t>
+          <t>Rodolfo Nogueira</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>ROBINSON MESQUITA DE FARIA</t>
+          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>dep.robinsonfaria@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G437" s="2" t="inlineStr"/>
-      <c r="H437" s="2" t="inlineStr"/>
-      <c r="I437" s="2" t="inlineStr"/>
+          <t>dep.rodolfonogueira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>@rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RodolfoNogueirams</t>
+        </is>
+      </c>
       <c r="J437" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>220546</v>
+        <v>230767</v>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>Rodolfo Nogueira</t>
+          <t>Rodrigo da Zaeli</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
+          <t>RODRIGO LUGLI</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
@@ -19695,507 +19699,507 @@
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>dep.rodolfonogueira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>@rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="H438" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="I438" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RodolfoNogueirams</t>
-        </is>
-      </c>
+          <t>dep.rodrigodazaeli@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr"/>
+      <c r="H438" s="2" t="inlineStr"/>
+      <c r="I438" s="2" t="inlineStr"/>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>230767</v>
+        <v>141531</v>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo da Zaeli</t>
+          <t>Rodrigo de Castro</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO LUGLI</t>
+          <t>RODRIGO BATISTA DE CASTRO</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodazaeli@camara.leg.br</t>
+          <t>dep.rodrigodecastro@camara.leg.br</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr"/>
       <c r="H439" s="2" t="inlineStr"/>
-      <c r="I439" s="2" t="inlineStr"/>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>http://www.youtube.com/rodrigocastro45</t>
+        </is>
+      </c>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>141531</v>
+        <v>220641</v>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo de Castro</t>
+          <t>Rodrigo Gambale</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO BATISTA DE CASTRO</t>
+          <t>RODRIGO GAMBALE VIEIRA</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodecastro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G440" s="2" t="inlineStr"/>
-      <c r="H440" s="2" t="inlineStr"/>
-      <c r="I440" s="2" t="inlineStr">
-        <is>
-          <t>http://www.youtube.com/rodrigocastro45</t>
-        </is>
-      </c>
+          <t>dep.rodrigogambale@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>@rodrigogambale</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodrigogambale</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr"/>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>220641</v>
+        <v>141533</v>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Gambale</t>
+          <t>Rodrigo Rollemberg</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO GAMBALE VIEIRA</t>
+          <t>RODRIGO SOBRAL ROLLEMBERG</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigogambale@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G441" s="2" t="inlineStr">
-        <is>
-          <t>@rodrigogambale</t>
-        </is>
-      </c>
-      <c r="H441" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodrigogambale</t>
-        </is>
-      </c>
+          <t>dep.rodrigorollemberg@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr"/>
+      <c r="H441" s="2" t="inlineStr"/>
       <c r="I441" s="2" t="inlineStr"/>
       <c r="J441" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>141533</v>
+        <v>165470</v>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Rollemberg</t>
+          <t>Rodrigo Valadares</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SOBRAL ROLLEMBERG</t>
+          <t>RODRIGO SANTANA VALADARES</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigorollemberg@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G442" s="2" t="inlineStr"/>
-      <c r="H442" s="2" t="inlineStr"/>
-      <c r="I442" s="2" t="inlineStr"/>
+          <t>dep.rodrigovaladares@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>@rodrigovaladares_</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodrigovaladares_</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/deputadorodrigovaladares1954</t>
+        </is>
+      </c>
       <c r="J442" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>165470</v>
+        <v>220695</v>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Valadares</t>
+          <t>Rogéria Santos</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SANTANA VALADARES</t>
+          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigovaladares@camara.leg.br</t>
+          <t>dep.rogeriasantos@camara.leg.br</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>@rodrigovaladares_</t>
+          <t>@rogeriasantosoficial</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rodrigovaladares_</t>
+          <t>https://instagram.com/rogeriasantosoficial</t>
         </is>
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/deputadorodrigovaladares1954</t>
+          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>220695</v>
+        <v>204480</v>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>Rogéria Santos</t>
+          <t>Rogério Correia</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
+          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriasantos@camara.leg.br</t>
+          <t>dep.rogeriocorreia@camara.leg.br</t>
         </is>
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>@rogeriasantosoficial</t>
+          <t>@rogeriocorreia_</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriasantosoficial</t>
+          <t>https://instagram.com/rogeriocorreia_</t>
         </is>
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
+          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>204480</v>
+        <v>160629</v>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>Rogério Correia</t>
+          <t>Romero Rodrigues</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
+          <t>ROMERO RODRIGUES VEIGA</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriocorreia@camara.leg.br</t>
+          <t>dep.romerorodrigues@camara.leg.br</t>
         </is>
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>@rogeriocorreia_</t>
+          <t>@romerorodriguespb</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriocorreia_</t>
+          <t>https://instagram.com/romerorodriguespb</t>
         </is>
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
+          <t>https://youtube.com/romerorodriguespb</t>
         </is>
       </c>
       <c r="J445" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160629</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>160629</v>
+        <v>204525</v>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>Romero Rodrigues</t>
+          <t>Rosana Valle</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>ROMERO RODRIGUES VEIGA</t>
+          <t>ROSANA DE OLIVEIRA VALLE</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>dep.romerorodrigues@camara.leg.br</t>
+          <t>dep.rosanavalle@camara.leg.br</t>
         </is>
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>@romerorodriguespb</t>
+          <t>@rosanavalleoficial</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/romerorodriguespb</t>
+          <t>https://instagram.com/rosanavalleoficial</t>
         </is>
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/romerorodriguespb</t>
+          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160629</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>204525</v>
+        <v>178945</v>
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>Rosana Valle</t>
+          <t>Rosangela Gomes</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>ROSANA DE OLIVEIRA VALLE</t>
+          <t>ROSANGELA DE SOUZA GOMES</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>dep.rosanavalle@camara.leg.br</t>
+          <t>dep.rosangelagomes@camara.leg.br</t>
         </is>
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>@rosanavalleoficial</t>
+          <t>@rosangelasgomes</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosanavalleoficial</t>
-        </is>
-      </c>
-      <c r="I447" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/rosangelasgomes</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr"/>
       <c r="J447" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>178945</v>
+        <v>220644</v>
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Gomes</t>
+          <t>Rosangela Moro</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE SOUZA GOMES</t>
+          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelagomes@camara.leg.br</t>
+          <t>dep.rosangelamoro@camara.leg.br</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>@rosangelasgomes</t>
+          <t>@rosangelawmoro</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosangelasgomes</t>
-        </is>
-      </c>
-      <c r="I448" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rosangelawmoro</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC5X-86dz8GEf6QGMm95ZoAA</t>
+        </is>
+      </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>220644</v>
+        <v>220620</v>
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Moro</t>
+          <t>Rosângela Reis</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
+          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
@@ -20205,93 +20209,81 @@
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelamoro@camara.leg.br</t>
+          <t>dep.rosangelareis@camara.leg.br</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>@rosangelawmoro</t>
+          <t>@rosangelareis.mg</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosangelawmoro</t>
-        </is>
-      </c>
-      <c r="I449" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC5X-86dz8GEf6QGMm95ZoAA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/rosangelareis.mg</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr"/>
       <c r="J449" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>220620</v>
+        <v>74371</v>
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>Rosângela Reis</t>
+          <t>Rubens Otoni</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
+          <t>RUBENS OTONI GOMIDE</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelareis@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G450" s="2" t="inlineStr">
-        <is>
-          <t>@rosangelareis.mg</t>
-        </is>
-      </c>
-      <c r="H450" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rosangelareis.mg</t>
-        </is>
-      </c>
+          <t>dep.rubensotoni@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr"/>
+      <c r="H450" s="2" t="inlineStr"/>
       <c r="I450" s="2" t="inlineStr"/>
       <c r="J450" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>74371</v>
+        <v>178887</v>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>Rubens Otoni</t>
+          <t>Rubens Pereira Júnior</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>RUBENS OTONI GOMIDE</t>
+          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
@@ -20301,35 +20293,47 @@
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>dep.rubensotoni@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G451" s="2" t="inlineStr"/>
-      <c r="H451" s="2" t="inlineStr"/>
-      <c r="I451" s="2" t="inlineStr"/>
+          <t>dep.rubenspereirajunior@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>@rubenspereirajr</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rubenspereirajr</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
+        </is>
+      </c>
       <c r="J451" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>178887</v>
+        <v>73604</v>
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>Rubens Pereira Júnior</t>
+          <t>Rui Falcão</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
+          <t>RUI GOETHE DA COSTA FALCÃO</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -20339,298 +20343,286 @@
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>dep.rubenspereirajunior@camara.leg.br</t>
+          <t>dep.ruifalcao@camara.leg.br</t>
         </is>
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>@rubenspereirajr</t>
+          <t>@ruifalcao13</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rubenspereirajr</t>
+          <t>https://instagram.com/ruifalcao13</t>
         </is>
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
+          <t>https://youtube.com/rfalcao13</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>73604</v>
+        <v>160635</v>
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>Rui Falcão</t>
+          <t>Ruy Carneiro</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>RUI GOETHE DA COSTA FALCÃO</t>
+          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>dep.ruifalcao@camara.leg.br</t>
+          <t>dep.ruycarneiro@camara.leg.br</t>
         </is>
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>@ruifalcao13</t>
+          <t>@ruy.carneiro</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruifalcao13</t>
-        </is>
-      </c>
-      <c r="I453" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/rfalcao13</t>
-        </is>
-      </c>
+          <t>https://instagram.com/ruy.carneiro</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr"/>
       <c r="J453" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>160635</v>
+        <v>204535</v>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>Ruy Carneiro</t>
+          <t>Sâmia Bomfim</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
+          <t>SAMIA DE SOUZA BOMFIM</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>dep.ruycarneiro@camara.leg.br</t>
+          <t>dep.samiabomfim@camara.leg.br</t>
         </is>
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>@ruy.carneiro</t>
+          <t>@samiabomfim</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruy.carneiro</t>
-        </is>
-      </c>
-      <c r="I454" s="2" t="inlineStr"/>
+          <t>https://instagram.com/samiabomfim</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/samiabomfimpsol</t>
+        </is>
+      </c>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>204535</v>
+        <v>220631</v>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>Sâmia Bomfim</t>
+          <t>Samuel Viana</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>SAMIA DE SOUZA BOMFIM</t>
+          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>dep.samiabomfim@camara.leg.br</t>
+          <t>dep.samuelviana@camara.leg.br</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>@samiabomfim</t>
+          <t>@vianasamuel</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/samiabomfim</t>
+          <t>https://instagram.com/vianasamuel</t>
         </is>
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/samiabomfimpsol</t>
+          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>220631</v>
+        <v>204416</v>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>Samuel Viana</t>
+          <t>Sanderson</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
+          <t>UBIRATAN ANTUNES SANDERSON</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>dep.samuelviana@camara.leg.br</t>
+          <t>dep.sanderson@camara.leg.br</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>@vianasamuel</t>
+          <t>@deputadosanderson</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/vianasamuel</t>
+          <t>https://instagram.com/deputadosanderson</t>
         </is>
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
+          <t>https://youtube.com/channel/UC3bESW2nMM1EW-in7OwlKwg?view_as=subscriber</t>
         </is>
       </c>
       <c r="J456" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>204416</v>
+        <v>160621</v>
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>Sanderson</t>
+          <t>Sandro Alex</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>UBIRATAN ANTUNES SANDERSON</t>
+          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>dep.sanderson@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G457" s="2" t="inlineStr">
-        <is>
-          <t>@deputadosanderson</t>
-        </is>
-      </c>
-      <c r="H457" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadosanderson</t>
-        </is>
-      </c>
-      <c r="I457" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC3bESW2nMM1EW-in7OwlKwg?view_as=subscriber</t>
-        </is>
-      </c>
+          <t>dep.sandroalex@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr"/>
+      <c r="H457" s="2" t="inlineStr"/>
+      <c r="I457" s="2" t="inlineStr"/>
       <c r="J457" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>160621</v>
+        <v>204387</v>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Sandro Alex</t>
+          <t>Sargento Fahur</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
+          <t>GILSON CARDOSO FAHUR</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -20640,30 +20632,42 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>dep.sandroalex@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G458" s="2" t="inlineStr"/>
-      <c r="H458" s="2" t="inlineStr"/>
-      <c r="I458" s="2" t="inlineStr"/>
+          <t>dep.sargentofahur@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>@sargentofahurpr</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sargentofahurpr</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCGtU73VeRj9hY1P3PtVUERw</t>
+        </is>
+      </c>
       <c r="J458" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204387</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>204387</v>
+        <v>220621</v>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Sargento Fahur</t>
+          <t>Sargento Gonçalves</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>GILSON CARDOSO FAHUR</t>
+          <t>EVANDRO GONÇALVES DA SILVA JÚNIOR</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
@@ -20673,181 +20677,169 @@
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentofahur@camara.leg.br</t>
+          <t>dep.sargentogoncalves@camara.leg.br</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>@sargentofahurpr</t>
+          <t>@sargentogoncalves22</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sargentofahurpr</t>
-        </is>
-      </c>
-      <c r="I459" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCGtU73VeRj9hY1P3PtVUERw</t>
-        </is>
-      </c>
+          <t>https://instagram.com/sargentogoncalves22</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr"/>
       <c r="J459" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204387</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220621</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>220621</v>
+        <v>220618</v>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>Sargento Gonçalves</t>
+          <t>Sargento Portugal</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>EVANDRO GONÇALVES DA SILVA JÚNIOR</t>
+          <t>JOSÉ PORTUGAL NETO</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentogoncalves@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G460" s="2" t="inlineStr">
-        <is>
-          <t>@sargentogoncalves22</t>
-        </is>
-      </c>
-      <c r="H460" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sargentogoncalves22</t>
-        </is>
-      </c>
+          <t>dep.sargentoportugal@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr"/>
+      <c r="H460" s="2" t="inlineStr"/>
       <c r="I460" s="2" t="inlineStr"/>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220621</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220618</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>220618</v>
+        <v>220713</v>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>Sargento Portugal</t>
+          <t>Saullo Vianna</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ PORTUGAL NETO</t>
+          <t>SAULLO VELAME VIANNA</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentoportugal@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G461" s="2" t="inlineStr"/>
-      <c r="H461" s="2" t="inlineStr"/>
-      <c r="I461" s="2" t="inlineStr"/>
+          <t>dep.saullovianna@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>@saullovianna</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/saullovianna</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/SaulloVianna</t>
+        </is>
+      </c>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220618</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220713</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>220713</v>
+        <v>226837</v>
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>Saullo Vianna</t>
+          <t>Saulo Pedroso</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>SAULLO VELAME VIANNA</t>
+          <t>SAULO PEDROSO DE SOUZA</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>dep.saullovianna@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G462" s="2" t="inlineStr">
-        <is>
-          <t>@saullovianna</t>
-        </is>
-      </c>
-      <c r="H462" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/saullovianna</t>
-        </is>
-      </c>
-      <c r="I462" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/SaulloVianna</t>
-        </is>
-      </c>
+          <t>dep.saulopedroso@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr"/>
+      <c r="H462" s="2" t="inlineStr"/>
+      <c r="I462" s="2" t="inlineStr"/>
       <c r="J462" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220713</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226837</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>226837</v>
+        <v>73808</v>
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>Saulo Pedroso</t>
+          <t>Sérgio Brito</t>
         </is>
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>SAULO PEDROSO DE SOUZA</t>
+          <t>SÉRGIO LUÍS LACERDA BRITO</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
@@ -20857,12 +20849,12 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>dep.saulopedroso@camara.leg.br</t>
+          <t>dep.sergiobrito@camara.leg.br</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr"/>
@@ -20870,125 +20862,125 @@
       <c r="I463" s="2" t="inlineStr"/>
       <c r="J463" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226837</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73808</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>73808</v>
+        <v>178933</v>
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Brito</t>
+          <t>Sergio Souza</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>SÉRGIO LUÍS LACERDA BRITO</t>
+          <t>SERGIO DE SOUZA</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>dep.sergiobrito@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G464" s="2" t="inlineStr"/>
-      <c r="H464" s="2" t="inlineStr"/>
-      <c r="I464" s="2" t="inlineStr"/>
+          <t>dep.sergiosouza@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>@sergiosouzapr</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sergiosouzapr</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/deputadofederalsergiosouza</t>
+        </is>
+      </c>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73808</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178933</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>178933</v>
+        <v>235776</v>
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>Sergio Souza</t>
+          <t>Sérgio Turra</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>SERGIO DE SOUZA</t>
+          <t>SERGIO BERGONSI TURRA</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>dep.sergiosouza@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G465" s="2" t="inlineStr">
-        <is>
-          <t>@sergiosouzapr</t>
-        </is>
-      </c>
-      <c r="H465" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sergiosouzapr</t>
-        </is>
-      </c>
-      <c r="I465" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadofederalsergiosouza</t>
-        </is>
-      </c>
+          <t>dep.sergioturra@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr"/>
+      <c r="H465" s="2" t="inlineStr"/>
+      <c r="I465" s="2" t="inlineStr"/>
       <c r="J465" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178933</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235776</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>235776</v>
+        <v>204557</v>
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Turra</t>
+          <t>Sidney Leite</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>SERGIO BERGONSI TURRA</t>
+          <t>SIDNEY RICARDO DE OLIVEIRA LEITE</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>dep.sergioturra@camara.leg.br</t>
+          <t>dep.sidneyleite@camara.leg.br</t>
         </is>
       </c>
       <c r="G466" s="2" t="inlineStr"/>
@@ -20996,37 +20988,37 @@
       <c r="I466" s="2" t="inlineStr"/>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235776</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204557</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>204557</v>
+        <v>204360</v>
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>Sidney Leite</t>
+          <t>Silvia Cristina</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>SIDNEY RICARDO DE OLIVEIRA LEITE</t>
+          <t>SILVIA CRISTINA AMANCIO CHAGAS</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>dep.sidneyleite@camara.leg.br</t>
+          <t>dep.silviacristina@camara.leg.br</t>
         </is>
       </c>
       <c r="G467" s="2" t="inlineStr"/>
@@ -21034,206 +21026,206 @@
       <c r="I467" s="2" t="inlineStr"/>
       <c r="J467" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204557</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204360</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>204360</v>
+        <v>227310</v>
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>Silvia Cristina</t>
+          <t>Silvio Antonio</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>SILVIA CRISTINA AMANCIO CHAGAS</t>
+          <t>SILVIO ANTONIO GUIMARAES MACHADO</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>dep.silviacristina@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G468" s="2" t="inlineStr"/>
-      <c r="H468" s="2" t="inlineStr"/>
-      <c r="I468" s="2" t="inlineStr"/>
+          <t>dep.silvioantonio@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>@silvioantonioma</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/silvioantonioma</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCmyO0mvtwWDuOmB9n0BaWRQ</t>
+        </is>
+      </c>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204360</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/227310</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>227310</v>
+        <v>204425</v>
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>Silvio Antonio</t>
+          <t>Silvio Costa Filho</t>
         </is>
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>SILVIO ANTONIO GUIMARAES MACHADO</t>
+          <t>SILVIO SERAFIM COSTA FILHO</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>dep.silvioantonio@camara.leg.br</t>
+          <t>dep.silviocostafilho@camara.leg.br</t>
         </is>
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>@silvioantonioma</t>
+          <t>@silviocostafilho</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/silvioantonioma</t>
+          <t>https://instagram.com/silviocostafilho</t>
         </is>
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCmyO0mvtwWDuOmB9n0BaWRQ</t>
+          <t>https://youtube.com/SilvioCostaFilhooficial</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/227310</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204425</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>204425</v>
+        <v>220569</v>
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>Silvio Costa Filho</t>
+          <t>Silvye Alves</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>SILVIO SERAFIM COSTA FILHO</t>
+          <t>SILVYE ALVES DA SILVA</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>dep.silviocostafilho@camara.leg.br</t>
+          <t>dep.silvyealves@camara.leg.br</t>
         </is>
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>@silviocostafilho</t>
+          <t>@silvyealves</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/silviocostafilho</t>
-        </is>
-      </c>
-      <c r="I470" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/SilvioCostaFilhooficial</t>
-        </is>
-      </c>
+          <t>https://instagram.com/silvyealves</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr"/>
       <c r="J470" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204425</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220569</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>220569</v>
+        <v>220651</v>
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>Silvye Alves</t>
+          <t>Simone Marquetto</t>
         </is>
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>SILVYE ALVES DA SILVA</t>
+          <t>SIMONE APARECIDA MARQUETO CURRALADAS</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>dep.silvyealves@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G471" s="2" t="inlineStr">
-        <is>
-          <t>@silvyealves</t>
-        </is>
-      </c>
-      <c r="H471" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/silvyealves</t>
-        </is>
-      </c>
+          <t>dep.simonemarquetto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr"/>
+      <c r="H471" s="2" t="inlineStr"/>
       <c r="I471" s="2" t="inlineStr"/>
       <c r="J471" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220569</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220651</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>220651</v>
+        <v>104552</v>
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>Simone Marquetto</t>
+          <t>Socorro Neri</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>SIMONE APARECIDA MARQUETO CURRALADAS</t>
+          <t>MARIA DO SOCORRO NERI MEDEIROS DE SOUZA</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
@@ -21243,119 +21235,131 @@
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>dep.simonemarquetto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G472" s="2" t="inlineStr"/>
-      <c r="H472" s="2" t="inlineStr"/>
+          <t>dep.socorroneri@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>@socorroneri</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/socorroneri</t>
+        </is>
+      </c>
       <c r="I472" s="2" t="inlineStr"/>
       <c r="J472" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220651</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/104552</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>104552</v>
+        <v>220643</v>
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>Socorro Neri</t>
+          <t>Sônia Guajajara</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>MARIA DO SOCORRO NERI MEDEIROS DE SOUZA</t>
+          <t>SONIA BONE DE SOUSA SILVA</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>dep.socorroneri@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G473" s="2" t="inlineStr">
-        <is>
-          <t>@socorroneri</t>
-        </is>
-      </c>
-      <c r="H473" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/socorroneri</t>
-        </is>
-      </c>
+          <t>dep.soniaguajajara@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr"/>
+      <c r="H473" s="2" t="inlineStr"/>
       <c r="I473" s="2" t="inlineStr"/>
       <c r="J473" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/104552</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220643</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>220643</v>
+        <v>178946</v>
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>Sônia Guajajara</t>
+          <t>Soraya Santos</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>SONIA BONE DE SOUSA SILVA</t>
+          <t>SORAYA ALENCAR DOS SANTOS</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>dep.soniaguajajara@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G474" s="2" t="inlineStr"/>
-      <c r="H474" s="2" t="inlineStr"/>
-      <c r="I474" s="2" t="inlineStr"/>
+          <t>dep.sorayasantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>@dep.sorayasantos</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dep.sorayasantos</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCYJ_VrjZS7ISX0Ut0bU_AMA</t>
+        </is>
+      </c>
       <c r="J474" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220643</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178946</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>178946</v>
+        <v>178947</v>
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>Soraya Santos</t>
+          <t>Sóstenes Cavalcante</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>SORAYA ALENCAR DOS SANTOS</t>
+          <t>SOSTENES SILVA CAVALCANTE</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
@@ -21370,203 +21374,191 @@
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>dep.sorayasantos@camara.leg.br</t>
+          <t>dep.sostenescavalcante@camara.leg.br</t>
         </is>
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>@dep.sorayasantos</t>
+          <t>@sostenescavalcante</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep.sorayasantos</t>
+          <t>https://instagram.com/sostenescavalcante</t>
         </is>
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/channel/UCYJ_VrjZS7ISX0Ut0bU_AMA</t>
+          <t>https://youtube.com/channel/UCI2j76o7JyLVSmooEcSvLxA</t>
         </is>
       </c>
       <c r="J475" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178946</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178947</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>178947</v>
+        <v>92776</v>
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>Sóstenes Cavalcante</t>
+          <t>Stefano Aguiar</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>SOSTENES SILVA CAVALCANTE</t>
+          <t>STEFANO AGUIAR DOS SANTOS</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>dep.sostenescavalcante@camara.leg.br</t>
+          <t>dep.stefanoaguiar@camara.leg.br</t>
         </is>
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
-          <t>@sostenescavalcante</t>
+          <t>@depstefano</t>
         </is>
       </c>
       <c r="H476" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sostenescavalcante</t>
-        </is>
-      </c>
-      <c r="I476" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCI2j76o7JyLVSmooEcSvLxA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/depstefano</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr"/>
       <c r="J476" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178947</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92776</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>92776</v>
+        <v>204534</v>
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>Stefano Aguiar</t>
+          <t>Tabata Amaral</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>STEFANO AGUIAR DOS SANTOS</t>
+          <t>TABATA CLAUDIA AMARAL DE PONTES</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>dep.stefanoaguiar@camara.leg.br</t>
+          <t>dep.tabataamaral@camara.leg.br</t>
         </is>
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>@depstefano</t>
+          <t>@tabataamaralsp</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/depstefano</t>
-        </is>
-      </c>
-      <c r="I477" s="2" t="inlineStr"/>
+          <t>https://instagram.com/tabataamaralsp</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCWcx5M5negY_kqSawo2bjZQ</t>
+        </is>
+      </c>
       <c r="J477" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92776</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204534</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>204534</v>
+        <v>220682</v>
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>Tabata Amaral</t>
+          <t>Tadeu Veneri</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>TABATA CLAUDIA AMARAL DE PONTES</t>
+          <t>ANTONIO TADEU VENERI</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>dep.tabataamaral@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G478" s="2" t="inlineStr">
-        <is>
-          <t>@tabataamaralsp</t>
-        </is>
-      </c>
-      <c r="H478" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/tabataamaralsp</t>
-        </is>
-      </c>
-      <c r="I478" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCWcx5M5negY_kqSawo2bjZQ</t>
-        </is>
-      </c>
+          <t>dep.tadeuveneri@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr"/>
+      <c r="H478" s="2" t="inlineStr"/>
+      <c r="I478" s="2" t="inlineStr"/>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204534</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220682</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>220682</v>
+        <v>204464</v>
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>Tadeu Veneri</t>
+          <t>Talíria Petrone</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO TADEU VENERI</t>
+          <t>TALIRIA PETRONE SOARES</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>dep.tadeuveneri@camara.leg.br</t>
+          <t>dep.taliriapetrone@camara.leg.br</t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr"/>
@@ -21574,22 +21566,22 @@
       <c r="I479" s="2" t="inlineStr"/>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220682</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204464</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>204464</v>
+        <v>220598</v>
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>Talíria Petrone</t>
+          <t>Tarcísio Motta</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>TALIRIA PETRONE SOARES</t>
+          <t>TARCISIO MOTTA DE CARVALHO</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
@@ -21604,191 +21596,191 @@
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>dep.taliriapetrone@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G480" s="2" t="inlineStr"/>
-      <c r="H480" s="2" t="inlineStr"/>
-      <c r="I480" s="2" t="inlineStr"/>
+          <t>dep.tarcisiomotta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>@tarcisiomottapsol</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tarcisiomottapsol</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/tarcisiomottapsol</t>
+        </is>
+      </c>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204464</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220598</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>220598</v>
+        <v>220560</v>
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>Tarcísio Motta</t>
+          <t>Thiago de Joaldo</t>
         </is>
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>TARCISIO MOTTA DE CARVALHO</t>
+          <t>JOSE THIAGO ALVES DE CARVALHO</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>dep.tarcisiomotta@camara.leg.br</t>
+          <t>dep.thiagodejoaldo@camara.leg.br</t>
         </is>
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>@tarcisiomottapsol</t>
+          <t>@thiagodejoaldo</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/tarcisiomottapsol</t>
-        </is>
-      </c>
-      <c r="I481" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/tarcisiomottapsol</t>
-        </is>
-      </c>
+          <t>https://instagram.com/thiagodejoaldo</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr"/>
       <c r="J481" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220598</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220560</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>220560</v>
+        <v>220597</v>
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>Thiago de Joaldo</t>
+          <t>Thiago Flores</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>JOSE THIAGO ALVES DE CARVALHO</t>
+          <t>THIAGO LEITE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>dep.thiagodejoaldo@camara.leg.br</t>
+          <t>dep.thiagoflores@camara.leg.br</t>
         </is>
       </c>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>@thiagodejoaldo</t>
+          <t>@deputadothiagoflores</t>
         </is>
       </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/thiagodejoaldo</t>
-        </is>
-      </c>
-      <c r="I482" s="2" t="inlineStr"/>
+          <t>https://instagram.com/deputadothiagoflores</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCF6Ks4RTqfjqxPMqUTotKkg</t>
+        </is>
+      </c>
       <c r="J482" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220560</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220597</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>220597</v>
+        <v>143084</v>
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>Thiago Flores</t>
+          <t>Tiago Dimas</t>
         </is>
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>THIAGO LEITE FLORES PEREIRA</t>
+          <t>Tiago Dimas Braga Pereira</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>dep.thiagoflores@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G483" s="2" t="inlineStr">
-        <is>
-          <t>@deputadothiagoflores</t>
-        </is>
-      </c>
-      <c r="H483" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadothiagoflores</t>
-        </is>
-      </c>
-      <c r="I483" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCF6Ks4RTqfjqxPMqUTotKkg</t>
-        </is>
-      </c>
+          <t>dep.tiagodimas@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr"/>
+      <c r="H483" s="2" t="inlineStr"/>
+      <c r="I483" s="2" t="inlineStr"/>
       <c r="J483" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220597</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/143084</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>143084</v>
+        <v>220684</v>
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>Tiago Dimas</t>
+          <t>Tião Medeiros</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>Tiago Dimas Braga Pereira</t>
+          <t>SEBASTIÃO HENRIQUE DE MEDEIROS</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>dep.tiagodimas@camara.leg.br</t>
+          <t>dep.tiaomedeiros@camara.leg.br</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr"/>
@@ -21796,37 +21788,37 @@
       <c r="I484" s="2" t="inlineStr"/>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/143084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220684</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>220684</v>
+        <v>160976</v>
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>Tião Medeiros</t>
+          <t>Tiririca</t>
         </is>
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>SEBASTIÃO HENRIQUE DE MEDEIROS</t>
+          <t>FRANCISCO EVERARDO TIRIRICA OLIVEIRA SILVA</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>dep.tiaomedeiros@camara.leg.br</t>
+          <t>dep.tiririca@camara.leg.br</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr"/>
@@ -21834,37 +21826,37 @@
       <c r="I485" s="2" t="inlineStr"/>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220684</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160976</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>160976</v>
+        <v>178934</v>
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>Tiririca</t>
+          <t>Toninho Wandscheer</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EVERARDO TIRIRICA OLIVEIRA SILVA</t>
+          <t>ANTONIO WANDSCHEER</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>dep.tiririca@camara.leg.br</t>
+          <t>dep.toninhowandscheer@camara.leg.br</t>
         </is>
       </c>
       <c r="G486" s="2" t="inlineStr"/>
@@ -21872,106 +21864,106 @@
       <c r="I486" s="2" t="inlineStr"/>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160976</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178934</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>178934</v>
+        <v>157130</v>
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>Toninho Wandscheer</t>
+          <t>Túlio Gadêlha</t>
         </is>
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO WANDSCHEER</t>
+          <t>TÚLIO GADÊLHA SALES DE MELO</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>dep.toninhowandscheer@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G487" s="2" t="inlineStr"/>
-      <c r="H487" s="2" t="inlineStr"/>
+          <t>dep.tuliogadelha@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>@tulio.gadelha</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tulio.gadelha</t>
+        </is>
+      </c>
       <c r="I487" s="2" t="inlineStr"/>
       <c r="J487" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178934</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/157130</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>157130</v>
+        <v>160610</v>
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>Túlio Gadêlha</t>
+          <t>Valmir Assunção</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>TÚLIO GADÊLHA SALES DE MELO</t>
+          <t>VALMIR CARLOS DA ASSUNÇÃO</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>dep.tuliogadelha@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G488" s="2" t="inlineStr">
-        <is>
-          <t>@tulio.gadelha</t>
-        </is>
-      </c>
-      <c r="H488" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/tulio.gadelha</t>
-        </is>
-      </c>
+          <t>dep.valmirassuncao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr"/>
+      <c r="H488" s="2" t="inlineStr"/>
       <c r="I488" s="2" t="inlineStr"/>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/157130</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160610</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>160610</v>
+        <v>74376</v>
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>Valmir Assunção</t>
+          <t>Vander Loubet</t>
         </is>
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>VALMIR CARLOS DA ASSUNÇÃO</t>
+          <t>VANDER LUIZ DOS SANTOS LOUBET</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
@@ -21981,249 +21973,261 @@
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>dep.valmirassuncao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G489" s="2" t="inlineStr"/>
-      <c r="H489" s="2" t="inlineStr"/>
+          <t>dep.vanderloubet@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>@vanderloubet</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/vanderloubet</t>
+        </is>
+      </c>
       <c r="I489" s="2" t="inlineStr"/>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160610</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74376</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>74376</v>
+        <v>234673</v>
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>Vander Loubet</t>
+          <t>Vanderlan Alves</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>VANDER LUIZ DOS SANTOS LOUBET</t>
+          <t>VALDERLAN ALVES DE SOUZA</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>dep.vanderloubet@camara.leg.br</t>
+          <t>dep.vanderlanalves@camara.leg.br</t>
         </is>
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>@vanderloubet</t>
+          <t>@vanderlan__alves</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/vanderloubet</t>
+          <t>https://instagram.com/vanderlan__alves</t>
         </is>
       </c>
       <c r="I490" s="2" t="inlineStr"/>
       <c r="J490" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74376</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/234673</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>234673</v>
+        <v>235712</v>
       </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
-          <t>Vanderlan Alves</t>
+          <t>Vavá</t>
         </is>
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>VALDERLAN ALVES DE SOUZA</t>
+          <t>HEBER GOMES NEIVA</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>dep.vanderlanalves@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G491" s="2" t="inlineStr">
-        <is>
-          <t>@vanderlan__alves</t>
-        </is>
-      </c>
-      <c r="H491" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/vanderlan__alves</t>
-        </is>
-      </c>
+          <t>dep.vava@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr"/>
+      <c r="H491" s="2" t="inlineStr"/>
       <c r="I491" s="2" t="inlineStr"/>
       <c r="J491" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/234673</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235712</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
-        <v>235712</v>
+        <v>204396</v>
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>Vavá</t>
+          <t>Vermelho</t>
         </is>
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>HEBER GOMES NEIVA</t>
+          <t>NELSI COGUETTO MARIA</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>dep.vava@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G492" s="2" t="inlineStr"/>
-      <c r="H492" s="2" t="inlineStr"/>
+          <t>dep.vermelho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>@deputado_vermelho</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputado_vermelho</t>
+        </is>
+      </c>
       <c r="I492" s="2" t="inlineStr"/>
       <c r="J492" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235712</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204396</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
-        <v>204396</v>
+        <v>137070</v>
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>Vermelho</t>
+          <t>Vicentinho Júnior</t>
         </is>
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>NELSI COGUETTO MARIA</t>
+          <t>VICENTE ALVES DE OLIVEIRA JUNIOR</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>dep.vermelho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G493" s="2" t="inlineStr">
-        <is>
-          <t>@deputado_vermelho</t>
-        </is>
-      </c>
-      <c r="H493" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputado_vermelho</t>
-        </is>
-      </c>
+          <t>dep.vicentinhojunior@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr"/>
+      <c r="H493" s="2" t="inlineStr"/>
       <c r="I493" s="2" t="inlineStr"/>
       <c r="J493" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204396</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/137070</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
-        <v>137070</v>
+        <v>141555</v>
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>Vicentinho Júnior</t>
+          <t>Vinicius Carvalho</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>VICENTE ALVES DE OLIVEIRA JUNIOR</t>
+          <t>VINICIUS RAPOZO DE CARVALHO</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>dep.vicentinhojunior@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G494" s="2" t="inlineStr"/>
-      <c r="H494" s="2" t="inlineStr"/>
-      <c r="I494" s="2" t="inlineStr"/>
+          <t>dep.viniciuscarvalho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>@viniciuscarvalhooficial</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/viniciuscarvalhooficial</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC0jfgVGfyujPS4YeBjTdJpw</t>
+        </is>
+      </c>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/137070</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141555</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
-        <v>141555</v>
+        <v>160591</v>
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Carvalho</t>
+          <t>Vinicius Gurgel</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>VINICIUS RAPOZO DE CARVALHO</t>
+          <t>VINICIUS DE AZEVEDO GURGEL</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
@@ -22233,215 +22237,211 @@
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>dep.viniciuscarvalho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G495" s="2" t="inlineStr">
-        <is>
-          <t>@viniciuscarvalhooficial</t>
-        </is>
-      </c>
-      <c r="H495" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/viniciuscarvalhooficial</t>
-        </is>
-      </c>
-      <c r="I495" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC0jfgVGfyujPS4YeBjTdJpw</t>
-        </is>
-      </c>
+          <t>dep.viniciusgurgel@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="inlineStr"/>
+      <c r="H495" s="2" t="inlineStr"/>
+      <c r="I495" s="2" t="inlineStr"/>
       <c r="J495" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141555</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160591</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
-        <v>160591</v>
+        <v>178992</v>
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Gurgel</t>
+          <t>Vitor Lippi</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>VINICIUS DE AZEVEDO GURGEL</t>
+          <t>VITOR LIPPI</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>dep.viniciusgurgel@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G496" s="2" t="inlineStr"/>
-      <c r="H496" s="2" t="inlineStr"/>
+          <t>dep.vitorlippi@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>@vitorlippi</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/vitorlippi</t>
+        </is>
+      </c>
       <c r="I496" s="2" t="inlineStr"/>
       <c r="J496" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160591</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178992</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
-        <v>178992</v>
+        <v>91228</v>
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>Vitor Lippi</t>
+          <t>Waldemar Oliveira</t>
         </is>
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>VITOR LIPPI</t>
+          <t>WALDEMAR DE ANDRADA IGNÁCIO DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>dep.vitorlippi@camara.leg.br</t>
+          <t>dep.waldemaroliveira@camara.leg.br</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>@vitorlippi</t>
+          <t>@waldemaroliveiraoficial</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/vitorlippi</t>
+          <t>https://instagram.com/waldemaroliveiraoficial</t>
         </is>
       </c>
       <c r="I497" s="2" t="inlineStr"/>
       <c r="J497" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178992</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/91228</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
-        <v>91228</v>
+        <v>160569</v>
       </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
-          <t>Waldemar Oliveira</t>
+          <t>Waldenor Pereira</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>WALDEMAR DE ANDRADA IGNÁCIO DE OLIVEIRA</t>
+          <t>WALDENOR ALVES PEREIRA FILHO</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>dep.waldemaroliveira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G498" s="2" t="inlineStr">
-        <is>
-          <t>@waldemaroliveiraoficial</t>
-        </is>
-      </c>
-      <c r="H498" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/waldemaroliveiraoficial</t>
-        </is>
-      </c>
+          <t>dep.waldenorpereira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G498" s="2" t="inlineStr"/>
+      <c r="H498" s="2" t="inlineStr"/>
       <c r="I498" s="2" t="inlineStr"/>
       <c r="J498" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/91228</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160569</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
-        <v>160569</v>
+        <v>160518</v>
       </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
-          <t>Waldenor Pereira</t>
+          <t>Weliton Prado</t>
         </is>
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>WALDENOR ALVES PEREIRA FILHO</t>
+          <t>WELITON FERNANDES PRADO</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>dep.waldenorpereira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G499" s="2" t="inlineStr"/>
-      <c r="H499" s="2" t="inlineStr"/>
+          <t>dep.welitonprado@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>@weliton.prado</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/weliton.prado</t>
+        </is>
+      </c>
       <c r="I499" s="2" t="inlineStr"/>
       <c r="J499" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160569</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160518</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
-        <v>160518</v>
+        <v>74043</v>
       </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
-          <t>Weliton Prado</t>
+          <t>Wellington Roberto</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>WELITON FERNANDES PRADO</t>
+          <t>JOSÉ WELLINGTON ROBERTO</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
@@ -22451,292 +22451,284 @@
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>dep.welitonprado@camara.leg.br</t>
+          <t>dep.wellingtonroberto@camara.leg.br</t>
         </is>
       </c>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>@weliton.prado</t>
+          <t>@wellingtonroberto.pb</t>
         </is>
       </c>
       <c r="H500" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/weliton.prado</t>
+          <t>https://instagram.com/wellingtonroberto.pb</t>
         </is>
       </c>
       <c r="I500" s="2" t="inlineStr"/>
       <c r="J500" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74043</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
-        <v>74043</v>
+        <v>224333</v>
       </c>
       <c r="B501" s="2" t="inlineStr">
         <is>
-          <t>Wellington Roberto</t>
+          <t>Welter</t>
         </is>
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ WELLINGTON ROBERTO</t>
+          <t>ELTON CARLOS WELTER</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>dep.wellingtonroberto@camara.leg.br</t>
+          <t>dep.welter@camara.leg.br</t>
         </is>
       </c>
       <c r="G501" s="2" t="inlineStr">
         <is>
-          <t>@wellingtonroberto.pb</t>
+          <t>@eltonwelter</t>
         </is>
       </c>
       <c r="H501" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/wellingtonroberto.pb</t>
+          <t>https://instagram.com/eltonwelter</t>
         </is>
       </c>
       <c r="I501" s="2" t="inlineStr"/>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74043</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/224333</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
-        <v>224333</v>
+        <v>74044</v>
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>Welter</t>
+          <t>Wilson Santiago</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>ELTON CARLOS WELTER</t>
+          <t>JOSÉ WILSON SANTIAGO</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>dep.welter@camara.leg.br</t>
+          <t>dep.wilsonsantiago@camara.leg.br</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>@eltonwelter</t>
+          <t>@wilsonsantiago</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/eltonwelter</t>
+          <t>https://instagram.com/wilsonsantiago</t>
         </is>
       </c>
       <c r="I502" s="2" t="inlineStr"/>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/224333</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74044</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
-        <v>74044</v>
+        <v>220564</v>
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>Wilson Santiago</t>
+          <t>Yandra Moura</t>
         </is>
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ WILSON SANTIAGO</t>
+          <t>YANDRA BARRETO FERREIRA</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>dep.wilsonsantiago@camara.leg.br</t>
+          <t>dep.yandramoura@camara.leg.br</t>
         </is>
       </c>
       <c r="G503" s="2" t="inlineStr">
         <is>
-          <t>@wilsonsantiago</t>
+          <t>@yandramourase</t>
         </is>
       </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/wilsonsantiago</t>
-        </is>
-      </c>
-      <c r="I503" s="2" t="inlineStr"/>
+          <t>https://instagram.com/yandramourase</t>
+        </is>
+      </c>
+      <c r="I503" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/Yandramourase</t>
+        </is>
+      </c>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74044</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220564</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
-        <v>220564</v>
+        <v>220660</v>
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>Yandra Moura</t>
+          <t>Yury do Paredão</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>YANDRA BARRETO FERREIRA</t>
+          <t>YURY BRUNO ALENCAR ARAUJO</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>dep.yandramoura@camara.leg.br</t>
+          <t>dep.yurydoparedao@camara.leg.br</t>
         </is>
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>@yandramourase</t>
+          <t>@yurydoparedao</t>
         </is>
       </c>
       <c r="H504" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/yandramourase</t>
-        </is>
-      </c>
-      <c r="I504" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/Yandramourase</t>
-        </is>
-      </c>
+          <t>https://instagram.com/yurydoparedao</t>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr"/>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220564</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220660</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
-        <v>220660</v>
+        <v>230768</v>
       </c>
       <c r="B505" s="2" t="inlineStr">
         <is>
-          <t>Yury do Paredão</t>
+          <t>Zé Adriano</t>
         </is>
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>YURY BRUNO ALENCAR ARAUJO</t>
+          <t>JOSE ADRIANO RIBEIRO DA SILVA</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>dep.yurydoparedao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G505" s="2" t="inlineStr">
-        <is>
-          <t>@yurydoparedao</t>
-        </is>
-      </c>
-      <c r="H505" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/yurydoparedao</t>
-        </is>
-      </c>
+          <t>dep.zeadriano@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G505" s="2" t="inlineStr"/>
+      <c r="H505" s="2" t="inlineStr"/>
       <c r="I505" s="2" t="inlineStr"/>
       <c r="J505" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220660</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230768</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
-        <v>230768</v>
+        <v>220536</v>
       </c>
       <c r="B506" s="2" t="inlineStr">
         <is>
-          <t>Zé Adriano</t>
+          <t>Zé Haroldo Cathedral</t>
         </is>
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>JOSE ADRIANO RIBEIRO DA SILVA</t>
+          <t>JOSÉ HAROLDO FIGUEIREDO CAMPOS</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>dep.zeadriano@camara.leg.br</t>
+          <t>dep.zeharoldocathedral@camara.leg.br</t>
         </is>
       </c>
       <c r="G506" s="2" t="inlineStr"/>
@@ -22744,37 +22736,37 @@
       <c r="I506" s="2" t="inlineStr"/>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230768</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220536</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
-        <v>220536</v>
+        <v>204559</v>
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>Zé Haroldo Cathedral</t>
+          <t>Zé Neto</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ HAROLDO FIGUEIREDO CAMPOS</t>
+          <t>JOSÉ CERQUEIRA DE SANTANA NETO</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>dep.zeharoldocathedral@camara.leg.br</t>
+          <t>dep.zeneto@camara.leg.br</t>
         </is>
       </c>
       <c r="G507" s="2" t="inlineStr"/>
@@ -22782,110 +22774,110 @@
       <c r="I507" s="2" t="inlineStr"/>
       <c r="J507" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220536</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204559</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
-        <v>204559</v>
+        <v>160632</v>
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>Zé Neto</t>
+          <t>Zé Silva</t>
         </is>
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ CERQUEIRA DE SANTANA NETO</t>
+          <t>JOSÉ SILVA SOARES</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>dep.zeneto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G508" s="2" t="inlineStr"/>
-      <c r="H508" s="2" t="inlineStr"/>
-      <c r="I508" s="2" t="inlineStr"/>
+          <t>dep.zesilva@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>@depzesilva</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depzesilva</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/deputadozesilva</t>
+        </is>
+      </c>
       <c r="J508" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204559</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160632</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
-        <v>160632</v>
+        <v>220558</v>
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>Zé Silva</t>
+          <t>Zé Trovão</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ SILVA SOARES</t>
+          <t>MARCOS ANTONIO PEREIRA GOMES</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>dep.zesilva@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G509" s="2" t="inlineStr">
-        <is>
-          <t>@depzesilva</t>
-        </is>
-      </c>
-      <c r="H509" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depzesilva</t>
-        </is>
-      </c>
-      <c r="I509" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadozesilva</t>
-        </is>
-      </c>
+          <t>dep.zetrovao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr"/>
+      <c r="H509" s="2" t="inlineStr"/>
+      <c r="I509" s="2" t="inlineStr"/>
       <c r="J509" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160632</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220558</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
-        <v>220558</v>
+        <v>204517</v>
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>Zé Trovão</t>
+          <t>Zé Vitor</t>
         </is>
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>MARCOS ANTONIO PEREIRA GOMES</t>
+          <t>JOSE VITOR DE RESENDE AGUIAR</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
@@ -22895,142 +22887,142 @@
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>dep.zetrovao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G510" s="2" t="inlineStr"/>
-      <c r="H510" s="2" t="inlineStr"/>
+          <t>dep.zevitor@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>@zevitormg</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/zevitormg</t>
+        </is>
+      </c>
       <c r="I510" s="2" t="inlineStr"/>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220558</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204517</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
-        <v>204517</v>
+        <v>160592</v>
       </c>
       <c r="B511" s="2" t="inlineStr">
         <is>
-          <t>Zé Vitor</t>
+          <t>Zeca Dirceu</t>
         </is>
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>JOSE VITOR DE RESENDE AGUIAR</t>
+          <t>JOSÉ CARLOS BECKER DE OLIVEIRA E SILVA</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>dep.zevitor@camara.leg.br</t>
+          <t>dep.zecadirceu@camara.leg.br</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
         <is>
-          <t>@zevitormg</t>
+          <t>@zecadirceuoficial</t>
         </is>
       </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/zevitormg</t>
+          <t>https://instagram.com/zecadirceuoficial</t>
         </is>
       </c>
       <c r="I511" s="2" t="inlineStr"/>
       <c r="J511" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204517</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160592</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
-        <v>160592</v>
+        <v>220592</v>
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>Zeca Dirceu</t>
+          <t>Zezinho Barbary</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ CARLOS BECKER DE OLIVEIRA E SILVA</t>
+          <t>JOSÉ ESTEPHAN AMORIM BARBARY FILHO</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>dep.zecadirceu@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G512" s="2" t="inlineStr">
-        <is>
-          <t>@zecadirceuoficial</t>
-        </is>
-      </c>
-      <c r="H512" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/zecadirceuoficial</t>
-        </is>
-      </c>
+          <t>dep.zezinhobarbary@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr"/>
+      <c r="H512" s="2" t="inlineStr"/>
       <c r="I512" s="2" t="inlineStr"/>
       <c r="J512" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160592</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220592</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
-        <v>220592</v>
+        <v>220552</v>
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
-          <t>Zezinho Barbary</t>
+          <t>Zucco</t>
         </is>
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ ESTEPHAN AMORIM BARBARY FILHO</t>
+          <t>LUCIANO LORENZINI ZUCCO</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>dep.zezinhobarbary@camara.leg.br</t>
+          <t>dep.zucco@camara.leg.br</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr"/>
@@ -23038,67 +23030,29 @@
       <c r="I513" s="2" t="inlineStr"/>
       <c r="J513" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220592</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" s="2" t="n">
-        <v>220552</v>
-      </c>
-      <c r="B514" s="2" t="inlineStr">
-        <is>
-          <t>Zucco</t>
-        </is>
-      </c>
-      <c r="C514" s="2" t="inlineStr">
-        <is>
-          <t>LUCIANO LORENZINI ZUCCO</t>
-        </is>
-      </c>
-      <c r="D514" s="2" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E514" s="2" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="F514" s="2" t="inlineStr">
-        <is>
-          <t>dep.zucco@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G514" s="2" t="inlineStr"/>
-      <c r="H514" s="2" t="inlineStr"/>
-      <c r="I514" s="2" t="inlineStr"/>
-      <c r="J514" s="2" t="inlineStr">
-        <is>
           <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220552</t>
         </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="3" t="inlineStr">
+        <is>
+          <t>Total deputados:</t>
+        </is>
+      </c>
+      <c r="B515">
+        <f>COUNTA(B2:B513)</f>
+        <v/>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
         <is>
-          <t>Total deputados:</t>
+          <t>Com Instagram:</t>
         </is>
       </c>
       <c r="B516">
-        <f>COUNTA(B2:B514)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" s="3" t="inlineStr">
-        <is>
-          <t>Com Instagram:</t>
-        </is>
-      </c>
-      <c r="B517">
-        <f>COUNTIF(G2:G514,"&lt;&gt;""")</f>
+        <f>COUNTIF(G2:G513,"&lt;&gt;""")</f>
         <v/>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -10022,7 +10022,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -13704,112 +13704,104 @@
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
-        <v>220616</v>
+        <v>178954</v>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Luciano Vieira</t>
+          <t>Lucio Mosquini</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>LUCIANO VIEIRA MENDES</t>
+          <t>LUCIO ANTONIO MOSQUINI</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>dep.lucianovieira@camara.leg.br</t>
+          <t>dep.luciomosquini@camara.leg.br</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>@lucianovieirarj</t>
+          <t>@luciomosquini</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/lucianovieirarj</t>
-        </is>
-      </c>
-      <c r="I302" s="2" t="inlineStr"/>
+          <t>https://instagram.com/luciomosquini</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/lucioantoniomosquinimosqui7885</t>
+        </is>
+      </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220616</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178954</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
-        <v>178954</v>
+        <v>204410</v>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Lucio Mosquini</t>
+          <t>Luisa Canziani</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>LUCIO ANTONIO MOSQUINI</t>
+          <t>LUISA CANZIANI DOS SANTOS SILVEIRA</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>dep.luciomosquini@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G303" s="2" t="inlineStr">
-        <is>
-          <t>@luciomosquini</t>
-        </is>
-      </c>
-      <c r="H303" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/luciomosquini</t>
-        </is>
-      </c>
-      <c r="I303" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/lucioantoniomosquinimosqui7885</t>
-        </is>
-      </c>
+          <t>dep.luisacanziani@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr"/>
+      <c r="H303" s="2" t="inlineStr"/>
+      <c r="I303" s="2" t="inlineStr"/>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178954</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204410</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
-        <v>204410</v>
+        <v>141485</v>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Luisa Canziani</t>
+          <t>Luiz Carlos Busato</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>LUISA CANZIANI DOS SANTOS SILVEIRA</t>
+          <t>LUIZ CARLOS GHIORZZI BUSATO</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -13819,196 +13811,196 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>dep.luisacanziani@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G304" s="2" t="inlineStr"/>
-      <c r="H304" s="2" t="inlineStr"/>
-      <c r="I304" s="2" t="inlineStr"/>
+          <t>dep.luizcarlosbusato@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>@lcbusato</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/lcbusato</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCI1WRKDHZA-6HQwN5_yWypw</t>
+        </is>
+      </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204410</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141485</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
-        <v>141485</v>
+        <v>73778</v>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Luiz Carlos Busato</t>
+          <t>Luiz Carlos Hauly</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>LUIZ CARLOS GHIORZZI BUSATO</t>
+          <t>LUIZ CARLOS JORGE HAULY</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
         <is>
-          <t>dep.luizcarlosbusato@camara.leg.br</t>
+          <t>dep.luizcarloshauly@camara.leg.br</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>@lcbusato</t>
+          <t>@deputadohauly</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/lcbusato</t>
-        </is>
-      </c>
-      <c r="I305" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCI1WRKDHZA-6HQwN5_yWypw</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadohauly</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr"/>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141485</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73778</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
-        <v>73778</v>
+        <v>204485</v>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Luiz Carlos Hauly</t>
+          <t>Luiz Carlos Motta</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>LUIZ CARLOS JORGE HAULY</t>
+          <t>LUIZ CARLOS MOTTA</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>dep.luizcarloshauly@camara.leg.br</t>
+          <t>dep.luizcarlosmotta@camara.leg.br</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>@deputadohauly</t>
+          <t>@deputadomotta</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadohauly</t>
-        </is>
-      </c>
-      <c r="I306" s="2" t="inlineStr"/>
+          <t>https://instagram.com/deputadomotta</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DeputadoMotta</t>
+        </is>
+      </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73778</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204485</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
-        <v>204485</v>
+        <v>74041</v>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Luiz Carlos Motta</t>
+          <t>Luiz Couto</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>LUIZ CARLOS MOTTA</t>
+          <t>LUIZ ALBUQUERQUE COUTO</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>dep.luizcarlosmotta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G307" s="2" t="inlineStr">
-        <is>
-          <t>@deputadomotta</t>
-        </is>
-      </c>
-      <c r="H307" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadomotta</t>
-        </is>
-      </c>
-      <c r="I307" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@DeputadoMotta</t>
-        </is>
-      </c>
+          <t>dep.luizcouto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr"/>
+      <c r="H307" s="2" t="inlineStr"/>
+      <c r="I307" s="2" t="inlineStr"/>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204485</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74041</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
-        <v>74041</v>
+        <v>141487</v>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Luiz Couto</t>
+          <t>Luiz Fernando Faria</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>LUIZ ALBUQUERQUE COUTO</t>
+          <t>LUIZ FERNANDO RAMOS FARIA</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>dep.luizcouto@camara.leg.br</t>
+          <t>dep.luizfernandofaria@camara.leg.br</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr"/>
@@ -14016,37 +14008,37 @@
       <c r="I308" s="2" t="inlineStr"/>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74041</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141487</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
-        <v>141487</v>
+        <v>220658</v>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Luiz Fernando Faria</t>
+          <t>Luiz Gastão</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>LUIZ FERNANDO RAMOS FARIA</t>
+          <t>LUIZ GASTÃO BITTENCOURT DA SILVA</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>dep.luizfernandofaria@camara.leg.br</t>
+          <t>dep.luizgastao@camara.leg.br</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr"/>
@@ -14054,153 +14046,165 @@
       <c r="I309" s="2" t="inlineStr"/>
       <c r="J309" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141487</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220658</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
-        <v>220658</v>
+        <v>204455</v>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Luiz Gastão</t>
+          <t>Luiz Lima</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>LUIZ GASTÃO BITTENCOURT DA SILVA</t>
+          <t>LUIZ EDUARDO CARNEIRO DA SILVA DE SOUZA LIMA</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>dep.luizgastao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G310" s="2" t="inlineStr"/>
-      <c r="H310" s="2" t="inlineStr"/>
-      <c r="I310" s="2" t="inlineStr"/>
+          <t>dep.luizlima@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>@oficialluizlima</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/oficialluizlima</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/oficialluizlima</t>
+        </is>
+      </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220658</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204455</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
-        <v>204455</v>
+        <v>162332</v>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Luiz Lima</t>
+          <t>Luiz Nishimori</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>LUIZ EDUARDO CARNEIRO DA SILVA DE SOUZA LIMA</t>
+          <t>LUIZ HILOSHI NISHIMORI</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
         <is>
-          <t>dep.luizlima@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>@oficialluizlima</t>
-        </is>
-      </c>
-      <c r="H311" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/oficialluizlima</t>
-        </is>
-      </c>
-      <c r="I311" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/oficialluizlima</t>
-        </is>
-      </c>
+          <t>dep.luiznishimori@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr"/>
+      <c r="H311" s="2" t="inlineStr"/>
+      <c r="I311" s="2" t="inlineStr"/>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204455</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/162332</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
-        <v>162332</v>
+        <v>204526</v>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Luiz Nishimori</t>
+          <t>Luiz Philippe de Orleans e Bragança</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>LUIZ HILOSHI NISHIMORI</t>
+          <t>LUIZ PHILIPPE DE ORLEANS BRAGANÇA</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>dep.luiznishimori@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G312" s="2" t="inlineStr"/>
-      <c r="H312" s="2" t="inlineStr"/>
-      <c r="I312" s="2" t="inlineStr"/>
+          <t>dep.luizphilippedeorleansebraganca@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>@lpbragancabr</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/lpbragancabr</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/luizphilippebr</t>
+        </is>
+      </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/162332</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204526</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
-        <v>204526</v>
+        <v>74784</v>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Luiz Philippe de Orleans e Bragança</t>
+          <t>Luiza Erundina</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>LUIZ PHILIPPE DE ORLEANS BRAGANÇA</t>
+          <t>LUIZA ERUNDINA DE SOUSA</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -14210,57 +14214,45 @@
       </c>
       <c r="F313" s="2" t="inlineStr">
         <is>
-          <t>dep.luizphilippedeorleansebraganca@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G313" s="2" t="inlineStr">
-        <is>
-          <t>@lpbragancabr</t>
-        </is>
-      </c>
-      <c r="H313" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/lpbragancabr</t>
-        </is>
-      </c>
-      <c r="I313" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/luizphilippebr</t>
-        </is>
-      </c>
+          <t>dep.luizaerundina@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr"/>
+      <c r="H313" s="2" t="inlineStr"/>
+      <c r="I313" s="2" t="inlineStr"/>
       <c r="J313" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204526</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74784</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
-        <v>74784</v>
+        <v>178866</v>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Luiza Erundina</t>
+          <t>Luizianne Lins</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>LUIZA ERUNDINA DE SOUSA</t>
+          <t>LUIZIANNE DE OLIVEIRA LINS</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>REDE</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>dep.luizaerundina@camara.leg.br</t>
+          <t>dep.luiziannelins@camara.leg.br</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr"/>
@@ -14268,37 +14260,37 @@
       <c r="I314" s="2" t="inlineStr"/>
       <c r="J314" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74784</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178866</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
-        <v>178866</v>
+        <v>220669</v>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Luizianne Lins</t>
+          <t>Lula da Fonte</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>LUIZIANNE DE OLIVEIRA LINS</t>
+          <t>LUIZ EDUARDO DE QUEIROZ CAMPOS DA FONTE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>REDE</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>dep.luiziannelins@camara.leg.br</t>
+          <t>dep.luladafonte@camara.leg.br</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr"/>
@@ -14306,267 +14298,267 @@
       <c r="I315" s="2" t="inlineStr"/>
       <c r="J315" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178866</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220669</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
-        <v>220669</v>
+        <v>166402</v>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Lula da Fonte</t>
+          <t>Magda Mofatto</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>LUIZ EDUARDO DE QUEIROZ CAMPOS DA FONTE ALBUQUERQUE</t>
+          <t>MAGDA MOFATTO HON</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>dep.luladafonte@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G316" s="2" t="inlineStr"/>
-      <c r="H316" s="2" t="inlineStr"/>
+          <t>dep.magdamofatto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>@magdamofatto.goias</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/magdamofatto.goias</t>
+        </is>
+      </c>
       <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220669</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/166402</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
-        <v>166402</v>
+        <v>220648</v>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Magda Mofatto</t>
+          <t>Marangoni</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>MAGDA MOFATTO HON</t>
+          <t>FERNANDO JOSE DE SOUZA MARANGONI</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>dep.magdamofatto@camara.leg.br</t>
+          <t>dep.marangoni@camara.leg.br</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>@magdamofatto.goias</t>
+          <t>@marangoni.oficial</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/magdamofatto.goias</t>
-        </is>
-      </c>
-      <c r="I317" s="2" t="inlineStr"/>
+          <t>https://instagram.com/marangoni.oficial</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@fernandomarangoni99/</t>
+        </is>
+      </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/166402</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220648</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
-        <v>220648</v>
+        <v>156190</v>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Marangoni</t>
+          <t>Marcel van Hattem</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>FERNANDO JOSE DE SOUZA MARANGONI</t>
+          <t>MARCEL VAN HATTEM</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>dep.marangoni@camara.leg.br</t>
+          <t>dep.marcelvanhattem@camara.leg.br</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>@marangoni.oficial</t>
+          <t>@MARCELVANHATTEM</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/marangoni.oficial</t>
+          <t>https://instagram.com/MARCELVANHATTEM</t>
         </is>
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@fernandomarangoni99/</t>
+          <t>https://youtube.com/channel/UCAGHY76tgzPiiXpJtM1sVCg</t>
         </is>
       </c>
       <c r="J318" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220648</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/156190</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
-        <v>156190</v>
+        <v>179000</v>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Marcel van Hattem</t>
+          <t>Marcelo Álvaro Antônio</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>MARCEL VAN HATTEM</t>
+          <t>MARCELO HENRIQUE TEIXEIRA DIAS</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
         <is>
-          <t>dep.marcelvanhattem@camara.leg.br</t>
+          <t>dep.marceloalvaroantonio@camara.leg.br</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>@MARCELVANHATTEM</t>
+          <t>@marceloalvaroantonio</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/MARCELVANHATTEM</t>
-        </is>
-      </c>
-      <c r="I319" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCAGHY76tgzPiiXpJtM1sVCg</t>
-        </is>
-      </c>
+          <t>https://instagram.com/marceloalvaroantonio</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr"/>
       <c r="J319" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/156190</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/179000</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
-        <v>179000</v>
+        <v>220599</v>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Álvaro Antônio</t>
+          <t>Marcelo Crivella</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>MARCELO HENRIQUE TEIXEIRA DIAS</t>
+          <t>MARCELO BEZERRA  CRIVELLA</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>dep.marceloalvaroantonio@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G320" s="2" t="inlineStr">
-        <is>
-          <t>@marceloalvaroantonio</t>
-        </is>
-      </c>
-      <c r="H320" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/marceloalvaroantonio</t>
-        </is>
-      </c>
+          <t>dep.marcelocrivella@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr"/>
+      <c r="H320" s="2" t="inlineStr"/>
       <c r="I320" s="2" t="inlineStr"/>
       <c r="J320" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/179000</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220599</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
-        <v>220599</v>
+        <v>133810</v>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Crivella</t>
+          <t>Marcelo Moraes</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>MARCELO BEZERRA  CRIVELLA</t>
+          <t>MARCELO PIRES MORAES</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr">
         <is>
-          <t>dep.marcelocrivella@camara.leg.br</t>
+          <t>dep.marcelomoraes@camara.leg.br</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr"/>
@@ -14574,37 +14566,37 @@
       <c r="I321" s="2" t="inlineStr"/>
       <c r="J321" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220599</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/133810</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
-        <v>133810</v>
+        <v>204558</v>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Moraes</t>
+          <t>Marcelo Nilo</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>MARCELO PIRES MORAES</t>
+          <t>JOSÉ MARCELO DO NASCIMENTO NILO</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>dep.marcelomoraes@camara.leg.br</t>
+          <t>dep.marcelonilo@camara.leg.br</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr"/>
@@ -14612,37 +14604,37 @@
       <c r="I322" s="2" t="inlineStr"/>
       <c r="J322" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/133810</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204558</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
-        <v>204558</v>
+        <v>160161</v>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Nilo</t>
+          <t>Marcelo Queiroz</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ MARCELO DO NASCIMENTO NILO</t>
+          <t>MARCELO ANDRE CID HERACLITO DO PORTO QUEIROZ</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>dep.marcelonilo@camara.leg.br</t>
+          <t>dep.marceloqueiroz@camara.leg.br</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr"/>
@@ -14650,37 +14642,37 @@
       <c r="I323" s="2" t="inlineStr"/>
       <c r="J323" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204558</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160161</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
-        <v>160161</v>
+        <v>178983</v>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Marcelo Queiroz</t>
+          <t>Marcio Alvino</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>MARCELO ANDRE CID HERACLITO DO PORTO QUEIROZ</t>
+          <t>MARCIO LUIZ ALVINO DE SOUZA</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>dep.marceloqueiroz@camara.leg.br</t>
+          <t>dep.marcioalvino@camara.leg.br</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr"/>
@@ -14688,37 +14680,37 @@
       <c r="I324" s="2" t="inlineStr"/>
       <c r="J324" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178983</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
-        <v>178983</v>
+        <v>179001</v>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Marcio Alvino</t>
+          <t>Márcio Biolchi</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>MARCIO LUIZ ALVINO DE SOUZA</t>
+          <t>MARCIO DELLA VALLE BIOLCHI</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>dep.marcioalvino@camara.leg.br</t>
+          <t>dep.marciobiolchi@camara.leg.br</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr"/>
@@ -14726,65 +14718,73 @@
       <c r="I325" s="2" t="inlineStr"/>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178983</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/179001</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
-        <v>179001</v>
+        <v>220687</v>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Márcio Biolchi</t>
+          <t>Márcio Honaiser</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>MARCIO DELLA VALLE BIOLCHI</t>
+          <t>MARCIO JOSE HONAISER</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>dep.marciobiolchi@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G326" s="2" t="inlineStr"/>
-      <c r="H326" s="2" t="inlineStr"/>
+          <t>dep.marciohonaiser@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>@marciohonaiser</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/marciohonaiser</t>
+        </is>
+      </c>
       <c r="I326" s="2" t="inlineStr"/>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/179001</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220687</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
-        <v>220687</v>
+        <v>81055</v>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Márcio Honaiser</t>
+          <t>Márcio Jerry</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>MARCIO JOSE HONAISER</t>
+          <t>MÁRCIO JERRY SARAIVA BARROSO</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -14794,207 +14794,207 @@
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>dep.marciohonaiser@camara.leg.br</t>
+          <t>dep.marciojerry@camara.leg.br</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>@marciohonaiser</t>
+          <t>@marciojerry</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/marciohonaiser</t>
-        </is>
-      </c>
-      <c r="I327" s="2" t="inlineStr"/>
+          <t>https://instagram.com/marciojerry</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/marciojerry</t>
+        </is>
+      </c>
       <c r="J327" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220687</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/81055</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
-        <v>81055</v>
+        <v>150418</v>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Márcio Jerry</t>
+          <t>Márcio Marinho</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>MÁRCIO JERRY SARAIVA BARROSO</t>
+          <t>MÁRCIO CARLOS MARINHO</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>dep.marciojerry@camara.leg.br</t>
+          <t>dep.marciomarinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>@marciojerry</t>
+          <t>@deputadomarciomarinho</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/marciojerry</t>
+          <t>https://instagram.com/deputadomarciomarinho</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/marciojerry</t>
+          <t>https://youtube.com/channel/UCx3t_YQx8H-93UD5k9Mt1lQ</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/81055</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/150418</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
-        <v>150418</v>
+        <v>160535</v>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Márcio Marinho</t>
+          <t>Marcon</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>MÁRCIO CARLOS MARINHO</t>
+          <t>DIONILSO MATEUS MARCON</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>dep.marciomarinho@camara.leg.br</t>
+          <t>dep.marcon@camara.leg.br</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>@deputadomarciomarinho</t>
+          <t>@deputadomarcon</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadomarciomarinho</t>
-        </is>
-      </c>
-      <c r="I329" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCx3t_YQx8H-93UD5k9Mt1lQ</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadomarcon</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr"/>
       <c r="J329" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/150418</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160535</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
-        <v>160535</v>
+        <v>204431</v>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Marcon</t>
+          <t>Marcos Aurélio Sampaio</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>DIONILSO MATEUS MARCON</t>
+          <t>MARCOS AURÉLIO  PÁDUA RIBEIRO GONÇALVES DE SAMPAIO</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>dep.marcon@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G330" s="2" t="inlineStr">
-        <is>
-          <t>@deputadomarcon</t>
-        </is>
-      </c>
-      <c r="H330" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadomarcon</t>
-        </is>
-      </c>
+          <t>dep.marcosaureliosampaio@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr"/>
+      <c r="H330" s="2" t="inlineStr"/>
       <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160535</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204431</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
-        <v>204431</v>
+        <v>236375</v>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Marcos Aurélio Sampaio</t>
+          <t>Marcos Braz</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>MARCOS AURÉLIO  PÁDUA RIBEIRO GONÇALVES DE SAMPAIO</t>
+          <t>MARCOS TEIXEIRA BRAZ</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr">
         <is>
-          <t>dep.marcosaureliosampaio@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G331" s="2" t="inlineStr"/>
-      <c r="H331" s="2" t="inlineStr"/>
+          <t>dep.marcosbraz@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>@marcosbrazoficial</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/marcosbrazoficial</t>
+        </is>
+      </c>
       <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204431</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236375</t>
         </is>
       </c>
     </row>
@@ -16432,104 +16432,116 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>220584</v>
+        <v>204453</v>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Murilo Galdino</t>
+          <t>Natália Bonavides</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>CÁSSIO MURILO GALDINO DE ARAÚJO</t>
+          <t>NATÁLIA BASTOS BONAVIDES</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>dep.murilogaldino@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G364" s="2" t="inlineStr"/>
-      <c r="H364" s="2" t="inlineStr"/>
-      <c r="I364" s="2" t="inlineStr"/>
+          <t>dep.nataliabonavides@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>@nataliabonavides</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nataliabonavides</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC4SZ1UNy6t9Mz99In-Rt1tw</t>
+        </is>
+      </c>
       <c r="J364" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220584</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204453</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>204453</v>
+        <v>204449</v>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Natália Bonavides</t>
+          <t>Nelson Barbudo</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>NATÁLIA BASTOS BONAVIDES</t>
+          <t>NELSON NED PREVIDENTE</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>dep.nataliabonavides@camara.leg.br</t>
+          <t>dep.nelsonbarbudo@camara.leg.br</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>@nataliabonavides</t>
+          <t>@nelsonbarbudo</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nataliabonavides</t>
+          <t>https://instagram.com/nelsonbarbudo</t>
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC4SZ1UNy6t9Mz99In-Rt1tw</t>
+          <t>https://youtube.com/channel/UC2wzaVfyw_DJ7Dw8vMqNoCw</t>
         </is>
       </c>
       <c r="J365" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204453</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204449</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>204449</v>
+        <v>220622</v>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Nelson Barbudo</t>
+          <t>Nely Aquino</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>NELSON NED PREVIDENTE</t>
+          <t>NELI PEREIRA DE AQUINO</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -16539,181 +16551,181 @@
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>dep.nelsonbarbudo@camara.leg.br</t>
+          <t>dep.nelyaquino@camara.leg.br</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>@nelsonbarbudo</t>
+          <t>@nelyaquinooficial</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelsonbarbudo</t>
+          <t>https://instagram.com/nelyaquinooficial</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC2wzaVfyw_DJ7Dw8vMqNoCw</t>
+          <t>https://youtube.com/NelyAquino</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204449</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220622</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>220622</v>
+        <v>220703</v>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Nely Aquino</t>
+          <t>Neto Carletto</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>NELI PEREIRA DE AQUINO</t>
+          <t>ORLANDO SULZ DE ALMEIDA NETO</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>dep.nelyaquino@camara.leg.br</t>
+          <t>dep.netocarletto@camara.leg.br</t>
         </is>
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>@nelyaquinooficial</t>
+          <t>@netocarletto</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelyaquinooficial</t>
-        </is>
-      </c>
-      <c r="I367" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/NelyAquino</t>
-        </is>
-      </c>
+          <t>https://instagram.com/netocarletto</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr"/>
       <c r="J367" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220622</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220703</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>220703</v>
+        <v>178896</v>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>Neto Carletto</t>
+          <t>Newton Cardoso Jr</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>ORLANDO SULZ DE ALMEIDA NETO</t>
+          <t>NEWTON CARDOSO JUNIOR</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>dep.netocarletto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G368" s="2" t="inlineStr">
-        <is>
-          <t>@netocarletto</t>
-        </is>
-      </c>
-      <c r="H368" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/netocarletto</t>
-        </is>
-      </c>
+          <t>dep.newtoncardosojr@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr"/>
+      <c r="H368" s="2" t="inlineStr"/>
       <c r="I368" s="2" t="inlineStr"/>
       <c r="J368" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220703</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178896</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>178896</v>
+        <v>204479</v>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>Newton Cardoso Jr</t>
+          <t>Nicoletti</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>NEWTON CARDOSO JUNIOR</t>
+          <t>ANTONIO CARLOS NICOLETTI</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>dep.newtoncardosojr@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G369" s="2" t="inlineStr"/>
-      <c r="H369" s="2" t="inlineStr"/>
-      <c r="I369" s="2" t="inlineStr"/>
+          <t>dep.nicoletti@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>@deputadonicoletti</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadonicoletti</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/DeputadoNicoletti</t>
+        </is>
+      </c>
       <c r="J369" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178896</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204479</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>204479</v>
+        <v>209787</v>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Nicoletti</t>
+          <t>Nikolas Ferreira</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO CARLOS NICOLETTI</t>
+          <t>NIKOLAS FERREIRA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -16723,653 +16735,641 @@
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>dep.nicoletti@camara.leg.br</t>
+          <t>dep.nikolasferreira@camara.leg.br</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>@deputadonicoletti</t>
+          <t>@nikolasferreiradm</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadonicoletti</t>
+          <t>https://instagram.com/nikolasferreiradm</t>
         </is>
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/DeputadoNicoletti</t>
+          <t>https://www.youtube.com/@NikolasFerreiraO</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204479</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/209787</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>209787</v>
+        <v>178986</v>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Nikolas Ferreira</t>
+          <t>Nilto Tatto</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>NIKOLAS FERREIRA DE OLIVEIRA</t>
+          <t>NILTO IGNACIO TATTO</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>dep.nikolasferreira@camara.leg.br</t>
+          <t>dep.niltotatto@camara.leg.br</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>@nikolasferreiradm</t>
+          <t>@niltotatto</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nikolasferreiradm</t>
-        </is>
-      </c>
-      <c r="I371" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@NikolasFerreiraO</t>
-        </is>
-      </c>
+          <t>https://instagram.com/niltotatto</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr"/>
       <c r="J371" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/209787</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178986</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>178986</v>
+        <v>204498</v>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Nilto Tatto</t>
+          <t>Olival Marques</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>NILTO IGNACIO TATTO</t>
+          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>dep.niltotatto@camara.leg.br</t>
+          <t>dep.olivalmarques@camara.leg.br</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>@niltotatto</t>
+          <t>@OlivalMarques</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/niltotatto</t>
+          <t>https://instagram.com/OlivalMarques</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr"/>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178986</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>204498</v>
+        <v>178987</v>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Olival Marques</t>
+          <t>Orlando Silva</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
+          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>dep.olivalmarques@camara.leg.br</t>
+          <t>dep.orlandosilva@camara.leg.br</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>@OlivalMarques</t>
+          <t>@orlandosilvasp</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/OlivalMarques</t>
+          <t>https://instagram.com/orlandosilvasp</t>
         </is>
       </c>
       <c r="I373" s="2" t="inlineStr"/>
       <c r="J373" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>178987</v>
+        <v>73692</v>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Orlando Silva</t>
+          <t>Osmar Terra</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
+          <t>OSMAR GASPARINI TERRA</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>dep.orlandosilva@camara.leg.br</t>
+          <t>dep.osmarterra@camara.leg.br</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>@orlandosilvasp</t>
+          <t>@terra.osmar</t>
         </is>
       </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/orlandosilvasp</t>
-        </is>
-      </c>
-      <c r="I374" s="2" t="inlineStr"/>
+          <t>https://instagram.com/terra.osmar</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
+        </is>
+      </c>
       <c r="J374" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>73692</v>
+        <v>204441</v>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Osmar Terra</t>
+          <t>Otoni de Paula</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>OSMAR GASPARINI TERRA</t>
+          <t>OTONI MOURA DE PAULO JUNIOR</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>dep.osmarterra@camara.leg.br</t>
+          <t>dep.otonidepaula@camara.leg.br</t>
         </is>
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>@terra.osmar</t>
+          <t>@otonidepaulaoficial</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/terra.osmar</t>
-        </is>
-      </c>
-      <c r="I375" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/otonidepaulaoficial</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr"/>
       <c r="J375" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>204441</v>
+        <v>220706</v>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Otoni de Paula</t>
+          <t>Padovani</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>OTONI MOURA DE PAULO JUNIOR</t>
+          <t>NELSON FERNANDO PADOVANI</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>dep.otonidepaula@camara.leg.br</t>
+          <t>dep.padovani@camara.leg.br</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>@otonidepaulaoficial</t>
+          <t>@nelsinhopadovani</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/otonidepaulaoficial</t>
+          <t>https://instagram.com/nelsinhopadovani</t>
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr"/>
       <c r="J376" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220706</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>220706</v>
+        <v>160556</v>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Padovani</t>
+          <t>Padre João</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>NELSON FERNANDO PADOVANI</t>
+          <t>JOÃO CARLOS SIQUEIRA</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>dep.padovani@camara.leg.br</t>
+          <t>dep.padrejoao@camara.leg.br</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>@nelsinhopadovani</t>
+          <t>@dep_padrejoao</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelsinhopadovani</t>
-        </is>
-      </c>
-      <c r="I377" s="2" t="inlineStr"/>
+          <t>https://instagram.com/dep_padrejoao</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
+        </is>
+      </c>
       <c r="J377" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220706</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>160556</v>
+        <v>180214</v>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Padre João</t>
+          <t>Pastor Diniz</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>JOÃO CARLOS SIQUEIRA</t>
+          <t>RAIMUNDO DINIZ ARAÚJO</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>dep.padrejoao@camara.leg.br</t>
+          <t>dep.pastordiniz@camara.leg.br</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>@dep_padrejoao</t>
+          <t>@pastordiniz.ad</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep_padrejoao</t>
-        </is>
-      </c>
-      <c r="I378" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
-        </is>
-      </c>
+          <t>https://instagram.com/pastordiniz.ad</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr"/>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>180214</v>
+        <v>160642</v>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Pastor Diniz</t>
+          <t>Pastor Eurico</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO DINIZ ARAÚJO</t>
+          <t>FRANCISCO EURICO DA SILVA</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>dep.pastordiniz@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G379" s="2" t="inlineStr">
-        <is>
-          <t>@pastordiniz.ad</t>
-        </is>
-      </c>
-      <c r="H379" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pastordiniz.ad</t>
-        </is>
-      </c>
+          <t>dep.pastoreurico@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr"/>
+      <c r="H379" s="2" t="inlineStr"/>
       <c r="I379" s="2" t="inlineStr"/>
       <c r="J379" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>160642</v>
+        <v>204570</v>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Pastor Eurico</t>
+          <t>Pastor Gil</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EURICO DA SILVA</t>
+          <t>GILDENEMIR DE LIMA SOUSA</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>dep.pastoreurico@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G380" s="2" t="inlineStr"/>
-      <c r="H380" s="2" t="inlineStr"/>
+          <t>dep.pastorgil@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>@deputadogildenemyr</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadogildenemyr</t>
+        </is>
+      </c>
       <c r="I380" s="2" t="inlineStr"/>
       <c r="J380" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>204570</v>
+        <v>220615</v>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Pastor Gil</t>
+          <t>Pastor Henrique Vieira</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>GILDENEMIR DE LIMA SOUSA</t>
+          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorgil@camara.leg.br</t>
+          <t>dep.pastorhenriquevieira@camara.leg.br</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>@deputadogildenemyr</t>
+          <t>@pastorhenriquevieira</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadogildenemyr</t>
-        </is>
-      </c>
-      <c r="I381" s="2" t="inlineStr"/>
+          <t>https://instagram.com/pastorhenriquevieira</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PastorHenriqueVieira</t>
+        </is>
+      </c>
       <c r="J381" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>220615</v>
+        <v>204553</v>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>Pastor Henrique Vieira</t>
+          <t>Pastor Sargento Isidório</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
+          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorhenriquevieira@camara.leg.br</t>
+          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>@pastorhenriquevieira</t>
+          <t>@pastorsargentoisidorio</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastorhenriquevieira</t>
-        </is>
-      </c>
-      <c r="I382" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/PastorHenriqueVieira</t>
-        </is>
-      </c>
+          <t>https://instagram.com/pastorsargentoisidorio</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr"/>
       <c r="J382" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>204553</v>
+        <v>74160</v>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>Pastor Sargento Isidório</t>
+          <t>Patrus Ananias</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
+          <t>PATRUS ANANIAS DE SOUZA</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>@pastorsargentoisidorio</t>
-        </is>
-      </c>
-      <c r="H383" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pastorsargentoisidorio</t>
-        </is>
-      </c>
+          <t>dep.patrusananias@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr"/>
+      <c r="H383" s="2" t="inlineStr"/>
       <c r="I383" s="2" t="inlineStr"/>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>74160</v>
+        <v>171617</v>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>Patrus Ananias</t>
+          <t>Paulão</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS DE SOUZA</t>
+          <t>PAULO FERNANDO DOS SANTOS</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
@@ -17379,12 +17379,12 @@
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>dep.patrusananias@camara.leg.br</t>
+          <t>dep.paulao@camara.leg.br</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr"/>
@@ -17392,37 +17392,37 @@
       <c r="I384" s="2" t="inlineStr"/>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171617</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>171617</v>
+        <v>141518</v>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Paulão</t>
+          <t>Paulinho da Força</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>PAULO FERNANDO DOS SANTOS</t>
+          <t>PAULO PEREIRA DA SILVA</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>dep.paulao@camara.leg.br</t>
+          <t>dep.paulinhodaforca@camara.leg.br</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr"/>
@@ -17430,37 +17430,37 @@
       <c r="I385" s="2" t="inlineStr"/>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171617</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>141518</v>
+        <v>141516</v>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Paulinho da Força</t>
+          <t>Paulo Abi-Ackel</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>PAULO PEREIRA DA SILVA</t>
+          <t>PAULO ABI-ACKEL</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>dep.paulinhodaforca@camara.leg.br</t>
+          <t>dep.pauloabiackel@camara.leg.br</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr"/>
@@ -17468,213 +17468,213 @@
       <c r="I386" s="2" t="inlineStr"/>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>141516</v>
+        <v>220650</v>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Paulo Abi-Ackel</t>
+          <t>Paulo Alexandre Barbosa</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>PAULO ABI-ACKEL</t>
+          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloabiackel@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G387" s="2" t="inlineStr"/>
-      <c r="H387" s="2" t="inlineStr"/>
+          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>@pauloalexandrebarbosa</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pauloalexandrebarbosa</t>
+        </is>
+      </c>
       <c r="I387" s="2" t="inlineStr"/>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>220650</v>
+        <v>178860</v>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>Paulo Alexandre Barbosa</t>
+          <t>Paulo Azi</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
+          <t>PAULO VELLOSO DANTAS AZI</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
+          <t>dep.pauloazi@camara.leg.br</t>
         </is>
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>@pauloalexandrebarbosa</t>
+          <t>@PauloAziofcial</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pauloalexandrebarbosa</t>
+          <t>https://instagram.com/PauloAziofcial</t>
         </is>
       </c>
       <c r="I388" s="2" t="inlineStr"/>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>178860</v>
+        <v>160517</v>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>Paulo Azi</t>
+          <t>Paulo Folletto</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>PAULO VELLOSO DANTAS AZI</t>
+          <t>PAULO ROBERTO FOLLETTO</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloazi@camara.leg.br</t>
+          <t>dep.paulofolletto@camara.leg.br</t>
         </is>
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>@PauloAziofcial</t>
+          <t>@paulo.folletto</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/PauloAziofcial</t>
+          <t>https://instagram.com/paulo.folletto</t>
         </is>
       </c>
       <c r="I389" s="2" t="inlineStr"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>160517</v>
+        <v>160558</v>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>Paulo Folletto</t>
+          <t>Paulo Freire Costa</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FOLLETTO</t>
+          <t>PAULO ROBERTO FREIRE DA COSTA</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofolletto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G390" s="2" t="inlineStr">
-        <is>
-          <t>@paulo.folletto</t>
-        </is>
-      </c>
-      <c r="H390" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/paulo.folletto</t>
-        </is>
-      </c>
+          <t>dep.paulofreirecosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr"/>
+      <c r="H390" s="2" t="inlineStr"/>
       <c r="I390" s="2" t="inlineStr"/>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>160558</v>
+        <v>204492</v>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>Paulo Freire Costa</t>
+          <t>Paulo Guedes</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FREIRE DA COSTA</t>
+          <t>PAULO JOSE CARLOS GUEDES</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofreirecosta@camara.leg.br</t>
+          <t>dep.pauloguedes@camara.leg.br</t>
         </is>
       </c>
       <c r="G391" s="2" t="inlineStr"/>
@@ -17682,22 +17682,22 @@
       <c r="I391" s="2" t="inlineStr"/>
       <c r="J391" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>204492</v>
+        <v>233592</v>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>Paulo Guedes</t>
+          <t>Paulo Lemos</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>PAULO JOSE CARLOS GUEDES</t>
+          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -17707,100 +17707,100 @@
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloguedes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G392" s="2" t="inlineStr"/>
-      <c r="H392" s="2" t="inlineStr"/>
-      <c r="I392" s="2" t="inlineStr"/>
+          <t>dep.paulolemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>@paulolemosap</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/paulolemosap</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
+        </is>
+      </c>
       <c r="J392" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>233592</v>
+        <v>220685</v>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>Paulo Lemos</t>
+          <t>Paulo Litro</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
+          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G393" s="2" t="inlineStr">
-        <is>
-          <t>@paulolemosap</t>
-        </is>
-      </c>
-      <c r="H393" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/paulolemosap</t>
-        </is>
-      </c>
-      <c r="I393" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
-        </is>
-      </c>
+          <t>dep.paulolitro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr"/>
+      <c r="H393" s="2" t="inlineStr"/>
+      <c r="I393" s="2" t="inlineStr"/>
       <c r="J393" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>220685</v>
+        <v>74574</v>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>Paulo Litro</t>
+          <t>Paulo Magalhães</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
+          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolitro@camara.leg.br</t>
+          <t>dep.paulomagalhaes@camara.leg.br</t>
         </is>
       </c>
       <c r="G394" s="2" t="inlineStr"/>
@@ -17808,37 +17808,37 @@
       <c r="I394" s="2" t="inlineStr"/>
       <c r="J394" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>74574</v>
+        <v>128760</v>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>Paulo Magalhães</t>
+          <t>Paulo Marinho Jr</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
+          <t>PAULO CELSO FONSECA MARINHO JÚNIOR</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>dep.paulomagalhaes@camara.leg.br</t>
+          <t>dep.paulomarinhojr@camara.leg.br</t>
         </is>
       </c>
       <c r="G395" s="2" t="inlineStr"/>
@@ -17846,37 +17846,37 @@
       <c r="I395" s="2" t="inlineStr"/>
       <c r="J395" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/128760</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>128760</v>
+        <v>74400</v>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>Paulo Marinho Jr</t>
+          <t>Paulo Pimenta</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>PAULO CELSO FONSECA MARINHO JÚNIOR</t>
+          <t>PAULO ROBERTO SEVERO PIMENTA</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>dep.paulomarinhojr@camara.leg.br</t>
+          <t>dep.paulopimenta@camara.leg.br</t>
         </is>
       </c>
       <c r="G396" s="2" t="inlineStr"/>
@@ -17884,22 +17884,22 @@
       <c r="I396" s="2" t="inlineStr"/>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/128760</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>74400</v>
+        <v>141488</v>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>Paulo Pimenta</t>
+          <t>Paulo Teixeira</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO SEVERO PIMENTA</t>
+          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
@@ -17909,272 +17909,272 @@
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>dep.paulopimenta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G397" s="2" t="inlineStr"/>
-      <c r="H397" s="2" t="inlineStr"/>
+          <t>dep.pauloteixeira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>@pauloteixeira13</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pauloteixeira13</t>
+        </is>
+      </c>
       <c r="I397" s="2" t="inlineStr"/>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>141488</v>
+        <v>220630</v>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Paulo Teixeira</t>
+          <t>Pedro Aihara</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
+          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloteixeira@camara.leg.br</t>
+          <t>dep.pedroaihara@camara.leg.br</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>@pauloteixeira13</t>
+          <t>@pedroaihara</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pauloteixeira13</t>
+          <t>https://instagram.com/pedroaihara</t>
         </is>
       </c>
       <c r="I398" s="2" t="inlineStr"/>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>220630</v>
+        <v>220667</v>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>Pedro Aihara</t>
+          <t>Pedro Campos</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
+          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>dep.pedroaihara@camara.leg.br</t>
+          <t>dep.pedrocampos@camara.leg.br</t>
         </is>
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>@pedroaihara</t>
+          <t>@pedrocampospe</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedroaihara</t>
+          <t>https://instagram.com/pedrocampospe</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr"/>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>220667</v>
+        <v>122974</v>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Pedro Campos</t>
+          <t>Pedro Lucas Fernandes</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
+          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrocampos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G400" s="2" t="inlineStr">
-        <is>
-          <t>@pedrocampospe</t>
-        </is>
-      </c>
-      <c r="H400" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrocampospe</t>
-        </is>
-      </c>
+          <t>dep.pedrolucasfernandes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr"/>
+      <c r="H400" s="2" t="inlineStr"/>
       <c r="I400" s="2" t="inlineStr"/>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>122974</v>
+        <v>204395</v>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lucas Fernandes</t>
+          <t>Pedro Lupion</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
+          <t>PEDRO DEBONI LUPION MELLO</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolucasfernandes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G401" s="2" t="inlineStr"/>
-      <c r="H401" s="2" t="inlineStr"/>
+          <t>dep.pedrolupion@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>@pedrolupion</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrolupion</t>
+        </is>
+      </c>
       <c r="I401" s="2" t="inlineStr"/>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>204395</v>
+        <v>122158</v>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lupion</t>
+          <t>Pedro Paulo</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DEBONI LUPION MELLO</t>
+          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolupion@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G402" s="2" t="inlineStr">
-        <is>
-          <t>@pedrolupion</t>
-        </is>
-      </c>
-      <c r="H402" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrolupion</t>
-        </is>
-      </c>
+          <t>dep.pedropaulo@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr"/>
+      <c r="H402" s="2" t="inlineStr"/>
       <c r="I402" s="2" t="inlineStr"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>122158</v>
+        <v>160604</v>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Pedro Paulo</t>
+          <t>Pedro Uczai</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
+          <t>PEDRO FRANCISCO UCZAI</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>dep.pedropaulo@camara.leg.br</t>
+          <t>dep.pedrouczai@camara.leg.br</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr"/>
@@ -18182,37 +18182,37 @@
       <c r="I403" s="2" t="inlineStr"/>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>160604</v>
+        <v>204406</v>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Pedro Uczai</t>
+          <t>Pedro Westphalen</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>PEDRO FRANCISCO UCZAI</t>
+          <t>PEDRO BANDARRA WESTPHALEN</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrouczai@camara.leg.br</t>
+          <t>dep.pedrowestphalen@camara.leg.br</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr"/>
@@ -18220,612 +18220,612 @@
       <c r="I404" s="2" t="inlineStr"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>204406</v>
+        <v>161440</v>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Pedro Westphalen</t>
+          <t>Pezenti</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>PEDRO BANDARRA WESTPHALEN</t>
+          <t>RAFAEL PEZENTI</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrowestphalen@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G405" s="2" t="inlineStr"/>
-      <c r="H405" s="2" t="inlineStr"/>
+          <t>dep.pezenti@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>@deputadopezenti</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadopezenti</t>
+        </is>
+      </c>
       <c r="I405" s="2" t="inlineStr"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>161440</v>
+        <v>204524</v>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Pezenti</t>
+          <t>Pinheirinho</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL PEZENTI</t>
+          <t>ANTÔNIO PINHEIRO NETO</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>dep.pezenti@camara.leg.br</t>
+          <t>dep.pinheirinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>@deputadopezenti</t>
+          <t>@pinheirinhomg</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadopezenti</t>
-        </is>
-      </c>
-      <c r="I406" s="2" t="inlineStr"/>
+          <t>https://instagram.com/pinheirinhomg</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
+        </is>
+      </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>204524</v>
+        <v>73486</v>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>Pinheirinho</t>
+          <t>Pompeo de Mattos</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>ANTÔNIO PINHEIRO NETO</t>
+          <t>DARCI POMPEO DE MATTOS</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>dep.pinheirinho@camara.leg.br</t>
+          <t>dep.pompeodemattos@camara.leg.br</t>
         </is>
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>@pinheirinhomg</t>
+          <t>@pompeodemattospdt</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pinheirinhomg</t>
+          <t>https://instagram.com/pompeodemattospdt</t>
         </is>
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
+          <t>https://youtube.com/PompeodeMattos</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>73486</v>
+        <v>160601</v>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Pompeo de Mattos</t>
+          <t>Pr. Marco Feliciano</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>DARCI POMPEO DE MATTOS</t>
+          <t>MARCO ANTÔNIO FELICIANO</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>dep.pompeodemattos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G408" s="2" t="inlineStr">
-        <is>
-          <t>@pompeodemattospdt</t>
-        </is>
-      </c>
-      <c r="H408" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pompeodemattospdt</t>
-        </is>
-      </c>
-      <c r="I408" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/PompeodeMattos</t>
-        </is>
-      </c>
+          <t>dep.pr.marcofeliciano@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr"/>
+      <c r="H408" s="2" t="inlineStr"/>
+      <c r="I408" s="2" t="inlineStr"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>160601</v>
+        <v>220533</v>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Pr. Marco Feliciano</t>
+          <t>Prof. Reginaldo Veras</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>MARCO ANTÔNIO FELICIANO</t>
+          <t>Reginaldo Veras Coelho</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>dep.pr.marcofeliciano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G409" s="2" t="inlineStr"/>
-      <c r="H409" s="2" t="inlineStr"/>
-      <c r="I409" s="2" t="inlineStr"/>
+          <t>dep.prof.reginaldoveras@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>@reginaldo.veras</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/reginaldo.veras</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/Reginaldoveras12</t>
+        </is>
+      </c>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>220533</v>
+        <v>204390</v>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Prof. Reginaldo Veras</t>
+          <t>Professor Alcides</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Veras Coelho</t>
+          <t>ALCIDES RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>dep.prof.reginaldoveras@camara.leg.br</t>
+          <t>dep.professoralcides@camara.leg.br</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>@reginaldo.veras</t>
+          <t>@professoralcidesoficial</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/reginaldo.veras</t>
+          <t>https://instagram.com/professoralcidesoficial</t>
         </is>
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/Reginaldoveras12</t>
+          <t>https://youtube.com/DeputadoProfessorAlcides</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>204390</v>
+        <v>221338</v>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Professor Alcides</t>
+          <t>Professora Luciene Cavalcante</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>ALCIDES RIBEIRO FILHO</t>
+          <t>LUCIENE CAVALCANTE DA SILVA</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralcides@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G411" s="2" t="inlineStr">
-        <is>
-          <t>@professoralcidesoficial</t>
-        </is>
-      </c>
-      <c r="H411" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/professoralcidesoficial</t>
-        </is>
-      </c>
-      <c r="I411" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/DeputadoProfessorAlcides</t>
-        </is>
-      </c>
+          <t>dep.professoralucienecavalcante@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr"/>
+      <c r="H411" s="2" t="inlineStr"/>
+      <c r="I411" s="2" t="inlineStr"/>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>221338</v>
+        <v>160641</v>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Professora Luciene Cavalcante</t>
+          <t>Professora Marcivania</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>LUCIENE CAVALCANTE DA SILVA</t>
+          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralucienecavalcante@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G412" s="2" t="inlineStr"/>
-      <c r="H412" s="2" t="inlineStr"/>
+          <t>dep.professoramarcivania@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>@profmarcivania</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/profmarcivania</t>
+        </is>
+      </c>
       <c r="I412" s="2" t="inlineStr"/>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>160641</v>
+        <v>220586</v>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Professora Marcivania</t>
+          <t>Rafael Brito</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
+          <t>RAFAEL DE GOES BRITO</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>dep.professoramarcivania@camara.leg.br</t>
+          <t>dep.rafaelbrito@camara.leg.br</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>@profmarcivania</t>
+          <t>@rafaelbrito15</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/profmarcivania</t>
-        </is>
-      </c>
-      <c r="I413" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
+        </is>
+      </c>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>220586</v>
+        <v>233594</v>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Rafael Brito</t>
+          <t>Rafael Fera</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL DE GOES BRITO</t>
+          <t>RAFAEL BENTO PEREIRA</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelbrito@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="H414" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="I414" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
-        </is>
-      </c>
+          <t>dep.rafaelfera@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr"/>
+      <c r="H414" s="2" t="inlineStr"/>
+      <c r="I414" s="2" t="inlineStr"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>233594</v>
+        <v>220532</v>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Rafael Fera</t>
+          <t>Rafael Prudente</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL BENTO PEREIRA</t>
+          <t>RAFAEL CAVALCANTI PRUDENTE</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelfera@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G415" s="2" t="inlineStr"/>
-      <c r="H415" s="2" t="inlineStr"/>
-      <c r="I415" s="2" t="inlineStr"/>
+          <t>dep.rafaelprudente@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RafaelPrudente</t>
+        </is>
+      </c>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>220532</v>
+        <v>220626</v>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Rafael Prudente</t>
+          <t>Rafael Simoes</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL CAVALCANTI PRUDENTE</t>
+          <t>RAFAEL TADEU SIMÕES</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelprudente@camara.leg.br</t>
+          <t>dep.rafaelsimoes@camara.leg.br</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>@rafaelprudentedep</t>
+          <t>@rafaelsimoesmg</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="I416" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RafaelPrudente</t>
-        </is>
-      </c>
+          <t>https://instagram.com/rafaelsimoesmg</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr"/>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>220626</v>
+        <v>204567</v>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Rafael Simoes</t>
+          <t>Raimundo Costa</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL TADEU SIMÕES</t>
+          <t>RAIMUNDO MAGALHÃES COSTA</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelsimoes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G417" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelsimoesmg</t>
-        </is>
-      </c>
-      <c r="H417" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelsimoesmg</t>
-        </is>
-      </c>
+          <t>dep.raimundocosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr"/>
+      <c r="H417" s="2" t="inlineStr"/>
       <c r="I417" s="2" t="inlineStr"/>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>204567</v>
+        <v>74084</v>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Costa</t>
+          <t>Raimundo Santos</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO MAGALHÃES COSTA</t>
+          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
@@ -18835,70 +18835,70 @@
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundocosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G418" s="2" t="inlineStr"/>
-      <c r="H418" s="2" t="inlineStr"/>
-      <c r="I418" s="2" t="inlineStr"/>
+          <t>dep.raimundosantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>@depraimundosantos</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depraimundosantos</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
+        </is>
+      </c>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>74084</v>
+        <v>115200</v>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Santos</t>
+          <t>Raniery Paulino</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
+          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundosantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G419" s="2" t="inlineStr">
-        <is>
-          <t>@depraimundosantos</t>
-        </is>
-      </c>
-      <c r="H419" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depraimundosantos</t>
-        </is>
-      </c>
-      <c r="I419" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
-        </is>
-      </c>
+          <t>dep.ranierypaulino@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr"/>
+      <c r="H419" s="2" t="inlineStr"/>
+      <c r="I419" s="2" t="inlineStr"/>
       <c r="J419" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -15552,115 +15552,123 @@
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
-        <v>220572</v>
+        <v>204566</v>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Marussa Boldrin</t>
+          <t>Marreca Filho</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>MARUSSA CASSIA FAVARO BOLDRIN</t>
+          <t>ANTONIO DA CRUZ FILGUEIRA NETO</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PRD</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
-          <t>dep.marussaboldrin@camara.leg.br</t>
+          <t>dep.marrecafilho@camara.leg.br</t>
         </is>
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>@marussa.boldrin</t>
+          <t>@depmarrecafilho</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/marussa.boldrin</t>
+          <t>https://instagram.com/depmarrecafilho</t>
         </is>
       </c>
       <c r="I344" s="2" t="inlineStr"/>
       <c r="J344" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220572</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204566</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
-        <v>178843</v>
+        <v>220572</v>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Marx Beltrão</t>
+          <t>Marussa Boldrin</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>MARX BELTRÃO LIMA SIQUEIRA</t>
+          <t>MARUSSA CASSIA FAVARO BOLDRIN</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
-          <t>dep.marxbeltrao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G345" s="2" t="inlineStr"/>
-      <c r="H345" s="2" t="inlineStr"/>
+          <t>dep.marussaboldrin@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>@marussa.boldrin</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/marussa.boldrin</t>
+        </is>
+      </c>
       <c r="I345" s="2" t="inlineStr"/>
       <c r="J345" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178843</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220572</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
-        <v>220661</v>
+        <v>178843</v>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Matheus Noronha</t>
+          <t>Marx Beltrão</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>MATHEUS SOARES NORONHA</t>
+          <t>MARX BELTRÃO LIMA SIQUEIRA</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>dep.matheusnoronha@camara.leg.br</t>
+          <t>dep.marxbeltrao@camara.leg.br</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr"/>
@@ -15668,37 +15676,37 @@
       <c r="I346" s="2" t="inlineStr"/>
       <c r="J346" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220661</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178843</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
-        <v>220609</v>
+        <v>220661</v>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Maurício Carvalho</t>
+          <t>Matheus Noronha</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>MAURICIO FONSECA RIBEIRO CARVALHO DE MORAES</t>
+          <t>MATHEUS SOARES NORONHA</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr">
         <is>
-          <t>dep.mauriciocarvalho@camara.leg.br</t>
+          <t>dep.matheusnoronha@camara.leg.br</t>
         </is>
       </c>
       <c r="G347" s="2" t="inlineStr"/>
@@ -15706,68 +15714,60 @@
       <c r="I347" s="2" t="inlineStr"/>
       <c r="J347" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220609</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220661</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
-        <v>220628</v>
+        <v>220609</v>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Mauricio do Vôlei</t>
+          <t>Maurício Carvalho</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>MAURICIO LUIZ DE SOUZA</t>
+          <t>MAURICIO FONSECA RIBEIRO CARVALHO DE MORAES</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>dep.mauriciodovolei@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G348" s="2" t="inlineStr">
-        <is>
-          <t>@mauriciodovolei</t>
-        </is>
-      </c>
-      <c r="H348" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/mauriciodovolei</t>
-        </is>
-      </c>
+          <t>dep.mauriciocarvalho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr"/>
+      <c r="H348" s="2" t="inlineStr"/>
       <c r="I348" s="2" t="inlineStr"/>
       <c r="J348" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220628</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220609</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
-        <v>220550</v>
+        <v>220628</v>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Marcon</t>
+          <t>Mauricio do Vôlei</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>MAURICIO BEDIN MARCON</t>
+          <t>MAURICIO LUIZ DE SOUZA</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -15777,131 +15777,131 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
-          <t>dep.mauriciomarcon@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G349" s="2" t="inlineStr"/>
-      <c r="H349" s="2" t="inlineStr"/>
+          <t>dep.mauriciodovolei@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>@mauriciodovolei</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mauriciodovolei</t>
+        </is>
+      </c>
       <c r="I349" s="2" t="inlineStr"/>
       <c r="J349" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220550</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220628</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
-        <v>220647</v>
+        <v>220550</v>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Mauricio Neves</t>
+          <t>Mauricio Marcon</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>MANOEL MAURICIO SILVA NEVES</t>
+          <t>MAURICIO BEDIN MARCON</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>dep.mauricioneves@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G350" s="2" t="inlineStr">
-        <is>
-          <t>@mauricioneves_oficial</t>
-        </is>
-      </c>
-      <c r="H350" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/mauricioneves_oficial</t>
-        </is>
-      </c>
-      <c r="I350" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/mauricioneves9642</t>
-        </is>
-      </c>
+          <t>dep.mauriciomarcon@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr"/>
+      <c r="H350" s="2" t="inlineStr"/>
+      <c r="I350" s="2" t="inlineStr"/>
       <c r="J350" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220647</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220550</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>204486</v>
+        <v>220647</v>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Mauro Benevides Filho</t>
+          <t>Mauricio Neves</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>CARLOS MAURO BENEVIDES FILHO</t>
+          <t>MANOEL MAURICIO SILVA NEVES</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>dep.maurobenevidesfilho@camara.leg.br</t>
+          <t>dep.mauricioneves@camara.leg.br</t>
         </is>
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>@mauro_benevidesfilho</t>
+          <t>@mauricioneves_oficial</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/mauro_benevidesfilho</t>
-        </is>
-      </c>
-      <c r="I351" s="2" t="inlineStr"/>
+          <t>https://instagram.com/mauricioneves_oficial</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/mauricioneves9642</t>
+        </is>
+      </c>
       <c r="J351" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204486</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220647</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>220607</v>
+        <v>204486</v>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Max Lemos</t>
+          <t>Mauro Benevides Filho</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>MAX RODRIGUES LEMOS</t>
+          <t>CARLOS MAURO BENEVIDES FILHO</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -15911,47 +15911,43 @@
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>dep.maxlemos@camara.leg.br</t>
+          <t>dep.maurobenevidesfilho@camara.leg.br</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>@maxlemosoficial</t>
+          <t>@mauro_benevidesfilho</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/maxlemosoficial</t>
-        </is>
-      </c>
-      <c r="I352" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/@maxlemos9960</t>
-        </is>
-      </c>
+          <t>https://instagram.com/mauro_benevidesfilho</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr"/>
       <c r="J352" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220607</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204486</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>220591</v>
+        <v>220607</v>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Meire Serafim</t>
+          <t>Max Lemos</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>ROZIMEIRE RIBEIRO ANDRADE</t>
+          <t>MAX RODRIGUES LEMOS</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
@@ -15961,316 +15957,316 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>dep.meireserafim@camara.leg.br</t>
+          <t>dep.maxlemos@camara.leg.br</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>@dep.meireserafim</t>
+          <t>@maxlemosoficial</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep.meireserafim</t>
-        </is>
-      </c>
-      <c r="I353" s="2" t="inlineStr"/>
+          <t>https://instagram.com/maxlemosoficial</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@maxlemos9960</t>
+        </is>
+      </c>
       <c r="J353" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220591</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220607</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>74428</v>
+        <v>220591</v>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Mendonça Filho</t>
+          <t>Meire Serafim</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ MENDONÇA BEZERRA FILHO</t>
+          <t>ROZIMEIRE RIBEIRO ANDRADE</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>dep.mendoncafilho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G354" s="2" t="inlineStr"/>
-      <c r="H354" s="2" t="inlineStr"/>
+          <t>dep.meireserafim@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>@dep.meireserafim</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dep.meireserafim</t>
+        </is>
+      </c>
       <c r="I354" s="2" t="inlineStr"/>
       <c r="J354" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74428</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220591</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>188097</v>
+        <v>74428</v>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Merlong Solano</t>
+          <t>Mendonça Filho</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>MERLONG SOLANO NOGUEIRA</t>
+          <t>JOSÉ MENDONÇA BEZERRA FILHO</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>dep.merlongsolano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G355" s="2" t="inlineStr">
-        <is>
-          <t>@merlongsolano</t>
-        </is>
-      </c>
-      <c r="H355" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/merlongsolano</t>
-        </is>
-      </c>
+          <t>dep.mendoncafilho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr"/>
+      <c r="H355" s="2" t="inlineStr"/>
       <c r="I355" s="2" t="inlineStr"/>
       <c r="J355" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/188097</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74428</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>220585</v>
+        <v>188097</v>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Mersinho Lucena</t>
+          <t>Merlong Solano</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EMERSON ASSIS DE LUCENA</t>
+          <t>MERLONG SOLANO NOGUEIRA</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>dep.mersinholucena@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G356" s="2" t="inlineStr"/>
-      <c r="H356" s="2" t="inlineStr"/>
+          <t>dep.merlongsolano@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>@merlongsolano</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/merlongsolano</t>
+        </is>
+      </c>
       <c r="I356" s="2" t="inlineStr"/>
       <c r="J356" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220585</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/188097</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>220530</v>
+        <v>220585</v>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Messias Donato</t>
+          <t>Mersinho Lucena</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Manoel Messias Donato Bezerra</t>
+          <t>FRANCISCO EMERSON ASSIS DE LUCENA</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>dep.messiasdonato@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G357" s="2" t="inlineStr">
-        <is>
-          <t>@messiasdonato</t>
-        </is>
-      </c>
-      <c r="H357" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/messiasdonato</t>
-        </is>
-      </c>
-      <c r="I357" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCzw1O2NLEynTs9dm3X2AILA</t>
-        </is>
-      </c>
+          <t>dep.mersinholucena@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr"/>
+      <c r="H357" s="2" t="inlineStr"/>
+      <c r="I357" s="2" t="inlineStr"/>
       <c r="J357" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220530</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220585</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>171786</v>
+        <v>220530</v>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Miguel Ângelo</t>
+          <t>Messias Donato</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>MIGUEL ÂNGELO MONTEIRO ANDRADE</t>
+          <t>Manoel Messias Donato Bezerra</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>dep.miguelangelo@camara.leg.br</t>
+          <t>dep.messiasdonato@camara.leg.br</t>
         </is>
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>@miguelangelomg13</t>
+          <t>@messiasdonato</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/miguelangelomg13</t>
-        </is>
-      </c>
-      <c r="I358" s="2" t="inlineStr"/>
+          <t>https://instagram.com/messiasdonato</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCzw1O2NLEynTs9dm3X2AILA</t>
+        </is>
+      </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171786</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220530</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>178985</v>
+        <v>171786</v>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>Miguel Lombardi</t>
+          <t>Miguel Ângelo</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>MIGUEL LOMBARDI</t>
+          <t>MIGUEL ÂNGELO MONTEIRO ANDRADE</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>dep.miguellombardi@camara.leg.br</t>
+          <t>dep.miguelangelo@camara.leg.br</t>
         </is>
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>@dep.miguellombardi</t>
+          <t>@miguelangelomg13</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep.miguellombardi</t>
-        </is>
-      </c>
-      <c r="I359" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCzP0L6ymrNXOBJuOpflBwgA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/miguelangelomg13</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr"/>
       <c r="J359" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178985</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171786</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>154178</v>
+        <v>178985</v>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Milton Vieira</t>
+          <t>Miguel Lombardi</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>MILTON VIEIRA PINTO</t>
+          <t>MIGUEL LOMBARDI</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -16280,318 +16276,318 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>dep.miltonvieira@camara.leg.br</t>
+          <t>dep.miguellombardi@camara.leg.br</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>@miltonvieiraoficial</t>
+          <t>@dep.miguellombardi</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/miltonvieiraoficial</t>
+          <t>https://instagram.com/dep.miguellombardi</t>
         </is>
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/user/depmiltonvieira/</t>
+          <t>https://youtube.com/channel/UCzP0L6ymrNXOBJuOpflBwgA</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/154178</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178985</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>178895</v>
+        <v>154178</v>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Misael Varella</t>
+          <t>Milton Vieira</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>MISAEL ARTUR FERREIRA VARELLA</t>
+          <t>MILTON VIEIRA PINTO</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>dep.misaelvarella@camara.leg.br</t>
+          <t>dep.miltonvieira@camara.leg.br</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>@misaelvarella</t>
+          <t>@miltonvieiraoficial</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/misaelvarella</t>
-        </is>
-      </c>
-      <c r="I361" s="2" t="inlineStr"/>
+          <t>https://instagram.com/miltonvieiraoficial</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/depmiltonvieira/</t>
+        </is>
+      </c>
       <c r="J361" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178895</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/154178</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>160561</v>
+        <v>178895</v>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Missionário José Olimpio</t>
+          <t>Misael Varella</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ OLIMPIO SILVEIRA MORAES</t>
+          <t>MISAEL ARTUR FERREIRA VARELLA</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>dep.missionariojoseolimpio@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G362" s="2" t="inlineStr"/>
-      <c r="H362" s="2" t="inlineStr"/>
+          <t>dep.misaelvarella@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>@misaelvarella</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/misaelvarella</t>
+        </is>
+      </c>
       <c r="I362" s="2" t="inlineStr"/>
       <c r="J362" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160561</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178895</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>178997</v>
+        <v>160561</v>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Moses Rodrigues</t>
+          <t>Missionário José Olimpio</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>MOSES HAENDEL MELO RODRIGUES</t>
+          <t>JOSÉ OLIMPIO SILVEIRA MORAES</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>dep.mosesrodrigues@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G363" s="2" t="inlineStr">
-        <is>
-          <t>@mosesrodriguesoficial</t>
-        </is>
-      </c>
-      <c r="H363" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/mosesrodriguesoficial</t>
-        </is>
-      </c>
+          <t>dep.missionariojoseolimpio@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr"/>
+      <c r="H363" s="2" t="inlineStr"/>
       <c r="I363" s="2" t="inlineStr"/>
       <c r="J363" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178997</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160561</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>220617</v>
+        <v>178997</v>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Murillo Gouvea</t>
+          <t>Moses Rodrigues</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>MURILLO GOUVEA RODRIGUES</t>
+          <t>MOSES HAENDEL MELO RODRIGUES</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>dep.murillogouvea@camara.leg.br</t>
+          <t>dep.mosesrodrigues@camara.leg.br</t>
         </is>
       </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>@murillogouvea.rj</t>
+          <t>@mosesrodriguesoficial</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/murillogouvea.rj</t>
+          <t>https://instagram.com/mosesrodriguesoficial</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr"/>
       <c r="J364" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220617</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178997</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>204453</v>
+        <v>220617</v>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Natália Bonavides</t>
+          <t>Murillo Gouvea</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>NATÁLIA BASTOS BONAVIDES</t>
+          <t>MURILLO GOUVEA RODRIGUES</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>dep.nataliabonavides@camara.leg.br</t>
+          <t>dep.murillogouvea@camara.leg.br</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>@nataliabonavides</t>
+          <t>@murillogouvea.rj</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nataliabonavides</t>
-        </is>
-      </c>
-      <c r="I365" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC4SZ1UNy6t9Mz99In-Rt1tw</t>
-        </is>
-      </c>
+          <t>https://instagram.com/murillogouvea.rj</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr"/>
       <c r="J365" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204453</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220617</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>204449</v>
+        <v>204453</v>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Nelson Barbudo</t>
+          <t>Natália Bonavides</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>NELSON NED PREVIDENTE</t>
+          <t>NATÁLIA BASTOS BONAVIDES</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>dep.nelsonbarbudo@camara.leg.br</t>
+          <t>dep.nataliabonavides@camara.leg.br</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>@nelsonbarbudo</t>
+          <t>@nataliabonavides</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelsonbarbudo</t>
+          <t>https://instagram.com/nataliabonavides</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC2wzaVfyw_DJ7Dw8vMqNoCw</t>
+          <t>https://youtube.com/channel/UC4SZ1UNy6t9Mz99In-Rt1tw</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204449</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204453</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>220622</v>
+        <v>204449</v>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Nely Aquino</t>
+          <t>Nelson Barbudo</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>NELI PEREIRA DE AQUINO</t>
+          <t>NELSON NED PREVIDENTE</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -16601,181 +16597,181 @@
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>dep.nelyaquino@camara.leg.br</t>
+          <t>dep.nelsonbarbudo@camara.leg.br</t>
         </is>
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>@nelyaquinooficial</t>
+          <t>@nelsonbarbudo</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelyaquinooficial</t>
+          <t>https://instagram.com/nelsonbarbudo</t>
         </is>
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/NelyAquino</t>
+          <t>https://youtube.com/channel/UC2wzaVfyw_DJ7Dw8vMqNoCw</t>
         </is>
       </c>
       <c r="J367" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220622</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204449</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>220703</v>
+        <v>220622</v>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>Neto Carletto</t>
+          <t>Nely Aquino</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>ORLANDO SULZ DE ALMEIDA NETO</t>
+          <t>NELI PEREIRA DE AQUINO</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>dep.netocarletto@camara.leg.br</t>
+          <t>dep.nelyaquino@camara.leg.br</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>@netocarletto</t>
+          <t>@nelyaquinooficial</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/netocarletto</t>
-        </is>
-      </c>
-      <c r="I368" s="2" t="inlineStr"/>
+          <t>https://instagram.com/nelyaquinooficial</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/NelyAquino</t>
+        </is>
+      </c>
       <c r="J368" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220703</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220622</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>178896</v>
+        <v>220703</v>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>Newton Cardoso Jr</t>
+          <t>Neto Carletto</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>NEWTON CARDOSO JUNIOR</t>
+          <t>ORLANDO SULZ DE ALMEIDA NETO</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>dep.newtoncardosojr@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G369" s="2" t="inlineStr"/>
-      <c r="H369" s="2" t="inlineStr"/>
+          <t>dep.netocarletto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>@netocarletto</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/netocarletto</t>
+        </is>
+      </c>
       <c r="I369" s="2" t="inlineStr"/>
       <c r="J369" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178896</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220703</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>204479</v>
+        <v>178896</v>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Nicoletti</t>
+          <t>Newton Cardoso Jr</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO CARLOS NICOLETTI</t>
+          <t>NEWTON CARDOSO JUNIOR</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>dep.nicoletti@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G370" s="2" t="inlineStr">
-        <is>
-          <t>@deputadonicoletti</t>
-        </is>
-      </c>
-      <c r="H370" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadonicoletti</t>
-        </is>
-      </c>
-      <c r="I370" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/DeputadoNicoletti</t>
-        </is>
-      </c>
+          <t>dep.newtoncardosojr@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr"/>
+      <c r="H370" s="2" t="inlineStr"/>
+      <c r="I370" s="2" t="inlineStr"/>
       <c r="J370" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204479</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178896</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>209787</v>
+        <v>204479</v>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Nikolas Ferreira</t>
+          <t>Nicoletti</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>NIKOLAS FERREIRA DE OLIVEIRA</t>
+          <t>ANTONIO CARLOS NICOLETTI</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -16785,641 +16781,653 @@
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>dep.nikolasferreira@camara.leg.br</t>
+          <t>dep.nicoletti@camara.leg.br</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>@nikolasferreiradm</t>
+          <t>@deputadonicoletti</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nikolasferreiradm</t>
+          <t>https://instagram.com/deputadonicoletti</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NikolasFerreiraO</t>
+          <t>https://youtube.com/DeputadoNicoletti</t>
         </is>
       </c>
       <c r="J371" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/209787</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204479</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>178986</v>
+        <v>209787</v>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Nilto Tatto</t>
+          <t>Nikolas Ferreira</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>NILTO IGNACIO TATTO</t>
+          <t>NIKOLAS FERREIRA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>dep.niltotatto@camara.leg.br</t>
+          <t>dep.nikolasferreira@camara.leg.br</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>@niltotatto</t>
+          <t>@nikolasferreiradm</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/niltotatto</t>
-        </is>
-      </c>
-      <c r="I372" s="2" t="inlineStr"/>
+          <t>https://instagram.com/nikolasferreiradm</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@NikolasFerreiraO</t>
+        </is>
+      </c>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178986</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/209787</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>204498</v>
+        <v>178986</v>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Olival Marques</t>
+          <t>Nilto Tatto</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
+          <t>NILTO IGNACIO TATTO</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>dep.olivalmarques@camara.leg.br</t>
+          <t>dep.niltotatto@camara.leg.br</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>@OlivalMarques</t>
+          <t>@niltotatto</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/OlivalMarques</t>
+          <t>https://instagram.com/niltotatto</t>
         </is>
       </c>
       <c r="I373" s="2" t="inlineStr"/>
       <c r="J373" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178986</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>178987</v>
+        <v>204498</v>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Orlando Silva</t>
+          <t>Olival Marques</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
+          <t>OLIVAL HENRIQUE MARQUES DE SOUZA</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>dep.orlandosilva@camara.leg.br</t>
+          <t>dep.olivalmarques@camara.leg.br</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>@orlandosilvasp</t>
+          <t>@OlivalMarques</t>
         </is>
       </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/orlandosilvasp</t>
+          <t>https://instagram.com/OlivalMarques</t>
         </is>
       </c>
       <c r="I374" s="2" t="inlineStr"/>
       <c r="J374" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204498</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>73692</v>
+        <v>178987</v>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Osmar Terra</t>
+          <t>Orlando Silva</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>OSMAR GASPARINI TERRA</t>
+          <t>ORLANDO SILVA DE JESUS JUNIOR</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>dep.osmarterra@camara.leg.br</t>
+          <t>dep.orlandosilva@camara.leg.br</t>
         </is>
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>@terra.osmar</t>
+          <t>@orlandosilvasp</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/terra.osmar</t>
-        </is>
-      </c>
-      <c r="I375" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/orlandosilvasp</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr"/>
       <c r="J375" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178987</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>204441</v>
+        <v>73692</v>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Otoni de Paula</t>
+          <t>Osmar Terra</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>OTONI MOURA DE PAULO JUNIOR</t>
+          <t>OSMAR GASPARINI TERRA</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>dep.otonidepaula@camara.leg.br</t>
+          <t>dep.osmarterra@camara.leg.br</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>@otonidepaulaoficial</t>
+          <t>@terra.osmar</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/otonidepaulaoficial</t>
-        </is>
-      </c>
-      <c r="I376" s="2" t="inlineStr"/>
+          <t>https://instagram.com/terra.osmar</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCZdKvhFxyXQm-JmyvHUYojA</t>
+        </is>
+      </c>
       <c r="J376" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73692</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>220706</v>
+        <v>204441</v>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Padovani</t>
+          <t>Otoni de Paula</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>NELSON FERNANDO PADOVANI</t>
+          <t>OTONI MOURA DE PAULO JUNIOR</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>dep.padovani@camara.leg.br</t>
+          <t>dep.otonidepaula@camara.leg.br</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>@nelsinhopadovani</t>
+          <t>@otonidepaulaoficial</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/nelsinhopadovani</t>
+          <t>https://instagram.com/otonidepaulaoficial</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr"/>
       <c r="J377" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220706</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204441</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>160556</v>
+        <v>220706</v>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Padre João</t>
+          <t>Padovani</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>JOÃO CARLOS SIQUEIRA</t>
+          <t>NELSON FERNANDO PADOVANI</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>dep.padrejoao@camara.leg.br</t>
+          <t>dep.padovani@camara.leg.br</t>
         </is>
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>@dep_padrejoao</t>
+          <t>@nelsinhopadovani</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dep_padrejoao</t>
-        </is>
-      </c>
-      <c r="I378" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
-        </is>
-      </c>
+          <t>https://instagram.com/nelsinhopadovani</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr"/>
       <c r="J378" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220706</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>180214</v>
+        <v>160556</v>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Pastor Diniz</t>
+          <t>Padre João</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO DINIZ ARAÚJO</t>
+          <t>JOÃO CARLOS SIQUEIRA</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>dep.pastordiniz@camara.leg.br</t>
+          <t>dep.padrejoao@camara.leg.br</t>
         </is>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>@pastordiniz.ad</t>
+          <t>@dep_padrejoao</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastordiniz.ad</t>
-        </is>
-      </c>
-      <c r="I379" s="2" t="inlineStr"/>
+          <t>https://instagram.com/dep_padrejoao</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC3xn6en0oZZdxt56VW8PS9A</t>
+        </is>
+      </c>
       <c r="J379" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160556</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>160642</v>
+        <v>180214</v>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Pastor Eurico</t>
+          <t>Pastor Diniz</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EURICO DA SILVA</t>
+          <t>RAIMUNDO DINIZ ARAÚJO</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>dep.pastoreurico@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G380" s="2" t="inlineStr"/>
-      <c r="H380" s="2" t="inlineStr"/>
+          <t>dep.pastordiniz@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>@pastordiniz.ad</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pastordiniz.ad</t>
+        </is>
+      </c>
       <c r="I380" s="2" t="inlineStr"/>
       <c r="J380" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/180214</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>204570</v>
+        <v>160642</v>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Pastor Gil</t>
+          <t>Pastor Eurico</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>GILDENEMIR DE LIMA SOUSA</t>
+          <t>FRANCISCO EURICO DA SILVA</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorgil@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G381" s="2" t="inlineStr">
-        <is>
-          <t>@deputadogildenemyr</t>
-        </is>
-      </c>
-      <c r="H381" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadogildenemyr</t>
-        </is>
-      </c>
+          <t>dep.pastoreurico@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr"/>
+      <c r="H381" s="2" t="inlineStr"/>
       <c r="I381" s="2" t="inlineStr"/>
       <c r="J381" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160642</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>220615</v>
+        <v>204570</v>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>Pastor Henrique Vieira</t>
+          <t>Pastor Gil</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
+          <t>GILDENEMIR DE LIMA SOUSA</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorhenriquevieira@camara.leg.br</t>
+          <t>dep.pastorgil@camara.leg.br</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>@pastorhenriquevieira</t>
+          <t>@deputadogildenemyr</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastorhenriquevieira</t>
-        </is>
-      </c>
-      <c r="I382" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/PastorHenriqueVieira</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadogildenemyr</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr"/>
       <c r="J382" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204570</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>204553</v>
+        <v>220615</v>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>Pastor Sargento Isidório</t>
+          <t>Pastor Henrique Vieira</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
+          <t>HENRIQUE DOS SANTOS VIEIRA LIMA</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
+          <t>dep.pastorhenriquevieira@camara.leg.br</t>
         </is>
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>@pastorsargentoisidorio</t>
+          <t>@pastorhenriquevieira</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pastorsargentoisidorio</t>
-        </is>
-      </c>
-      <c r="I383" s="2" t="inlineStr"/>
+          <t>https://instagram.com/pastorhenriquevieira</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PastorHenriqueVieira</t>
+        </is>
+      </c>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220615</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>74160</v>
+        <v>204553</v>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>Patrus Ananias</t>
+          <t>Pastor Sargento Isidório</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>PATRUS ANANIAS DE SOUZA</t>
+          <t>MANOEL ISIDORIO DE SANTANA JUNIOR</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>dep.patrusananias@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G384" s="2" t="inlineStr"/>
-      <c r="H384" s="2" t="inlineStr"/>
+          <t>dep.pastorsargentoisidorio@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>@pastorsargentoisidorio</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pastorsargentoisidorio</t>
+        </is>
+      </c>
       <c r="I384" s="2" t="inlineStr"/>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204553</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>171617</v>
+        <v>74160</v>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Paulão</t>
+          <t>Patrus Ananias</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>PAULO FERNANDO DOS SANTOS</t>
+          <t>PATRUS ANANIAS DE SOUZA</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
@@ -17429,12 +17437,12 @@
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>dep.paulao@camara.leg.br</t>
+          <t>dep.patrusananias@camara.leg.br</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr"/>
@@ -17442,37 +17450,37 @@
       <c r="I385" s="2" t="inlineStr"/>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171617</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74160</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>141518</v>
+        <v>171617</v>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Paulinho da Força</t>
+          <t>Paulão</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>PAULO PEREIRA DA SILVA</t>
+          <t>PAULO FERNANDO DOS SANTOS</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>dep.paulinhodaforca@camara.leg.br</t>
+          <t>dep.paulao@camara.leg.br</t>
         </is>
       </c>
       <c r="G386" s="2" t="inlineStr"/>
@@ -17480,37 +17488,37 @@
       <c r="I386" s="2" t="inlineStr"/>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171617</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>141516</v>
+        <v>141518</v>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Paulo Abi-Ackel</t>
+          <t>Paulinho da Força</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>PAULO ABI-ACKEL</t>
+          <t>PAULO PEREIRA DA SILVA</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>SOLIDARIEDADE</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloabiackel@camara.leg.br</t>
+          <t>dep.paulinhodaforca@camara.leg.br</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr"/>
@@ -17518,213 +17526,213 @@
       <c r="I387" s="2" t="inlineStr"/>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141518</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>220650</v>
+        <v>141516</v>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>Paulo Alexandre Barbosa</t>
+          <t>Paulo Abi-Ackel</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
+          <t>PAULO ABI-ACKEL</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G388" s="2" t="inlineStr">
-        <is>
-          <t>@pauloalexandrebarbosa</t>
-        </is>
-      </c>
-      <c r="H388" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pauloalexandrebarbosa</t>
-        </is>
-      </c>
+          <t>dep.pauloabiackel@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr"/>
+      <c r="H388" s="2" t="inlineStr"/>
       <c r="I388" s="2" t="inlineStr"/>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141516</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>178860</v>
+        <v>220650</v>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>Paulo Azi</t>
+          <t>Paulo Alexandre Barbosa</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>PAULO VELLOSO DANTAS AZI</t>
+          <t>PAULO ALEXANDRE PEREIRA BARBOSA</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloazi@camara.leg.br</t>
+          <t>dep.pauloalexandrebarbosa@camara.leg.br</t>
         </is>
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>@PauloAziofcial</t>
+          <t>@pauloalexandrebarbosa</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/PauloAziofcial</t>
+          <t>https://instagram.com/pauloalexandrebarbosa</t>
         </is>
       </c>
       <c r="I389" s="2" t="inlineStr"/>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220650</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>160517</v>
+        <v>178860</v>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>Paulo Folletto</t>
+          <t>Paulo Azi</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FOLLETTO</t>
+          <t>PAULO VELLOSO DANTAS AZI</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofolletto@camara.leg.br</t>
+          <t>dep.pauloazi@camara.leg.br</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>@paulo.folletto</t>
+          <t>@PauloAziofcial</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/paulo.folletto</t>
+          <t>https://instagram.com/PauloAziofcial</t>
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr"/>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178860</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>160558</v>
+        <v>160517</v>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>Paulo Freire Costa</t>
+          <t>Paulo Folletto</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO FREIRE DA COSTA</t>
+          <t>PAULO ROBERTO FOLLETTO</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>dep.paulofreirecosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G391" s="2" t="inlineStr"/>
-      <c r="H391" s="2" t="inlineStr"/>
+          <t>dep.paulofolletto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>@paulo.folletto</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/paulo.folletto</t>
+        </is>
+      </c>
       <c r="I391" s="2" t="inlineStr"/>
       <c r="J391" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160517</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>204492</v>
+        <v>160558</v>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>Paulo Guedes</t>
+          <t>Paulo Freire Costa</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>PAULO JOSE CARLOS GUEDES</t>
+          <t>PAULO ROBERTO FREIRE DA COSTA</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloguedes@camara.leg.br</t>
+          <t>dep.paulofreirecosta@camara.leg.br</t>
         </is>
       </c>
       <c r="G392" s="2" t="inlineStr"/>
@@ -17732,22 +17740,22 @@
       <c r="I392" s="2" t="inlineStr"/>
       <c r="J392" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160558</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>233592</v>
+        <v>204492</v>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>Paulo Lemos</t>
+          <t>Paulo Guedes</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
+          <t>PAULO JOSE CARLOS GUEDES</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
@@ -17757,100 +17765,100 @@
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G393" s="2" t="inlineStr">
-        <is>
-          <t>@paulolemosap</t>
-        </is>
-      </c>
-      <c r="H393" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/paulolemosap</t>
-        </is>
-      </c>
-      <c r="I393" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
-        </is>
-      </c>
+          <t>dep.pauloguedes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr"/>
+      <c r="H393" s="2" t="inlineStr"/>
+      <c r="I393" s="2" t="inlineStr"/>
       <c r="J393" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204492</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>220685</v>
+        <v>233592</v>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>Paulo Litro</t>
+          <t>Paulo Lemos</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
+          <t>PAULO CESAR LEMOS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>dep.paulolitro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G394" s="2" t="inlineStr"/>
-      <c r="H394" s="2" t="inlineStr"/>
-      <c r="I394" s="2" t="inlineStr"/>
+          <t>dep.paulolemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>@paulolemosap</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/paulolemosap</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCPt5rQPkiVFL3kskxR0CP7Q</t>
+        </is>
+      </c>
       <c r="J394" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233592</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>74574</v>
+        <v>220685</v>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>Paulo Magalhães</t>
+          <t>Paulo Litro</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
+          <t>PAULO HENRIQUE COLETTI FERNANDES</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>dep.paulomagalhaes@camara.leg.br</t>
+          <t>dep.paulolitro@camara.leg.br</t>
         </is>
       </c>
       <c r="G395" s="2" t="inlineStr"/>
@@ -17858,37 +17866,37 @@
       <c r="I395" s="2" t="inlineStr"/>
       <c r="J395" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220685</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>128760</v>
+        <v>74574</v>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>Paulo Marinho Jr</t>
+          <t>Paulo Magalhães</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>PAULO CELSO FONSECA MARINHO JÚNIOR</t>
+          <t>PAULO SÉRGIO PARANHOS DE MAGALHÃES</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>dep.paulomarinhojr@camara.leg.br</t>
+          <t>dep.paulomagalhaes@camara.leg.br</t>
         </is>
       </c>
       <c r="G396" s="2" t="inlineStr"/>
@@ -17896,37 +17904,37 @@
       <c r="I396" s="2" t="inlineStr"/>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/128760</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74574</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>74400</v>
+        <v>128760</v>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>Paulo Pimenta</t>
+          <t>Paulo Marinho Jr</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>PAULO ROBERTO SEVERO PIMENTA</t>
+          <t>PAULO CELSO FONSECA MARINHO JÚNIOR</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>dep.paulopimenta@camara.leg.br</t>
+          <t>dep.paulomarinhojr@camara.leg.br</t>
         </is>
       </c>
       <c r="G397" s="2" t="inlineStr"/>
@@ -17934,22 +17942,22 @@
       <c r="I397" s="2" t="inlineStr"/>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/128760</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>141488</v>
+        <v>74400</v>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Paulo Teixeira</t>
+          <t>Paulo Pimenta</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
+          <t>PAULO ROBERTO SEVERO PIMENTA</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
@@ -17959,272 +17967,272 @@
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloteixeira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G398" s="2" t="inlineStr">
-        <is>
-          <t>@pauloteixeira13</t>
-        </is>
-      </c>
-      <c r="H398" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pauloteixeira13</t>
-        </is>
-      </c>
+          <t>dep.paulopimenta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr"/>
+      <c r="H398" s="2" t="inlineStr"/>
       <c r="I398" s="2" t="inlineStr"/>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74400</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>220630</v>
+        <v>141488</v>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>Pedro Aihara</t>
+          <t>Paulo Teixeira</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
+          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>dep.pedroaihara@camara.leg.br</t>
+          <t>dep.pauloteixeira@camara.leg.br</t>
         </is>
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>@pedroaihara</t>
+          <t>@pauloteixeira13</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedroaihara</t>
+          <t>https://instagram.com/pauloteixeira13</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr"/>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>220667</v>
+        <v>220630</v>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Pedro Campos</t>
+          <t>Pedro Aihara</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
+          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrocampos@camara.leg.br</t>
+          <t>dep.pedroaihara@camara.leg.br</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>@pedrocampospe</t>
+          <t>@pedroaihara</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedrocampospe</t>
+          <t>https://instagram.com/pedroaihara</t>
         </is>
       </c>
       <c r="I400" s="2" t="inlineStr"/>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>122974</v>
+        <v>220667</v>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lucas Fernandes</t>
+          <t>Pedro Campos</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
+          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolucasfernandes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G401" s="2" t="inlineStr"/>
-      <c r="H401" s="2" t="inlineStr"/>
+          <t>dep.pedrocampos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>@pedrocampospe</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrocampospe</t>
+        </is>
+      </c>
       <c r="I401" s="2" t="inlineStr"/>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>204395</v>
+        <v>122974</v>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lupion</t>
+          <t>Pedro Lucas Fernandes</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DEBONI LUPION MELLO</t>
+          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolupion@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G402" s="2" t="inlineStr">
-        <is>
-          <t>@pedrolupion</t>
-        </is>
-      </c>
-      <c r="H402" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrolupion</t>
-        </is>
-      </c>
+          <t>dep.pedrolucasfernandes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr"/>
+      <c r="H402" s="2" t="inlineStr"/>
       <c r="I402" s="2" t="inlineStr"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>122158</v>
+        <v>204395</v>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Pedro Paulo</t>
+          <t>Pedro Lupion</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
+          <t>PEDRO DEBONI LUPION MELLO</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>dep.pedropaulo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G403" s="2" t="inlineStr"/>
-      <c r="H403" s="2" t="inlineStr"/>
+          <t>dep.pedrolupion@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>@pedrolupion</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrolupion</t>
+        </is>
+      </c>
       <c r="I403" s="2" t="inlineStr"/>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>160604</v>
+        <v>122158</v>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Pedro Uczai</t>
+          <t>Pedro Paulo</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>PEDRO FRANCISCO UCZAI</t>
+          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrouczai@camara.leg.br</t>
+          <t>dep.pedropaulo@camara.leg.br</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr"/>
@@ -18232,37 +18240,37 @@
       <c r="I404" s="2" t="inlineStr"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>204406</v>
+        <v>160604</v>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Pedro Westphalen</t>
+          <t>Pedro Uczai</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>PEDRO BANDARRA WESTPHALEN</t>
+          <t>PEDRO FRANCISCO UCZAI</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrowestphalen@camara.leg.br</t>
+          <t>dep.pedrouczai@camara.leg.br</t>
         </is>
       </c>
       <c r="G405" s="2" t="inlineStr"/>
@@ -18270,612 +18278,612 @@
       <c r="I405" s="2" t="inlineStr"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>161440</v>
+        <v>204406</v>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Pezenti</t>
+          <t>Pedro Westphalen</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL PEZENTI</t>
+          <t>PEDRO BANDARRA WESTPHALEN</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>dep.pezenti@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G406" s="2" t="inlineStr">
-        <is>
-          <t>@deputadopezenti</t>
-        </is>
-      </c>
-      <c r="H406" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadopezenti</t>
-        </is>
-      </c>
+          <t>dep.pedrowestphalen@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr"/>
+      <c r="H406" s="2" t="inlineStr"/>
       <c r="I406" s="2" t="inlineStr"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>204524</v>
+        <v>161440</v>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>Pinheirinho</t>
+          <t>Pezenti</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>ANTÔNIO PINHEIRO NETO</t>
+          <t>RAFAEL PEZENTI</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>dep.pinheirinho@camara.leg.br</t>
+          <t>dep.pezenti@camara.leg.br</t>
         </is>
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>@pinheirinhomg</t>
+          <t>@deputadopezenti</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pinheirinhomg</t>
-        </is>
-      </c>
-      <c r="I407" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadopezenti</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>73486</v>
+        <v>204524</v>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Pompeo de Mattos</t>
+          <t>Pinheirinho</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>DARCI POMPEO DE MATTOS</t>
+          <t>ANTÔNIO PINHEIRO NETO</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>dep.pompeodemattos@camara.leg.br</t>
+          <t>dep.pinheirinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>@pompeodemattospdt</t>
+          <t>@pinheirinhomg</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pompeodemattospdt</t>
+          <t>https://instagram.com/pinheirinhomg</t>
         </is>
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/PompeodeMattos</t>
+          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>160601</v>
+        <v>73486</v>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Pr. Marco Feliciano</t>
+          <t>Pompeo de Mattos</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>MARCO ANTÔNIO FELICIANO</t>
+          <t>DARCI POMPEO DE MATTOS</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>dep.pr.marcofeliciano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G409" s="2" t="inlineStr"/>
-      <c r="H409" s="2" t="inlineStr"/>
-      <c r="I409" s="2" t="inlineStr"/>
+          <t>dep.pompeodemattos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>@pompeodemattospdt</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pompeodemattospdt</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PompeodeMattos</t>
+        </is>
+      </c>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>220533</v>
+        <v>160601</v>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Prof. Reginaldo Veras</t>
+          <t>Pr. Marco Feliciano</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Veras Coelho</t>
+          <t>MARCO ANTÔNIO FELICIANO</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>dep.prof.reginaldoveras@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G410" s="2" t="inlineStr">
-        <is>
-          <t>@reginaldo.veras</t>
-        </is>
-      </c>
-      <c r="H410" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/reginaldo.veras</t>
-        </is>
-      </c>
-      <c r="I410" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/Reginaldoveras12</t>
-        </is>
-      </c>
+          <t>dep.pr.marcofeliciano@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr"/>
+      <c r="H410" s="2" t="inlineStr"/>
+      <c r="I410" s="2" t="inlineStr"/>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>204390</v>
+        <v>220533</v>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Professor Alcides</t>
+          <t>Prof. Reginaldo Veras</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>ALCIDES RIBEIRO FILHO</t>
+          <t>Reginaldo Veras Coelho</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralcides@camara.leg.br</t>
+          <t>dep.prof.reginaldoveras@camara.leg.br</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>@professoralcidesoficial</t>
+          <t>@reginaldo.veras</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/professoralcidesoficial</t>
+          <t>https://instagram.com/reginaldo.veras</t>
         </is>
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+          <t>https://youtube.com/Reginaldoveras12</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>221338</v>
+        <v>204390</v>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Professora Luciene Cavalcante</t>
+          <t>Professor Alcides</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>LUCIENE CAVALCANTE DA SILVA</t>
+          <t>ALCIDES RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralucienecavalcante@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G412" s="2" t="inlineStr"/>
-      <c r="H412" s="2" t="inlineStr"/>
-      <c r="I412" s="2" t="inlineStr"/>
+          <t>dep.professoralcides@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>@professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+        </is>
+      </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>160641</v>
+        <v>221338</v>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Professora Marcivania</t>
+          <t>Professora Luciene Cavalcante</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
+          <t>LUCIENE CAVALCANTE DA SILVA</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>dep.professoramarcivania@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G413" s="2" t="inlineStr">
-        <is>
-          <t>@profmarcivania</t>
-        </is>
-      </c>
-      <c r="H413" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/profmarcivania</t>
-        </is>
-      </c>
+          <t>dep.professoralucienecavalcante@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr"/>
+      <c r="H413" s="2" t="inlineStr"/>
       <c r="I413" s="2" t="inlineStr"/>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>220586</v>
+        <v>160641</v>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Rafael Brito</t>
+          <t>Professora Marcivania</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL DE GOES BRITO</t>
+          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelbrito@camara.leg.br</t>
+          <t>dep.professoramarcivania@camara.leg.br</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>@rafaelbrito15</t>
+          <t>@profmarcivania</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="I414" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
-        </is>
-      </c>
+          <t>https://instagram.com/profmarcivania</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>233594</v>
+        <v>220586</v>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Rafael Fera</t>
+          <t>Rafael Brito</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL BENTO PEREIRA</t>
+          <t>RAFAEL DE GOES BRITO</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelfera@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G415" s="2" t="inlineStr"/>
-      <c r="H415" s="2" t="inlineStr"/>
-      <c r="I415" s="2" t="inlineStr"/>
+          <t>dep.rafaelbrito@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
+        </is>
+      </c>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>220532</v>
+        <v>233594</v>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Rafael Prudente</t>
+          <t>Rafael Fera</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL CAVALCANTI PRUDENTE</t>
+          <t>RAFAEL BENTO PEREIRA</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelprudente@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G416" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="H416" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="I416" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RafaelPrudente</t>
-        </is>
-      </c>
+          <t>dep.rafaelfera@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr"/>
+      <c r="H416" s="2" t="inlineStr"/>
+      <c r="I416" s="2" t="inlineStr"/>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>220626</v>
+        <v>220532</v>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Rafael Simoes</t>
+          <t>Rafael Prudente</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL TADEU SIMÕES</t>
+          <t>RAFAEL CAVALCANTI PRUDENTE</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelsimoes@camara.leg.br</t>
+          <t>dep.rafaelprudente@camara.leg.br</t>
         </is>
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>@rafaelsimoesmg</t>
+          <t>@rafaelprudentedep</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelsimoesmg</t>
-        </is>
-      </c>
-      <c r="I417" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RafaelPrudente</t>
+        </is>
+      </c>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>204567</v>
+        <v>220626</v>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Costa</t>
+          <t>Rafael Simoes</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO MAGALHÃES COSTA</t>
+          <t>RAFAEL TADEU SIMÕES</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundocosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G418" s="2" t="inlineStr"/>
-      <c r="H418" s="2" t="inlineStr"/>
+          <t>dep.rafaelsimoes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelsimoesmg</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelsimoesmg</t>
+        </is>
+      </c>
       <c r="I418" s="2" t="inlineStr"/>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>74084</v>
+        <v>204567</v>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Santos</t>
+          <t>Raimundo Costa</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
+          <t>RAIMUNDO MAGALHÃES COSTA</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
@@ -18885,127 +18893,123 @@
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundosantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G419" s="2" t="inlineStr">
-        <is>
-          <t>@depraimundosantos</t>
-        </is>
-      </c>
-      <c r="H419" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depraimundosantos</t>
-        </is>
-      </c>
-      <c r="I419" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
-        </is>
-      </c>
+          <t>dep.raimundocosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr"/>
+      <c r="H419" s="2" t="inlineStr"/>
+      <c r="I419" s="2" t="inlineStr"/>
       <c r="J419" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>115200</v>
+        <v>74084</v>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>Raniery Paulino</t>
+          <t>Raimundo Santos</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
+          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>dep.ranierypaulino@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G420" s="2" t="inlineStr"/>
-      <c r="H420" s="2" t="inlineStr"/>
-      <c r="I420" s="2" t="inlineStr"/>
+          <t>dep.raimundosantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>@depraimundosantos</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depraimundosantos</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
+        </is>
+      </c>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>74161</v>
+        <v>115200</v>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Lopes</t>
+          <t>Raniery Paulino</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
+          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>dep.reginaldolopes@camara.leg.br</t>
+          <t>dep.ranierypaulino@camara.leg.br</t>
         </is>
       </c>
       <c r="G421" s="2" t="inlineStr"/>
       <c r="H421" s="2" t="inlineStr"/>
-      <c r="I421" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
-        </is>
-      </c>
+      <c r="I421" s="2" t="inlineStr"/>
       <c r="J421" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>220606</v>
+        <v>74161</v>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>Reimont</t>
+          <t>Reginaldo Lopes</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
+          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -19015,50 +19019,54 @@
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>dep.reimont@camara.leg.br</t>
+          <t>dep.reginaldolopes@camara.leg.br</t>
         </is>
       </c>
       <c r="G422" s="2" t="inlineStr"/>
       <c r="H422" s="2" t="inlineStr"/>
-      <c r="I422" s="2" t="inlineStr"/>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
+        </is>
+      </c>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>178989</v>
+        <v>220606</v>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>Renata Abreu</t>
+          <t>Reimont</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>RENATA HELLMEISTER DE ABREU</t>
+          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>dep.renataabreu@camara.leg.br</t>
+          <t>dep.reimont@camara.leg.br</t>
         </is>
       </c>
       <c r="G423" s="2" t="inlineStr"/>
@@ -19066,183 +19074,175 @@
       <c r="I423" s="2" t="inlineStr"/>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178989</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>153423</v>
+        <v>178989</v>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>Renilce Nicodemos</t>
+          <t>Renata Abreu</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
+          <t>RENATA HELLMEISTER DE ABREU</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>dep.renilcenicodemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>@renilcenicodemoss</t>
-        </is>
-      </c>
-      <c r="H424" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/renilcenicodemoss</t>
-        </is>
-      </c>
+          <t>dep.renataabreu@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr"/>
+      <c r="H424" s="2" t="inlineStr"/>
       <c r="I424" s="2" t="inlineStr"/>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178989</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>73801</v>
+        <v>153423</v>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>Renildo Calheiros</t>
+          <t>Renilce Nicodemos</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>RENILDO VASCONCELOS CALHEIROS</t>
+          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>dep.renildocalheiros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G425" s="2" t="inlineStr"/>
-      <c r="H425" s="2" t="inlineStr"/>
+          <t>dep.renilcenicodemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>@renilcenicodemoss</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/renilcenicodemoss</t>
+        </is>
+      </c>
       <c r="I425" s="2" t="inlineStr"/>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>175765</v>
+        <v>73801</v>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>Ribamar Silva</t>
+          <t>Renildo Calheiros</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>RIBAMAR ANTONIO DA SILVA</t>
+          <t>RENILDO VASCONCELOS CALHEIROS</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>dep.ribamarsilva@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G426" s="2" t="inlineStr">
-        <is>
-          <t>@ribamarsilvaoficial</t>
-        </is>
-      </c>
-      <c r="H426" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ribamarsilvaoficial</t>
-        </is>
-      </c>
+          <t>dep.renildocalheiros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr"/>
+      <c r="H426" s="2" t="inlineStr"/>
       <c r="I426" s="2" t="inlineStr"/>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>235088</v>
+        <v>175765</v>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>Ribeiro Neto</t>
+          <t>Ribamar Silva</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>AIRES DO ESPIRITO SANTO RIBEIRO NETO</t>
+          <t>RIBAMAR ANTONIO DA SILVA</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>SOLIDARIEDADE</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>dep.ribeironeto@camara.leg.br</t>
+          <t>dep.ribamarsilva@camara.leg.br</t>
         </is>
       </c>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>@ribeironeto.ma</t>
+          <t>@ribamarsilvaoficial</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ribeironeto.ma</t>
+          <t>https://instagram.com/ribamarsilvaoficial</t>
         </is>
       </c>
       <c r="I427" s="2" t="inlineStr"/>
       <c r="J427" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235088</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
         </is>
       </c>
     </row>
@@ -20637,17 +20637,17 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>@deputadosanderson</t>
+          <t>@sandersonrs</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadosanderson</t>
+          <t>https://instagram.com/sandersonrs</t>
         </is>
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC3bESW2nMM1EW-in7OwlKwg?view_as=subscriber</t>
+          <t>https://youtube.com/channel/UCR_FE7jk9lWQKLixmnf0_sA</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -10070,31 +10070,31 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>204419</v>
+        <v>152605</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Glaustin da Fokus</t>
+          <t>Glauber Braga</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>GLAUSKSTON BATISTA RIOS</t>
+          <t>GLAUBER DE MEDEIROS BRAGA</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>dep.glaustindafokus@camara.leg.br</t>
+          <t>dep.glauberbraga@camara.leg.br</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr"/>
@@ -10102,37 +10102,37 @@
       <c r="I219" s="2" t="inlineStr"/>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204419</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/152605</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>236284</v>
+        <v>204419</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Glaycon Franco</t>
+          <t>Glaustin da Fokus</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>GLYCON MOREIRA FRANCO</t>
+          <t>GLAUSKSTON BATISTA RIOS</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>dep.glayconfranco@camara.leg.br</t>
+          <t>dep.glaustindafokus@camara.leg.br</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr"/>
@@ -10140,321 +10140,321 @@
       <c r="I220" s="2" t="inlineStr"/>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236284</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204419</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>107283</v>
+        <v>236284</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Gleisi Hoffmann</t>
+          <t>Glaycon Franco</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>GLEISI HELENA HOFFMANN</t>
+          <t>GLYCON MOREIRA FRANCO</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>dep.gleisihoffmann@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t>@gleisihoffmann</t>
-        </is>
-      </c>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/gleisihoffmann</t>
-        </is>
-      </c>
-      <c r="I221" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/GleisiHoffmannPT</t>
-        </is>
-      </c>
+          <t>dep.glayconfranco@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr"/>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/107283</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236284</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>198197</v>
+        <v>107283</v>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Greyce Elias</t>
+          <t>Gleisi Hoffmann</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>GREYCE DE QUEIROZ ELIAS</t>
+          <t>GLEISI HELENA HOFFMANN</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>dep.greyceelias@camara.leg.br</t>
+          <t>dep.gleisihoffmann@camara.leg.br</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>@greyceelias</t>
+          <t>@gleisihoffmann</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/greyceelias</t>
+          <t>https://instagram.com/gleisihoffmann</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCcSZxLiSfO1dFmAryUnxPHg</t>
+          <t>https://youtube.com/GleisiHoffmannPT</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/198197</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/107283</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>204531</v>
+        <v>198197</v>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Derrite</t>
+          <t>Greyce Elias</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>GUILHERME MURARO DERRITE</t>
+          <t>GREYCE DE QUEIROZ ELIAS</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>dep.guilhermederrite@camara.leg.br</t>
+          <t>dep.greyceelias@camara.leg.br</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>@capitaoderrite</t>
+          <t>@greyceelias</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/capitaoderrite</t>
+          <t>https://instagram.com/greyceelias</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCZHZxgmwC2c5tz3_Jn-gGOw</t>
+          <t>https://youtube.com/channel/UCcSZxLiSfO1dFmAryUnxPHg</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204531</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/198197</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>220664</v>
+        <v>204531</v>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Uchoa</t>
+          <t>Guilherme Derrite</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>GUILHERME A. UCHOA CAVALCANTI PESSOA DE MELO JUNIOR</t>
+          <t>GUILHERME MURARO DERRITE</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>dep.guilhermeuchoa@camara.leg.br</t>
+          <t>dep.guilhermederrite@camara.leg.br</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>@GUILHERMEUCHOAJR</t>
+          <t>@capitaoderrite</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/GUILHERMEUCHOAJR</t>
-        </is>
-      </c>
-      <c r="I224" s="2" t="inlineStr"/>
+          <t>https://instagram.com/capitaoderrite</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCZHZxgmwC2c5tz3_Jn-gGOw</t>
+        </is>
+      </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220664</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204531</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>220568</v>
+        <v>220664</v>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Gayer</t>
+          <t>Guilherme Uchoa</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>GUSTAVO GAYER MACHADO DE ARAUJO</t>
+          <t>GUILHERME A. UCHOA CAVALCANTI PESSOA DE MELO JUNIOR</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>dep.gustavogayer@camara.leg.br</t>
+          <t>dep.guilhermeuchoa@camara.leg.br</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>@gusgayer</t>
+          <t>@GUILHERMEUCHOAJR</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gusgayer</t>
-        </is>
-      </c>
-      <c r="I225" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/GustavoGayer</t>
-        </is>
-      </c>
+          <t>https://instagram.com/GUILHERMEUCHOAJR</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr"/>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220568</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220664</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>204408</v>
+        <v>220568</v>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Gustinho Ribeiro</t>
+          <t>Gustavo Gayer</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>LUIZ AUGUSTO CARVALHO RIBEIRO FILHO</t>
+          <t>GUSTAVO GAYER MACHADO DE ARAUJO</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>dep.gustinhoribeiro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr"/>
-      <c r="I226" s="2" t="inlineStr"/>
+          <t>dep.gustavogayer@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>@gusgayer</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/gusgayer</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/GustavoGayer</t>
+        </is>
+      </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204408</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220568</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>204456</v>
+        <v>204408</v>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Gutemberg Reis</t>
+          <t>Gustinho Ribeiro</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>GUTEMBERG REIS DE OLIVEIRA</t>
+          <t>LUIZ AUGUSTO CARVALHO RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>dep.gutembergreis@camara.leg.br</t>
+          <t>dep.gustinhoribeiro@camara.leg.br</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr"/>
@@ -10462,203 +10462,195 @@
       <c r="I227" s="2" t="inlineStr"/>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204456</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204408</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>178964</v>
+        <v>204456</v>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Heitor Schuch</t>
+          <t>Gutemberg Reis</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>HEITOR JOSE SCHUCH</t>
+          <t>GUTEMBERG REIS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>dep.heitorschuch@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>@heitorschuch</t>
-        </is>
-      </c>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/heitorschuch</t>
-        </is>
-      </c>
+          <t>dep.gutembergreis@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr"/>
       <c r="I228" s="2" t="inlineStr"/>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178964</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204456</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>178873</v>
+        <v>178964</v>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Helder Salomão</t>
+          <t>Heitor Schuch</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>HELDER IGNACIO SALOMAO</t>
+          <t>HEITOR JOSE SCHUCH</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>dep.heldersalomao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr"/>
+          <t>dep.heitorschuch@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>@heitorschuch</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/heitorschuch</t>
+        </is>
+      </c>
       <c r="I229" s="2" t="inlineStr"/>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178873</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178964</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>220537</v>
+        <v>178873</v>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Helena Lima</t>
+          <t>Helder Salomão</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>MARIA HELENA TEIXEIRA LIMA</t>
+          <t>HELDER IGNACIO SALOMAO</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>dep.helenalima@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>@helenadaasatur</t>
-        </is>
-      </c>
-      <c r="H230" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/helenadaasatur</t>
-        </is>
-      </c>
+          <t>dep.heldersalomao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
       <c r="I230" s="2" t="inlineStr"/>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220537</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178873</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>204444</v>
+        <v>220537</v>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Helio Lopes</t>
+          <t>Helena Lima</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>HELIO FERNANDO BARBOSA LOPES</t>
+          <t>MARIA HELENA TEIXEIRA LIMA</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>dep.heliolopes@camara.leg.br</t>
+          <t>dep.helenalima@camara.leg.br</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>@depheliolopes</t>
+          <t>@helenadaasatur</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/depheliolopes</t>
+          <t>https://instagram.com/helenadaasatur</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204444</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220537</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>234788</v>
+        <v>204444</v>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Heloísa Helena</t>
+          <t>Helio Lopes</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>HELOÍSA HELENA LIMA DE MORAES CARVALHO</t>
+          <t>HELIO FERNANDO BARBOSA LOPES</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>REDE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -10668,23 +10660,23 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>dep.heloisahelena@camara.leg.br</t>
+          <t>dep.heliolopes@camara.leg.br</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>@_heloisa_helena</t>
+          <t>@depheliolopes</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/_heloisa_helena</t>
+          <t>https://instagram.com/depheliolopes</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/234788</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204444</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -17982,21 +17982,21 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>141488</v>
+        <v>154700</v>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>Paulo Teixeira</t>
+          <t>Paulo Soares</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
+          <t>PAULO ROMEIRO DE ALMEIDA SOARES</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
@@ -18006,267 +18006,267 @@
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>dep.pauloteixeira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G399" s="2" t="inlineStr">
-        <is>
-          <t>@pauloteixeira13</t>
-        </is>
-      </c>
-      <c r="H399" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pauloteixeira13</t>
-        </is>
-      </c>
+          <t>dep.paulosoares@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr"/>
+      <c r="H399" s="2" t="inlineStr"/>
       <c r="I399" s="2" t="inlineStr"/>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/154700</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>220630</v>
+        <v>141488</v>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Pedro Aihara</t>
+          <t>Paulo Teixeira</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
+          <t>LUIZ PAULO TEIXEIRA FERREIRA</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>dep.pedroaihara@camara.leg.br</t>
+          <t>dep.pauloteixeira@camara.leg.br</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>@pedroaihara</t>
+          <t>@pauloteixeira13</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedroaihara</t>
+          <t>https://instagram.com/pauloteixeira13</t>
         </is>
       </c>
       <c r="I400" s="2" t="inlineStr"/>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141488</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>220667</v>
+        <v>220630</v>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Pedro Campos</t>
+          <t>Pedro Aihara</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
+          <t>PEDRO DOSHIKAZU PIANCHAO AIHARA</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrocampos@camara.leg.br</t>
+          <t>dep.pedroaihara@camara.leg.br</t>
         </is>
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>@pedrocampospe</t>
+          <t>@pedroaihara</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pedrocampospe</t>
+          <t>https://instagram.com/pedroaihara</t>
         </is>
       </c>
       <c r="I401" s="2" t="inlineStr"/>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220630</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>122974</v>
+        <v>220667</v>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lucas Fernandes</t>
+          <t>Pedro Campos</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
+          <t>PEDRO HENRIQUE DE A. L. C. CAMPOS</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolucasfernandes@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G402" s="2" t="inlineStr"/>
-      <c r="H402" s="2" t="inlineStr"/>
+          <t>dep.pedrocampos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>@pedrocampospe</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrocampospe</t>
+        </is>
+      </c>
       <c r="I402" s="2" t="inlineStr"/>
       <c r="J402" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220667</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>204395</v>
+        <v>122974</v>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Pedro Lupion</t>
+          <t>Pedro Lucas Fernandes</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>PEDRO DEBONI LUPION MELLO</t>
+          <t>PEDRO LUCAS ANDRADE FERNANDES RIBEIRO</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrolupion@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G403" s="2" t="inlineStr">
-        <is>
-          <t>@pedrolupion</t>
-        </is>
-      </c>
-      <c r="H403" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/pedrolupion</t>
-        </is>
-      </c>
+          <t>dep.pedrolucasfernandes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr"/>
+      <c r="H403" s="2" t="inlineStr"/>
       <c r="I403" s="2" t="inlineStr"/>
       <c r="J403" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122974</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>122158</v>
+        <v>204395</v>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Pedro Paulo</t>
+          <t>Pedro Lupion</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
+          <t>PEDRO DEBONI LUPION MELLO</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>dep.pedropaulo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G404" s="2" t="inlineStr"/>
-      <c r="H404" s="2" t="inlineStr"/>
+          <t>dep.pedrolupion@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>@pedrolupion</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pedrolupion</t>
+        </is>
+      </c>
       <c r="I404" s="2" t="inlineStr"/>
       <c r="J404" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204395</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>160604</v>
+        <v>122158</v>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>Pedro Uczai</t>
+          <t>Pedro Paulo</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>PEDRO FRANCISCO UCZAI</t>
+          <t>PEDRO PAULO CARVALHO TEIXEIRA</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrouczai@camara.leg.br</t>
+          <t>dep.pedropaulo@camara.leg.br</t>
         </is>
       </c>
       <c r="G405" s="2" t="inlineStr"/>
@@ -18274,37 +18274,37 @@
       <c r="I405" s="2" t="inlineStr"/>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/122158</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>204406</v>
+        <v>160604</v>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Pedro Westphalen</t>
+          <t>Pedro Uczai</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>PEDRO BANDARRA WESTPHALEN</t>
+          <t>PEDRO FRANCISCO UCZAI</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>dep.pedrowestphalen@camara.leg.br</t>
+          <t>dep.pedrouczai@camara.leg.br</t>
         </is>
       </c>
       <c r="G406" s="2" t="inlineStr"/>
@@ -18312,612 +18312,612 @@
       <c r="I406" s="2" t="inlineStr"/>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160604</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>161440</v>
+        <v>204406</v>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>Pezenti</t>
+          <t>Pedro Westphalen</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL PEZENTI</t>
+          <t>PEDRO BANDARRA WESTPHALEN</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>dep.pezenti@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G407" s="2" t="inlineStr">
-        <is>
-          <t>@deputadopezenti</t>
-        </is>
-      </c>
-      <c r="H407" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/deputadopezenti</t>
-        </is>
-      </c>
+          <t>dep.pedrowestphalen@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr"/>
+      <c r="H407" s="2" t="inlineStr"/>
       <c r="I407" s="2" t="inlineStr"/>
       <c r="J407" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204406</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>204524</v>
+        <v>161440</v>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Pinheirinho</t>
+          <t>Pezenti</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>ANTÔNIO PINHEIRO NETO</t>
+          <t>RAFAEL PEZENTI</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>dep.pinheirinho@camara.leg.br</t>
+          <t>dep.pezenti@camara.leg.br</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>@pinheirinhomg</t>
+          <t>@deputadopezenti</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pinheirinhomg</t>
-        </is>
-      </c>
-      <c r="I408" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/deputadopezenti</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr"/>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/161440</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>73486</v>
+        <v>204524</v>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Pompeo de Mattos</t>
+          <t>Pinheirinho</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>DARCI POMPEO DE MATTOS</t>
+          <t>ANTÔNIO PINHEIRO NETO</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>dep.pompeodemattos@camara.leg.br</t>
+          <t>dep.pinheirinho@camara.leg.br</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>@pompeodemattospdt</t>
+          <t>@pinheirinhomg</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/pompeodemattospdt</t>
+          <t>https://instagram.com/pinheirinhomg</t>
         </is>
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/PompeodeMattos</t>
+          <t>https://youtube.com/channel/UCrsQcx5F8S_gHJTpfiE8FfA</t>
         </is>
       </c>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204524</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>160601</v>
+        <v>73486</v>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Pr. Marco Feliciano</t>
+          <t>Pompeo de Mattos</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>MARCO ANTÔNIO FELICIANO</t>
+          <t>DARCI POMPEO DE MATTOS</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>dep.pr.marcofeliciano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G410" s="2" t="inlineStr"/>
-      <c r="H410" s="2" t="inlineStr"/>
-      <c r="I410" s="2" t="inlineStr"/>
+          <t>dep.pompeodemattos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>@pompeodemattospdt</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pompeodemattospdt</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/PompeodeMattos</t>
+        </is>
+      </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73486</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>220533</v>
+        <v>160601</v>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Prof. Reginaldo Veras</t>
+          <t>Pr. Marco Feliciano</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Veras Coelho</t>
+          <t>MARCO ANTÔNIO FELICIANO</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>dep.prof.reginaldoveras@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G411" s="2" t="inlineStr">
-        <is>
-          <t>@reginaldo.veras</t>
-        </is>
-      </c>
-      <c r="H411" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/reginaldo.veras</t>
-        </is>
-      </c>
-      <c r="I411" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/Reginaldoveras12</t>
-        </is>
-      </c>
+          <t>dep.pr.marcofeliciano@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr"/>
+      <c r="H411" s="2" t="inlineStr"/>
+      <c r="I411" s="2" t="inlineStr"/>
       <c r="J411" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160601</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>204390</v>
+        <v>220533</v>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Professor Alcides</t>
+          <t>Prof. Reginaldo Veras</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>ALCIDES RIBEIRO FILHO</t>
+          <t>Reginaldo Veras Coelho</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralcides@camara.leg.br</t>
+          <t>dep.prof.reginaldoveras@camara.leg.br</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>@professoralcidesoficial</t>
+          <t>@reginaldo.veras</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/professoralcidesoficial</t>
+          <t>https://instagram.com/reginaldo.veras</t>
         </is>
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+          <t>https://youtube.com/Reginaldoveras12</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>221338</v>
+        <v>204390</v>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Professora Luciene Cavalcante</t>
+          <t>Professor Alcides</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>LUCIENE CAVALCANTE DA SILVA</t>
+          <t>ALCIDES RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralucienecavalcante@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G413" s="2" t="inlineStr"/>
-      <c r="H413" s="2" t="inlineStr"/>
-      <c r="I413" s="2" t="inlineStr"/>
+          <t>dep.professoralcides@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>@professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+        </is>
+      </c>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>160641</v>
+        <v>221338</v>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Professora Marcivania</t>
+          <t>Professora Luciene Cavalcante</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
+          <t>LUCIENE CAVALCANTE DA SILVA</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>dep.professoramarcivania@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>@profmarcivania</t>
-        </is>
-      </c>
-      <c r="H414" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/profmarcivania</t>
-        </is>
-      </c>
+          <t>dep.professoralucienecavalcante@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr"/>
+      <c r="H414" s="2" t="inlineStr"/>
       <c r="I414" s="2" t="inlineStr"/>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>220586</v>
+        <v>160641</v>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Rafael Brito</t>
+          <t>Professora Marcivania</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL DE GOES BRITO</t>
+          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelbrito@camara.leg.br</t>
+          <t>dep.professoramarcivania@camara.leg.br</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>@rafaelbrito15</t>
+          <t>@profmarcivania</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="I415" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
-        </is>
-      </c>
+          <t>https://instagram.com/profmarcivania</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr"/>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>233594</v>
+        <v>220586</v>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Rafael Fera</t>
+          <t>Rafael Brito</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL BENTO PEREIRA</t>
+          <t>RAFAEL DE GOES BRITO</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelfera@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G416" s="2" t="inlineStr"/>
-      <c r="H416" s="2" t="inlineStr"/>
-      <c r="I416" s="2" t="inlineStr"/>
+          <t>dep.rafaelbrito@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
+        </is>
+      </c>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>220532</v>
+        <v>233594</v>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Rafael Prudente</t>
+          <t>Rafael Fera</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL CAVALCANTI PRUDENTE</t>
+          <t>RAFAEL BENTO PEREIRA</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelprudente@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G417" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="H417" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="I417" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RafaelPrudente</t>
-        </is>
-      </c>
+          <t>dep.rafaelfera@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr"/>
+      <c r="H417" s="2" t="inlineStr"/>
+      <c r="I417" s="2" t="inlineStr"/>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>220626</v>
+        <v>220532</v>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Rafael Simoes</t>
+          <t>Rafael Prudente</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL TADEU SIMÕES</t>
+          <t>RAFAEL CAVALCANTI PRUDENTE</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelsimoes@camara.leg.br</t>
+          <t>dep.rafaelprudente@camara.leg.br</t>
         </is>
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>@rafaelsimoesmg</t>
+          <t>@rafaelprudentedep</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelsimoesmg</t>
-        </is>
-      </c>
-      <c r="I418" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RafaelPrudente</t>
+        </is>
+      </c>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>204567</v>
+        <v>220626</v>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Costa</t>
+          <t>Rafael Simoes</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO MAGALHÃES COSTA</t>
+          <t>RAFAEL TADEU SIMÕES</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundocosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G419" s="2" t="inlineStr"/>
-      <c r="H419" s="2" t="inlineStr"/>
+          <t>dep.rafaelsimoes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelsimoesmg</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelsimoesmg</t>
+        </is>
+      </c>
       <c r="I419" s="2" t="inlineStr"/>
       <c r="J419" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>74084</v>
+        <v>204567</v>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Santos</t>
+          <t>Raimundo Costa</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
+          <t>RAIMUNDO MAGALHÃES COSTA</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
@@ -18927,127 +18927,123 @@
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundosantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G420" s="2" t="inlineStr">
-        <is>
-          <t>@depraimundosantos</t>
-        </is>
-      </c>
-      <c r="H420" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depraimundosantos</t>
-        </is>
-      </c>
-      <c r="I420" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
-        </is>
-      </c>
+          <t>dep.raimundocosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr"/>
+      <c r="H420" s="2" t="inlineStr"/>
+      <c r="I420" s="2" t="inlineStr"/>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>115200</v>
+        <v>74084</v>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>Raniery Paulino</t>
+          <t>Raimundo Santos</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
+          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>dep.ranierypaulino@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G421" s="2" t="inlineStr"/>
-      <c r="H421" s="2" t="inlineStr"/>
-      <c r="I421" s="2" t="inlineStr"/>
+          <t>dep.raimundosantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>@depraimundosantos</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depraimundosantos</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
+        </is>
+      </c>
       <c r="J421" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>74161</v>
+        <v>115200</v>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Lopes</t>
+          <t>Raniery Paulino</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
+          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>dep.reginaldolopes@camara.leg.br</t>
+          <t>dep.ranierypaulino@camara.leg.br</t>
         </is>
       </c>
       <c r="G422" s="2" t="inlineStr"/>
       <c r="H422" s="2" t="inlineStr"/>
-      <c r="I422" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
-        </is>
-      </c>
+      <c r="I422" s="2" t="inlineStr"/>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>220606</v>
+        <v>74161</v>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>Reimont</t>
+          <t>Reginaldo Lopes</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
+          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
@@ -19057,50 +19053,54 @@
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>dep.reimont@camara.leg.br</t>
+          <t>dep.reginaldolopes@camara.leg.br</t>
         </is>
       </c>
       <c r="G423" s="2" t="inlineStr"/>
       <c r="H423" s="2" t="inlineStr"/>
-      <c r="I423" s="2" t="inlineStr"/>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
+        </is>
+      </c>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>178989</v>
+        <v>220606</v>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>Renata Abreu</t>
+          <t>Reimont</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>RENATA HELLMEISTER DE ABREU</t>
+          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>dep.renataabreu@camara.leg.br</t>
+          <t>dep.reimont@camara.leg.br</t>
         </is>
       </c>
       <c r="G424" s="2" t="inlineStr"/>
@@ -19108,7 +19108,7 @@
       <c r="I424" s="2" t="inlineStr"/>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178989</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -1191,21 +1191,9 @@
           <t>dep.alencarsantana@camara.leg.br</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>@AlencarBraga13</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/AlencarBraga13</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/AlencarBraga13</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204501</t>
@@ -20243,21 +20231,9 @@
           <t>dep.rosangelamoro@camara.leg.br</t>
         </is>
       </c>
-      <c r="G450" s="2" t="inlineStr">
-        <is>
-          <t>@rosangelawmoro</t>
-        </is>
-      </c>
-      <c r="H450" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rosangelawmoro</t>
-        </is>
-      </c>
-      <c r="I450" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC5X-86dz8GEf6QGMm95ZoAA</t>
-        </is>
-      </c>
+      <c r="G450" s="2" t="inlineStr"/>
+      <c r="H450" s="2" t="inlineStr"/>
+      <c r="I450" s="2" t="inlineStr"/>
       <c r="J450" s="2" t="inlineStr">
         <is>
           <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -20687,8 +20687,16 @@
           <t>dep.santinroveda@camara.leg.br</t>
         </is>
       </c>
-      <c r="G460" s="2" t="inlineStr"/>
-      <c r="H460" s="2" t="inlineStr"/>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>@santinroveda</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/santinroveda</t>
+        </is>
+      </c>
       <c r="I460" s="2" t="inlineStr"/>
       <c r="J460" s="2" t="inlineStr">
         <is>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -12052,7 +12052,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -8254,157 +8254,157 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>74454</v>
+        <v>204482</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Eunício Oliveira</t>
+          <t>Euclydes Pettersen</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>EUNÍCIO LOPES DE OLIVEIRA</t>
+          <t>EUCLYDES MARCOS PETTERSEN NETO</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>dep.euniciooliveira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>@euniciooliveira</t>
-        </is>
-      </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/euniciooliveira</t>
-        </is>
-      </c>
+          <t>dep.euclydespettersen@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr"/>
       <c r="I177" s="2" t="inlineStr"/>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74454</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204482</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>178871</v>
+        <v>74454</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Evair Vieira de Melo</t>
+          <t>Eunício Oliveira</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>EVAIR VIEIRA DE MELO</t>
+          <t>EUNÍCIO LOPES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>dep.evairvieirademelo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCT5EVLanh6IiCl01fzPSOBQ</t>
-        </is>
-      </c>
+          <t>dep.euniciooliveira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>@euniciooliveira</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/euniciooliveira</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178871</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74454</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>178905</v>
+        <v>178871</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Fabio Garcia</t>
+          <t>Evair Vieira de Melo</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>FABIO PAULINO GARCIA</t>
+          <t>EVAIR VIEIRA DE MELO</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>dep.fabiogarcia@camara.leg.br</t>
+          <t>dep.evairvieirademelo@camara.leg.br</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr"/>
-      <c r="I179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCT5EVLanh6IiCl01fzPSOBQ</t>
+        </is>
+      </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178905</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178871</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>220681</v>
+        <v>178905</v>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Fábio Macedo</t>
+          <t>Fabio Garcia</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>FÁBIO HENRIQUE DIAS DE  MACEDO</t>
+          <t>FABIO PAULINO GARCIA</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>dep.fabiomacedo@camara.leg.br</t>
+          <t>dep.fabiogarcia@camara.leg.br</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr"/>
@@ -8412,37 +8412,37 @@
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220681</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178905</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>171623</v>
+        <v>220681</v>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Fabio Reis</t>
+          <t>Fábio Macedo</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>FABIO DE ALMEIDA REIS</t>
+          <t>FÁBIO HENRIQUE DIAS DE  MACEDO</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>dep.fabioreis@camara.leg.br</t>
+          <t>dep.fabiomacedo@camara.leg.br</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr"/>
@@ -8450,37 +8450,37 @@
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171623</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220681</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>204368</v>
+        <v>171623</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Fabio Schiochet</t>
+          <t>Fabio Reis</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>FÁBIO LUIZ SCHIOCHET FILHO</t>
+          <t>FABIO DE ALMEIDA REIS</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>dep.fabioschiochet@camara.leg.br</t>
+          <t>dep.fabioreis@camara.leg.br</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
@@ -8488,110 +8488,110 @@
       <c r="I182" s="2" t="inlineStr"/>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204368</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/171623</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>220653</v>
+        <v>204368</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Fábio Teruel</t>
+          <t>Fabio Schiochet</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Fábio Eduardo de Oliveira Teruel</t>
+          <t>FÁBIO LUIZ SCHIOCHET FILHO</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>dep.fabioteruel@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="inlineStr">
-        <is>
-          <t>@fabioterueloficial</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/fabioterueloficial</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/FabioTeruelOficial</t>
-        </is>
-      </c>
+          <t>dep.fabioschiochet@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220653</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204368</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>220712</v>
+        <v>220653</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Fausto Jr.</t>
+          <t>Fábio Teruel</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>FAUSTO VIEIRA DOS SANTOS JUNIOR</t>
+          <t>Fábio Eduardo de Oliveira Teruel</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>dep.faustosantosjr@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr"/>
-      <c r="I184" s="2" t="inlineStr"/>
+          <t>dep.fabioteruel@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>@fabioterueloficial</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/fabioterueloficial</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/FabioTeruelOficial</t>
+        </is>
+      </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220712</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220653</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>66828</v>
+        <v>220712</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Fausto Pinato</t>
+          <t>Fausto Jr.</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>FAUSTO RUY PINATO</t>
+          <t>FAUSTO VIEIRA DOS SANTOS JUNIOR</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>dep.faustopinato@camara.leg.br</t>
+          <t>dep.faustosantosjr@camara.leg.br</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr"/>
@@ -8614,27 +8614,27 @@
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/66828</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220712</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>220646</v>
+        <v>66828</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Felipe Becari</t>
+          <t>Fausto Pinato</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>FELIPE BECARI COMENALE</t>
+          <t>FAUSTO RUY PINATO</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -8644,95 +8644,95 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>dep.felipebecari@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>@felipebecari</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/felipebecari</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel</t>
-        </is>
-      </c>
+          <t>dep.faustopinato@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr"/>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220646</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/66828</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>72442</v>
+        <v>220646</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Felipe Carreras</t>
+          <t>Felipe Becari</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>FELIPE AUGUSTO LYRA CARRERAS</t>
+          <t>FELIPE BECARI COMENALE</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>dep.felipecarreras@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr"/>
-      <c r="I187" s="2" t="inlineStr"/>
+          <t>dep.felipebecari@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>@felipebecari</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/felipebecari</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel</t>
+        </is>
+      </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/72442</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220646</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>204398</v>
+        <v>72442</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Felipe Francischini</t>
+          <t>Felipe Carreras</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>LUIS FELIPE BONATTO FRANCISCHINI</t>
+          <t>FELIPE AUGUSTO LYRA CARRERAS</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>dep.felipefrancischini@camara.leg.br</t>
+          <t>dep.felipecarreras@camara.leg.br</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
@@ -8740,121 +8740,121 @@
       <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204398</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/72442</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>160666</v>
+        <v>204398</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Félix Mendonça Júnior</t>
+          <t>Felipe Francischini</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>FELIX DE ALMEIDA MENDONÇA JÚNIOR</t>
+          <t>LUIS FELIPE BONATTO FRANCISCHINI</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>dep.felixmendoncajunior@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>@felixmendoncajr</t>
-        </is>
-      </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/felixmendoncajr</t>
-        </is>
-      </c>
+          <t>dep.felipefrancischini@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160666</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204398</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>204407</v>
+        <v>160666</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Fernanda Melchionna</t>
+          <t>Félix Mendonça Júnior</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>FERNANDA MELCHIONNA E SILVA</t>
+          <t>FELIX DE ALMEIDA MENDONÇA JÚNIOR</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PDT</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>dep.fernandamelchionna@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr"/>
+          <t>dep.felixmendoncajunior@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>@felixmendoncajr</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/felixmendoncajr</t>
+        </is>
+      </c>
       <c r="I190" s="2" t="inlineStr"/>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204407</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160666</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>220656</v>
+        <v>204407</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Fernanda Pessoa</t>
+          <t>Fernanda Melchionna</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>FERNANDA ENEIDA PESSOA CARACAS DE SOUZA</t>
+          <t>FERNANDA MELCHIONNA E SILVA</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>dep.fernandapessoa@camara.leg.br</t>
+          <t>dep.fernandamelchionna@camara.leg.br</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr"/>
@@ -8862,37 +8862,37 @@
       <c r="I191" s="2" t="inlineStr"/>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220656</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204407</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>141431</v>
+        <v>220656</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Fernando Coelho Filho</t>
+          <t>Fernanda Pessoa</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>FERNANDO BEZERRA DE SOUZA COELHO FILHO</t>
+          <t>FERNANDA ENEIDA PESSOA CARACAS DE SOUZA</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>dep.fernandocoelhofilho@camara.leg.br</t>
+          <t>dep.fernandapessoa@camara.leg.br</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr"/>
@@ -8900,111 +8900,111 @@
       <c r="I192" s="2" t="inlineStr"/>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141431</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220656</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>204445</v>
+        <v>141431</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Fernando Mineiro</t>
+          <t>Fernando Coelho Filho</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>FERNANDO WANDERLEY VARGAS DA SILVA</t>
+          <t>FERNANDO BEZERRA DE SOUZA COELHO FILHO</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>dep.fernandomineiro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G193" s="2" t="inlineStr">
-        <is>
-          <t>@mineiroptrn</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/mineiroptrn</t>
-        </is>
-      </c>
+          <t>dep.fernandocoelhofilho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204445</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141431</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>92699</v>
+        <v>204445</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Fernando Monteiro</t>
+          <t>Fernando Mineiro</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>FERNANDO MONTEIRO DE ALBUQUERQUE</t>
+          <t>FERNANDO WANDERLEY VARGAS DA SILVA</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>dep.fernandomonteiro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr"/>
+          <t>dep.fernandomineiro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>@mineiroptrn</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mineiroptrn</t>
+        </is>
+      </c>
       <c r="I194" s="2" t="inlineStr"/>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92699</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204445</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>204427</v>
+        <v>92699</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Fernando Rodolfo</t>
+          <t>Fernando Monteiro</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>FERNANDO RODOLFO TENORIO DE VASCONCELOS</t>
+          <t>FERNANDO MONTEIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>PRD</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -9014,84 +9014,76 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>dep.fernandorodolfo@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>@fernandorodolfooficial</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/fernandorodolfooficial</t>
-        </is>
-      </c>
+          <t>dep.fernandomonteiro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204427</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92699</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>204411</v>
+        <v>204427</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Filipe Barros</t>
+          <t>Fernando Rodolfo</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>FILIPE BARROS BAPTISTA DE TOLEDO RIBEIRO</t>
+          <t>FERNANDO RODOLFO TENORIO DE VASCONCELOS</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PRD</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>dep.filipebarros@camara.leg.br</t>
+          <t>dep.fernandorodolfo@camara.leg.br</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>@filipebarrosoficial</t>
+          <t>@fernandorodolfooficial</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/filipebarrosoficial</t>
+          <t>https://instagram.com/fernandorodolfooficial</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204411</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204427</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>220545</v>
+        <v>204411</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Filipe Martins</t>
+          <t>Filipe Barros</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>FILIPE MARTINS DOS SANTOS</t>
+          <t>FILIPE BARROS BAPTISTA DE TOLEDO RIBEIRO</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -9101,143 +9093,139 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>dep.filipemartins@camara.leg.br</t>
+          <t>dep.filipebarros@camara.leg.br</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>@filipemartinsto</t>
+          <t>@filipebarrosoficial</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/filipemartinsto</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/filipemartinsto</t>
-        </is>
-      </c>
+          <t>https://instagram.com/filipebarrosoficial</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220545</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204411</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>160598</v>
+        <v>220545</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Flávia Morais</t>
+          <t>Filipe Martins</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>FLÁVIA CARREIRO ALBUQUERQUE MORAIS</t>
+          <t>FILIPE MARTINS DOS SANTOS</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>dep.flaviamorais@camara.leg.br</t>
+          <t>dep.filipemartins@camara.leg.br</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>@flaviamorais1212</t>
+          <t>@filipemartinsto</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/flaviamorais1212</t>
-        </is>
-      </c>
-      <c r="I198" s="2" t="inlineStr"/>
+          <t>https://instagram.com/filipemartinsto</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/filipemartinsto</t>
+        </is>
+      </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160598</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220545</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>191923</v>
+        <v>160598</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Flávio Nogueira</t>
+          <t>Flávia Morais</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>FLÁVIO RODRIGUES NOGUEIRA</t>
+          <t>FLÁVIA CARREIRO ALBUQUERQUE MORAIS</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>dep.flavionogueira@camara.leg.br</t>
+          <t>dep.flaviamorais@camara.leg.br</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>@flavionogueirapi</t>
+          <t>@flaviamorais1212</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/flavionogueirapi</t>
-        </is>
-      </c>
-      <c r="I199" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCK5EmojEtDuJnbOAGHcWhiA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/flaviamorais1212</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/191923</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160598</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>220700</v>
+        <v>191923</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Florentino Neto</t>
+          <t>Flávio Nogueira</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>FLORENTINO ALVES VERAS NETO</t>
+          <t>FLÁVIO RODRIGUES NOGUEIRA</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -9252,45 +9240,57 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>dep.florentinoneto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr"/>
-      <c r="I200" s="2" t="inlineStr"/>
+          <t>dep.flavionogueira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>@flavionogueirapi</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/flavionogueirapi</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCK5EmojEtDuJnbOAGHcWhiA</t>
+        </is>
+      </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220700</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/191923</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>220551</v>
+        <v>220700</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Franciane Bayer</t>
+          <t>Florentino Neto</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>FRANCIANE ABADE BAYER MULLER</t>
+          <t>FLORENTINO ALVES VERAS NETO</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>dep.francianebayer@camara.leg.br</t>
+          <t>dep.florentinoneto@camara.leg.br</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr"/>
@@ -9298,171 +9298,171 @@
       <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220551</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220700</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>204494</v>
+        <v>220551</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Fred Costa</t>
+          <t>Franciane Bayer</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>FREDERICO BORGES DA COSTA</t>
+          <t>FRANCIANE ABADE BAYER MULLER</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>PRD</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>dep.fredcosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>@FredCostaDEP</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/FredCostaDEP</t>
-        </is>
-      </c>
+          <t>dep.francianebayer@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
       <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204494</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220551</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>220534</v>
+        <v>204494</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Fred Linhares</t>
+          <t>Fred Costa</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>DAVYS FREDERICO TEIXEIRA LINHARES</t>
+          <t>FREDERICO BORGES DA COSTA</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PRD</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>dep.fredlinhares@camara.leg.br</t>
+          <t>dep.fredcosta@camara.leg.br</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>@fredlinharesbrasilia</t>
+          <t>@FredCostaDEP</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/fredlinharesbrasilia</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@fredlinharesbrasilia/videos</t>
-        </is>
-      </c>
+          <t>https://instagram.com/FredCostaDEP</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220534</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204494</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>224117</v>
+        <v>220534</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Mota</t>
+          <t>Fred Linhares</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL MOTA E SILVA</t>
+          <t>DAVYS FREDERICO TEIXEIRA LINHARES</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>dep.gabrielmota@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr"/>
-      <c r="I204" s="2" t="inlineStr"/>
+          <t>dep.fredlinhares@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>@fredlinharesbrasilia</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/fredlinharesbrasilia</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@fredlinharesbrasilia/videos</t>
+        </is>
+      </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/224117</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220534</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>220708</v>
+        <v>224117</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Nunes</t>
+          <t>Gabriel Mota</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL JOSE MOURA NUNES SOARES</t>
+          <t>GABRIEL MOTA E SILVA</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>dep.gabrielnunes@camara.leg.br</t>
+          <t>dep.gabrielmota@camara.leg.br</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr"/>
@@ -9470,37 +9470,37 @@
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220708</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/224117</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>204473</v>
+        <v>220708</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>General Girão</t>
+          <t>Gabriel Nunes</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>ELIÉSER GIRÃO MONTEIRO FILHO</t>
+          <t>GABRIEL JOSE MOURA NUNES SOARES</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>dep.generalgirao@camara.leg.br</t>
+          <t>dep.gabrielnunes@camara.leg.br</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr"/>
@@ -9508,22 +9508,22 @@
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204473</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220708</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>220611</v>
+        <v>204473</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>General Pazuello</t>
+          <t>General Girão</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>EDUARDO PAZUELLO</t>
+          <t>ELIÉSER GIRÃO MONTEIRO FILHO</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>dep.generalpazuello@camara.leg.br</t>
+          <t>dep.generalgirao@camara.leg.br</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr"/>
@@ -9546,118 +9546,106 @@
       <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220611</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204473</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>178966</v>
+        <v>220611</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Geovania de Sá</t>
+          <t>General Pazuello</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Geovânia de Sá</t>
+          <t>EDUARDO PAZUELLO</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>dep.geovaniadesa@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>@geovaniasa</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/geovaniasa</t>
-        </is>
-      </c>
+          <t>dep.generalpazuello@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
       <c r="I208" s="2" t="inlineStr"/>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178966</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220611</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>220702</v>
+        <v>178966</v>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Geraldo Mendes</t>
+          <t>Geovania de Sá</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>GERALDO GABRIEL MENDES</t>
+          <t>Geovânia de Sá</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>dep.geraldomendes@camara.leg.br</t>
+          <t>dep.geovaniadesa@camara.leg.br</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>@geraldomendesoficial</t>
+          <t>@geovaniasa</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/geraldomendesoficial</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@geraldomendes3450</t>
-        </is>
-      </c>
+          <t>https://instagram.com/geovaniasa</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr"/>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220702</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178966</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>74374</v>
+        <v>220702</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Geraldo Resende</t>
+          <t>Geraldo Mendes</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>GERALDO RESENDE PEREIRA</t>
+          <t>GERALDO GABRIEL MENDES</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -9667,177 +9655,189 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>dep.geraldoresende@camara.leg.br</t>
+          <t>dep.geraldomendes@camara.leg.br</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>@geraldoresendems</t>
+          <t>@geraldomendesoficial</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/geraldoresendems</t>
+          <t>https://instagram.com/geraldomendesoficial</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCbnj5-ROiu04qLttEG6HNmQ</t>
+          <t>https://www.youtube.com/@geraldomendes3450</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74374</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220702</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>204394</v>
+        <v>74374</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Gervásio Maia</t>
+          <t>Geraldo Resende</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>GERVÁSIO AGRIPINO MAIA</t>
+          <t>GERALDO RESENDE PEREIRA</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>dep.gervasiomaia@camara.leg.br</t>
+          <t>dep.geraldoresende@camara.leg.br</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>@gervasiomaia</t>
+          <t>@geraldoresendems</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gervasiomaia</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr"/>
+          <t>https://instagram.com/geraldoresendems</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCbnj5-ROiu04qLttEG6HNmQ</t>
+        </is>
+      </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204394</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74374</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>204491</v>
+        <v>204394</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Gilberto Abramo</t>
+          <t>Gervásio Maia</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>GILBERTO APARECIDO ABRAMO</t>
+          <t>GERVÁSIO AGRIPINO MAIA</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>dep.gilbertoabramo@camara.leg.br</t>
+          <t>dep.gervasiomaia@camara.leg.br</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>@gilbertoabramo_</t>
+          <t>@gervasiomaia</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gilbertoabramo_</t>
+          <t>https://instagram.com/gervasiomaia</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204491</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204394</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>74270</v>
+        <v>204491</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Gilberto Nascimento</t>
+          <t>Gilberto Abramo</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>GILBERTO NASCIMENTO SILVA</t>
+          <t>GILBERTO APARECIDO ABRAMO</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>dep.gilbertonascimento@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr"/>
+          <t>dep.gilbertoabramo@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>@gilbertoabramo_</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/gilbertoabramo_</t>
+        </is>
+      </c>
       <c r="I213" s="2" t="inlineStr"/>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74270</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204491</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>220529</v>
+        <v>74270</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Gilson Daniel</t>
+          <t>Gilberto Nascimento</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>GILSON DANIEL BATISTA</t>
+          <t>GILBERTO NASCIMENTO SILVA</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9847,139 +9847,131 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>dep.gilsondaniel@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>@gilsondaniel1919</t>
-        </is>
-      </c>
-      <c r="H214" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/gilsondaniel1919</t>
-        </is>
-      </c>
+          <t>dep.gilbertonascimento@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
       <c r="I214" s="2" t="inlineStr"/>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220529</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74270</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>204365</v>
+        <v>220529</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Gilson Marques</t>
+          <t>Gilson Daniel</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>GILSON MARQUES VIEIRA</t>
+          <t>GILSON DANIEL BATISTA</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>dep.gilsonmarques@camara.leg.br</t>
+          <t>dep.gilsondaniel@camara.leg.br</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>@gilson.marques.novo</t>
+          <t>@gilsondaniel1919</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gilson.marques.novo</t>
-        </is>
-      </c>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/gilsonmarquesnovo</t>
-        </is>
-      </c>
+          <t>https://instagram.com/gilsondaniel1919</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr"/>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204365</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220529</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>220526</v>
+        <v>204365</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Gilvan da Federal</t>
+          <t>Gilson Marques</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>GILVAN AGUIAR COSTA</t>
+          <t>GILSON MARQUES VIEIRA</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>dep.gilvandafederal@camara.leg.br</t>
+          <t>dep.gilsonmarques@camara.leg.br</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>@gilvandafederal</t>
+          <t>@gilson.marques.novo</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gilvandafederal</t>
-        </is>
-      </c>
-      <c r="I216" s="2" t="inlineStr"/>
+          <t>https://instagram.com/gilson.marques.novo</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/gilsonmarquesnovo</t>
+        </is>
+      </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220526</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204365</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>160673</v>
+        <v>220526</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Giovani Cherini</t>
+          <t>Gilvan da Federal</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>GIOVANI CHERINI</t>
+          <t>GILVAN AGUIAR COSTA</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9989,50 +9981,58 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>dep.giovanicherini@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr"/>
+          <t>dep.gilvandafederal@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>@gilvandafederal</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/gilvandafederal</t>
+        </is>
+      </c>
       <c r="I217" s="2" t="inlineStr"/>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160673</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220526</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>152605</v>
+        <v>160673</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Glauber Braga</t>
+          <t>Giovani Cherini</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>GLAUBER DE MEDEIROS BRAGA</t>
+          <t>GIOVANI CHERINI</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>dep.glauberbraga@camara.leg.br</t>
+          <t>dep.giovanicherini@camara.leg.br</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr"/>
@@ -10040,37 +10040,37 @@
       <c r="I218" s="2" t="inlineStr"/>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/152605</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160673</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>204419</v>
+        <v>152605</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Glaustin da Fokus</t>
+          <t>Glauber Braga</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>GLAUSKSTON BATISTA RIOS</t>
+          <t>GLAUBER DE MEDEIROS BRAGA</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>dep.glaustindafokus@camara.leg.br</t>
+          <t>dep.glauberbraga@camara.leg.br</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr"/>
@@ -10078,37 +10078,37 @@
       <c r="I219" s="2" t="inlineStr"/>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204419</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/152605</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>236284</v>
+        <v>204419</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Glaycon Franco</t>
+          <t>Glaustin da Fokus</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>GLYCON MOREIRA FRANCO</t>
+          <t>GLAUSKSTON BATISTA RIOS</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>dep.glayconfranco@camara.leg.br</t>
+          <t>dep.glaustindafokus@camara.leg.br</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr"/>
@@ -10116,321 +10116,321 @@
       <c r="I220" s="2" t="inlineStr"/>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236284</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204419</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>107283</v>
+        <v>236284</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Gleisi Hoffmann</t>
+          <t>Glaycon Franco</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>GLEISI HELENA HOFFMANN</t>
+          <t>GLYCON MOREIRA FRANCO</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>dep.gleisihoffmann@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t>@gleisihoffmann</t>
-        </is>
-      </c>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/gleisihoffmann</t>
-        </is>
-      </c>
-      <c r="I221" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/GleisiHoffmannPT</t>
-        </is>
-      </c>
+          <t>dep.glayconfranco@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr"/>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/107283</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236284</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>198197</v>
+        <v>107283</v>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Greyce Elias</t>
+          <t>Gleisi Hoffmann</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>GREYCE DE QUEIROZ ELIAS</t>
+          <t>GLEISI HELENA HOFFMANN</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>dep.greyceelias@camara.leg.br</t>
+          <t>dep.gleisihoffmann@camara.leg.br</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>@greyceelias</t>
+          <t>@gleisihoffmann</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/greyceelias</t>
+          <t>https://instagram.com/gleisihoffmann</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCcSZxLiSfO1dFmAryUnxPHg</t>
+          <t>https://youtube.com/GleisiHoffmannPT</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/198197</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/107283</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>204531</v>
+        <v>198197</v>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Derrite</t>
+          <t>Greyce Elias</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>GUILHERME MURARO DERRITE</t>
+          <t>GREYCE DE QUEIROZ ELIAS</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>dep.guilhermederrite@camara.leg.br</t>
+          <t>dep.greyceelias@camara.leg.br</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>@capitaoderrite</t>
+          <t>@greyceelias</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/capitaoderrite</t>
+          <t>https://instagram.com/greyceelias</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCZHZxgmwC2c5tz3_Jn-gGOw</t>
+          <t>https://youtube.com/channel/UCcSZxLiSfO1dFmAryUnxPHg</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204531</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/198197</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>220664</v>
+        <v>204531</v>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Guilherme Uchoa</t>
+          <t>Guilherme Derrite</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>GUILHERME A. UCHOA CAVALCANTI PESSOA DE MELO JUNIOR</t>
+          <t>GUILHERME MURARO DERRITE</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>dep.guilhermeuchoa@camara.leg.br</t>
+          <t>dep.guilhermederrite@camara.leg.br</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>@GUILHERMEUCHOAJR</t>
+          <t>@capitaoderrite</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/GUILHERMEUCHOAJR</t>
-        </is>
-      </c>
-      <c r="I224" s="2" t="inlineStr"/>
+          <t>https://instagram.com/capitaoderrite</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCZHZxgmwC2c5tz3_Jn-gGOw</t>
+        </is>
+      </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220664</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204531</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>220568</v>
+        <v>220664</v>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Gayer</t>
+          <t>Guilherme Uchoa</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>GUSTAVO GAYER MACHADO DE ARAUJO</t>
+          <t>GUILHERME A. UCHOA CAVALCANTI PESSOA DE MELO JUNIOR</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>dep.gustavogayer@camara.leg.br</t>
+          <t>dep.guilhermeuchoa@camara.leg.br</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>@gusgayer</t>
+          <t>@GUILHERMEUCHOAJR</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/gusgayer</t>
-        </is>
-      </c>
-      <c r="I225" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/GustavoGayer</t>
-        </is>
-      </c>
+          <t>https://instagram.com/GUILHERMEUCHOAJR</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr"/>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220568</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220664</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>204408</v>
+        <v>220568</v>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Gustinho Ribeiro</t>
+          <t>Gustavo Gayer</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>LUIZ AUGUSTO CARVALHO RIBEIRO FILHO</t>
+          <t>GUSTAVO GAYER MACHADO DE ARAUJO</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>dep.gustinhoribeiro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr"/>
-      <c r="I226" s="2" t="inlineStr"/>
+          <t>dep.gustavogayer@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>@gusgayer</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/gusgayer</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/GustavoGayer</t>
+        </is>
+      </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204408</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220568</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>204456</v>
+        <v>204408</v>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Gutemberg Reis</t>
+          <t>Gustinho Ribeiro</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>GUTEMBERG REIS DE OLIVEIRA</t>
+          <t>LUIZ AUGUSTO CARVALHO RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>dep.gutembergreis@camara.leg.br</t>
+          <t>dep.gustinhoribeiro@camara.leg.br</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr"/>
@@ -10438,370 +10438,370 @@
       <c r="I227" s="2" t="inlineStr"/>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204456</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204408</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>178964</v>
+        <v>204456</v>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Heitor Schuch</t>
+          <t>Gutemberg Reis</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>HEITOR JOSE SCHUCH</t>
+          <t>GUTEMBERG REIS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>dep.heitorschuch@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>@heitorschuch</t>
-        </is>
-      </c>
-      <c r="H228" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/heitorschuch</t>
-        </is>
-      </c>
+          <t>dep.gutembergreis@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr"/>
       <c r="I228" s="2" t="inlineStr"/>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178964</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204456</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>178873</v>
+        <v>178964</v>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Helder Salomão</t>
+          <t>Heitor Schuch</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>HELDER IGNACIO SALOMAO</t>
+          <t>HEITOR JOSE SCHUCH</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>dep.heldersalomao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr"/>
+          <t>dep.heitorschuch@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>@heitorschuch</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/heitorschuch</t>
+        </is>
+      </c>
       <c r="I229" s="2" t="inlineStr"/>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178873</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178964</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>220537</v>
+        <v>178873</v>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Helena Lima</t>
+          <t>Helder Salomão</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>MARIA HELENA TEIXEIRA LIMA</t>
+          <t>HELDER IGNACIO SALOMAO</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>dep.helenalima@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>@helenadaasatur</t>
-        </is>
-      </c>
-      <c r="H230" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/helenadaasatur</t>
-        </is>
-      </c>
+          <t>dep.heldersalomao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
       <c r="I230" s="2" t="inlineStr"/>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220537</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178873</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>204444</v>
+        <v>220537</v>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Helio Lopes</t>
+          <t>Helena Lima</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>HELIO FERNANDO BARBOSA LOPES</t>
+          <t>MARIA HELENA TEIXEIRA LIMA</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>dep.heliolopes@camara.leg.br</t>
+          <t>dep.helenalima@camara.leg.br</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>@depheliolopes</t>
+          <t>@helenadaasatur</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/depheliolopes</t>
+          <t>https://instagram.com/helenadaasatur</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204444</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220537</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>220672</v>
+        <v>204444</v>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Henderson Pinto</t>
+          <t>Helio Lopes</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>HENDERSON LIRA PINTO</t>
+          <t>HELIO FERNANDO BARBOSA LOPES</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>dep.hendersonpinto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr"/>
+          <t>dep.heliolopes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>@depheliolopes</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depheliolopes</t>
+        </is>
+      </c>
       <c r="I232" s="2" t="inlineStr"/>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220672</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204444</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>204539</v>
+        <v>220672</v>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Hercílio Coelho Diniz</t>
+          <t>Henderson Pinto</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>HERCÍLIO ARAÚJO DINIZ FILHO</t>
+          <t>HENDERSON LIRA PINTO</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>dep.herciliocoelhodiniz@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>@herciliocoelhodinizoficial</t>
-        </is>
-      </c>
-      <c r="H233" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/herciliocoelhodinizoficial</t>
-        </is>
-      </c>
-      <c r="I233" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/HercílioCoelhoDinizOficial</t>
-        </is>
-      </c>
+          <t>dep.hendersonpinto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
+      <c r="I233" s="2" t="inlineStr"/>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204539</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220672</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>141450</v>
+        <v>204539</v>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Hugo Leal</t>
+          <t>Hercílio Coelho Diniz</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>HUGO LEAL MELO DA SILVA</t>
+          <t>HERCÍLIO ARAÚJO DINIZ FILHO</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>dep.hugoleal@camara.leg.br</t>
+          <t>dep.herciliocoelhodiniz@camara.leg.br</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>@dephugoleal</t>
+          <t>@herciliocoelhodinizoficial</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/dephugoleal</t>
-        </is>
-      </c>
-      <c r="I234" s="2" t="inlineStr"/>
+          <t>https://instagram.com/herciliocoelhodinizoficial</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/HercílioCoelhoDinizOficial</t>
+        </is>
+      </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141450</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204539</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>160674</v>
+        <v>141450</v>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Hugo Motta</t>
+          <t>Hugo Leal</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>HUGO MOTTA WANDERLEY DA NÓBREGA</t>
+          <t>HUGO LEAL MELO DA SILVA</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>dep.hugomotta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr"/>
+          <t>dep.hugoleal@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>@dephugoleal</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dephugoleal</t>
+        </is>
+      </c>
       <c r="I235" s="2" t="inlineStr"/>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160674</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141450</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>220563</v>
+        <v>160674</v>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Icaro de Valmir</t>
+          <t>Hugo Motta</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>ICARO BARBOSA COSTA</t>
+          <t>HUGO MOTTA WANDERLEY DA NÓBREGA</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -10811,140 +10811,132 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>dep.icarodevalmir@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G236" s="2" t="inlineStr">
-        <is>
-          <t>@icarodevalmir</t>
-        </is>
-      </c>
-      <c r="H236" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/icarodevalmir</t>
-        </is>
-      </c>
+          <t>dep.hugomotta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr"/>
       <c r="I236" s="2" t="inlineStr"/>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220563</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160674</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>204533</v>
+        <v>220563</v>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Idilvan Alencar</t>
+          <t>Icaro de Valmir</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO IDILVAN DE LIMA ALENCAR</t>
+          <t>ICARO BARBOSA COSTA</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>dep.idilvanalencar@camara.leg.br</t>
+          <t>dep.icarodevalmir@camara.leg.br</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>@idilvanalencar</t>
+          <t>@icarodevalmir</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/idilvanalencar</t>
+          <t>https://instagram.com/icarodevalmir</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220563</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>204508</v>
+        <v>204533</v>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Igor Timo</t>
+          <t>Idilvan Alencar</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>IGOR TARCIANO TIMO</t>
+          <t>ANTONIO IDILVAN DE LIMA ALENCAR</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>dep.igortimo@camara.leg.br</t>
+          <t>dep.idilvanalencar@camara.leg.br</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>@oficialigortimo</t>
+          <t>@idilvanalencar</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/oficialigortimo</t>
+          <t>https://instagram.com/idilvanalencar</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr"/>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204508</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204533</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>235620</v>
+        <v>204508</v>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Ilacir Bicalho</t>
+          <t>Igor Timo</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>ILACIR BICALHO DE BARROS</t>
+          <t>IGOR TARCIANO TIMO</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -10954,15 +10946,23 @@
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>dep.ilacirbicalho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr"/>
+          <t>dep.igortimo@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>@oficialigortimo</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/oficialigortimo</t>
+        </is>
+      </c>
       <c r="I239" s="2" t="inlineStr"/>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/235620</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204508</t>
         </is>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J516"/>
+  <dimension ref="A1:J517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18582,422 +18582,430 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>220533</v>
+        <v>226075</v>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Prof. Reginaldo Veras</t>
+          <t>Priscila Costa</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Veras Coelho</t>
+          <t>PRISCILA BEZERRA DA COSTA</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>dep.prof.reginaldoveras@camara.leg.br</t>
+          <t>dep.priscilacosta@camara.leg.br</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>@reginaldo.veras</t>
+          <t>@priscilacosta</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/reginaldo.veras</t>
-        </is>
-      </c>
-      <c r="I413" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/Reginaldoveras12</t>
-        </is>
-      </c>
+          <t>https://instagram.com/priscilacosta</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr"/>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226075</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>204390</v>
+        <v>220533</v>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Professor Alcides</t>
+          <t>Prof. Reginaldo Veras</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>ALCIDES RIBEIRO FILHO</t>
+          <t>Reginaldo Veras Coelho</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralcides@camara.leg.br</t>
+          <t>dep.prof.reginaldoveras@camara.leg.br</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>@professoralcidesoficial</t>
+          <t>@reginaldo.veras</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/professoralcidesoficial</t>
+          <t>https://instagram.com/reginaldo.veras</t>
         </is>
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+          <t>https://youtube.com/Reginaldoveras12</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220533</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>221338</v>
+        <v>204390</v>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Professora Luciene Cavalcante</t>
+          <t>Professor Alcides</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>LUCIENE CAVALCANTE DA SILVA</t>
+          <t>ALCIDES RIBEIRO FILHO</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>dep.professoralucienecavalcante@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G415" s="2" t="inlineStr"/>
-      <c r="H415" s="2" t="inlineStr"/>
-      <c r="I415" s="2" t="inlineStr"/>
+          <t>dep.professoralcides@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>@professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/professoralcidesoficial</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/DeputadoProfessorAlcides</t>
+        </is>
+      </c>
       <c r="J415" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204390</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>160641</v>
+        <v>221338</v>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Professora Marcivania</t>
+          <t>Professora Luciene Cavalcante</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
+          <t>LUCIENE CAVALCANTE DA SILVA</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>dep.professoramarcivania@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G416" s="2" t="inlineStr">
-        <is>
-          <t>@profmarcivania</t>
-        </is>
-      </c>
-      <c r="H416" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/profmarcivania</t>
-        </is>
-      </c>
+          <t>dep.professoralucienecavalcante@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr"/>
+      <c r="H416" s="2" t="inlineStr"/>
       <c r="I416" s="2" t="inlineStr"/>
       <c r="J416" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221338</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>220586</v>
+        <v>160641</v>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Rafael Brito</t>
+          <t>Professora Marcivania</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL DE GOES BRITO</t>
+          <t>MARCIVANIA DO SOCORRO DA ROCHA FLEXA</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelbrito@camara.leg.br</t>
+          <t>dep.professoramarcivania@camara.leg.br</t>
         </is>
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>@rafaelbrito15</t>
+          <t>@profmarcivania</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelbrito15</t>
-        </is>
-      </c>
-      <c r="I417" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
-        </is>
-      </c>
+          <t>https://instagram.com/profmarcivania</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr"/>
       <c r="J417" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160641</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>233594</v>
+        <v>220586</v>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Rafael Fera</t>
+          <t>Rafael Brito</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL BENTO PEREIRA</t>
+          <t>RAFAEL DE GOES BRITO</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelfera@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G418" s="2" t="inlineStr"/>
-      <c r="H418" s="2" t="inlineStr"/>
-      <c r="I418" s="2" t="inlineStr"/>
+          <t>dep.rafaelbrito@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelbrito15</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCq3xwtJvyjdU-ceUhWg-lPg</t>
+        </is>
+      </c>
       <c r="J418" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220586</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>220532</v>
+        <v>233594</v>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Rafael Prudente</t>
+          <t>Rafael Fera</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL CAVALCANTI PRUDENTE</t>
+          <t>RAFAEL BENTO PEREIRA</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelprudente@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G419" s="2" t="inlineStr">
-        <is>
-          <t>@rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="H419" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rafaelprudentedep</t>
-        </is>
-      </c>
-      <c r="I419" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RafaelPrudente</t>
-        </is>
-      </c>
+          <t>dep.rafaelfera@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr"/>
+      <c r="H419" s="2" t="inlineStr"/>
+      <c r="I419" s="2" t="inlineStr"/>
       <c r="J419" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/233594</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>220626</v>
+        <v>220532</v>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>Rafael Simoes</t>
+          <t>Rafael Prudente</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL TADEU SIMÕES</t>
+          <t>RAFAEL CAVALCANTI PRUDENTE</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>dep.rafaelsimoes@camara.leg.br</t>
+          <t>dep.rafaelprudente@camara.leg.br</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>@rafaelsimoesmg</t>
+          <t>@rafaelprudentedep</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rafaelsimoesmg</t>
-        </is>
-      </c>
-      <c r="I420" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rafaelprudentedep</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RafaelPrudente</t>
+        </is>
+      </c>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220532</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>204567</v>
+        <v>220626</v>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Costa</t>
+          <t>Rafael Simoes</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO MAGALHÃES COSTA</t>
+          <t>RAFAEL TADEU SIMÕES</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundocosta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G421" s="2" t="inlineStr"/>
-      <c r="H421" s="2" t="inlineStr"/>
+          <t>dep.rafaelsimoes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>@rafaelsimoesmg</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rafaelsimoesmg</t>
+        </is>
+      </c>
       <c r="I421" s="2" t="inlineStr"/>
       <c r="J421" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220626</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>74084</v>
+        <v>204567</v>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>Raimundo Santos</t>
+          <t>Raimundo Costa</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
+          <t>RAIMUNDO MAGALHÃES COSTA</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -19007,127 +19015,123 @@
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>dep.raimundosantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G422" s="2" t="inlineStr">
-        <is>
-          <t>@depraimundosantos</t>
-        </is>
-      </c>
-      <c r="H422" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depraimundosantos</t>
-        </is>
-      </c>
-      <c r="I422" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
-        </is>
-      </c>
+          <t>dep.raimundocosta@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr"/>
+      <c r="H422" s="2" t="inlineStr"/>
+      <c r="I422" s="2" t="inlineStr"/>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204567</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>115200</v>
+        <v>74084</v>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>Raniery Paulino</t>
+          <t>Raimundo Santos</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
+          <t>RAIMUNDO JOSÉ PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>dep.ranierypaulino@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G423" s="2" t="inlineStr"/>
-      <c r="H423" s="2" t="inlineStr"/>
-      <c r="I423" s="2" t="inlineStr"/>
+          <t>dep.raimundosantos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>@depraimundosantos</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depraimundosantos</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCDl2RREU083fkW3AR1PC3OQ</t>
+        </is>
+      </c>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74084</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>74161</v>
+        <v>115200</v>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>Reginaldo Lopes</t>
+          <t>Raniery Paulino</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
+          <t>ROBERTO RANIERY DE AQUINO PAULINO</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>dep.reginaldolopes@camara.leg.br</t>
+          <t>dep.ranierypaulino@camara.leg.br</t>
         </is>
       </c>
       <c r="G424" s="2" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr"/>
-      <c r="I424" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
-        </is>
-      </c>
+      <c r="I424" s="2" t="inlineStr"/>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/115200</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>220606</v>
+        <v>74161</v>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>Reimont</t>
+          <t>Reginaldo Lopes</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
+          <t>REGINALDO LÁZARO DE OLIVEIRA LOPES</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
@@ -19137,612 +19141,616 @@
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>dep.reimont@camara.leg.br</t>
+          <t>dep.reginaldolopes@camara.leg.br</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr"/>
       <c r="H425" s="2" t="inlineStr"/>
-      <c r="I425" s="2" t="inlineStr"/>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCKrXcydte7lEBDWVoogEptw</t>
+        </is>
+      </c>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74161</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>153423</v>
+        <v>220606</v>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>Renilce Nicodemos</t>
+          <t>Reimont</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
+          <t>REIMONT LUIZ OTONI SANTA BARBARA</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>dep.renilcenicodemos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G426" s="2" t="inlineStr">
-        <is>
-          <t>@renilcenicodemoss</t>
-        </is>
-      </c>
-      <c r="H426" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/renilcenicodemoss</t>
-        </is>
-      </c>
+          <t>dep.reimont@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr"/>
+      <c r="H426" s="2" t="inlineStr"/>
       <c r="I426" s="2" t="inlineStr"/>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220606</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>73801</v>
+        <v>153423</v>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>Renildo Calheiros</t>
+          <t>Renilce Nicodemos</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>RENILDO VASCONCELOS CALHEIROS</t>
+          <t>RENILCE CONCEIÇÃO NICODEMOS DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>PCdoB</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>dep.renildocalheiros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G427" s="2" t="inlineStr"/>
-      <c r="H427" s="2" t="inlineStr"/>
+          <t>dep.renilcenicodemos@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>@renilcenicodemoss</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/renilcenicodemoss</t>
+        </is>
+      </c>
       <c r="I427" s="2" t="inlineStr"/>
       <c r="J427" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/153423</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>175765</v>
+        <v>73801</v>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>Ribamar Silva</t>
+          <t>Renildo Calheiros</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>RIBAMAR ANTONIO DA SILVA</t>
+          <t>RENILDO VASCONCELOS CALHEIROS</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PCdoB</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>dep.ribamarsilva@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G428" s="2" t="inlineStr">
-        <is>
-          <t>@ribamarsilvaoficial</t>
-        </is>
-      </c>
-      <c r="H428" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ribamarsilvaoficial</t>
-        </is>
-      </c>
+          <t>dep.renildocalheiros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr"/>
+      <c r="H428" s="2" t="inlineStr"/>
       <c r="I428" s="2" t="inlineStr"/>
       <c r="J428" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73801</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>221329</v>
+        <v>175765</v>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Abrão</t>
+          <t>Ribamar Silva</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MARTINS DAVID</t>
+          <t>RIBAMAR ANTONIO DA SILVA</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoabrao@camara.leg.br</t>
+          <t>dep.ribamarsilva@camara.leg.br</t>
         </is>
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>@ricardoabraooficial</t>
+          <t>@ribamarsilvaoficial</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardoabraooficial</t>
+          <t>https://instagram.com/ribamarsilvaoficial</t>
         </is>
       </c>
       <c r="I429" s="2" t="inlineStr"/>
       <c r="J429" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/175765</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>220543</v>
+        <v>221329</v>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Ayres</t>
+          <t>Ricardo Abrão</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>RICARDO AYRES DE CARVALHO</t>
+          <t>RICARDO MARTINS DAVID</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoayres@camara.leg.br</t>
+          <t>dep.ricardoabrao@camara.leg.br</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>@ricardoayres_to</t>
+          <t>@ricardoabraooficial</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardoayres_to</t>
+          <t>https://instagram.com/ricardoabraooficial</t>
         </is>
       </c>
       <c r="I430" s="2" t="inlineStr"/>
       <c r="J430" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/221329</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>73788</v>
+        <v>220543</v>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Barros</t>
+          <t>Ricardo Ayres</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
+          <t>RICARDO AYRES DE CARVALHO</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardobarros@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G431" s="2" t="inlineStr"/>
-      <c r="H431" s="2" t="inlineStr"/>
+          <t>dep.ricardoayres@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>@ricardoayres_to</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ricardoayres_to</t>
+        </is>
+      </c>
       <c r="I431" s="2" t="inlineStr"/>
       <c r="J431" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220543</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>204362</v>
+        <v>73788</v>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Guidi</t>
+          <t>Ricardo Barros</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>RICARDO ZANATTA GUIDI</t>
+          <t>RICARDO JOSÉ MAGALHÃES BARROS</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardoguidi@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G432" s="2" t="inlineStr">
-        <is>
-          <t>@ricardozguidi</t>
-        </is>
-      </c>
-      <c r="H432" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/ricardozguidi</t>
-        </is>
-      </c>
+          <t>dep.ricardobarros@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr"/>
+      <c r="H432" s="2" t="inlineStr"/>
       <c r="I432" s="2" t="inlineStr"/>
       <c r="J432" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73788</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>220694</v>
+        <v>204362</v>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Maia</t>
+          <t>Ricardo Guidi</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>RICARDO MAIA CHAVES DE SOUZA</t>
+          <t>RICARDO ZANATTA GUIDI</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardomaia@camara.leg.br</t>
+          <t>dep.ricardoguidi@camara.leg.br</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr">
         <is>
-          <t>@ricardomaia.dabahia</t>
+          <t>@ricardozguidi</t>
         </is>
       </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ricardomaia.dabahia</t>
-        </is>
-      </c>
-      <c r="I433" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/ricardomaiadabahia5610</t>
-        </is>
-      </c>
+          <t>https://instagram.com/ricardozguidi</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr"/>
       <c r="J433" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204362</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>220633</v>
+        <v>220694</v>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Salles</t>
+          <t>Ricardo Maia</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>RICARDO DE AQUINO SALLES</t>
+          <t>RICARDO MAIA CHAVES DE SOUZA</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>dep.ricardosalles@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G434" s="2" t="inlineStr"/>
-      <c r="H434" s="2" t="inlineStr"/>
-      <c r="I434" s="2" t="inlineStr"/>
+          <t>dep.ricardomaia@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>@ricardomaia.dabahia</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ricardomaia.dabahia</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/ricardomaiadabahia5610</t>
+        </is>
+      </c>
       <c r="J434" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220694</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>204489</v>
+        <v>220633</v>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>Robério Monteiro</t>
+          <t>Ricardo Salles</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
+          <t>RICARDO DE AQUINO SALLES</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>NOVO</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>dep.roberiomonteiro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G435" s="2" t="inlineStr">
-        <is>
-          <t>@dep.roberiomonteiro</t>
-        </is>
-      </c>
-      <c r="H435" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/dep.roberiomonteiro</t>
-        </is>
-      </c>
+          <t>dep.ricardosalles@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr"/>
+      <c r="H435" s="2" t="inlineStr"/>
       <c r="I435" s="2" t="inlineStr"/>
       <c r="J435" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220633</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>220693</v>
+        <v>204489</v>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>Roberta Roma</t>
+          <t>Robério Monteiro</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Roberta de Araujo Costa Roma</t>
+          <t>MARCOS ROBERIO RIBEIRO MONTEIRO</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>dep.robertaroma@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G436" s="2" t="inlineStr"/>
-      <c r="H436" s="2" t="inlineStr"/>
+          <t>dep.roberiomonteiro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>@dep.roberiomonteiro</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dep.roberiomonteiro</t>
+        </is>
+      </c>
       <c r="I436" s="2" t="inlineStr"/>
       <c r="J436" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204489</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>220588</v>
+        <v>220693</v>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>Roberto Duarte</t>
+          <t>Roberta Roma</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO DUARTE JUNIOR</t>
+          <t>Roberta de Araujo Costa Roma</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>dep.robertoduarte@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G437" s="2" t="inlineStr">
-        <is>
-          <t>@rdnarede</t>
-        </is>
-      </c>
-      <c r="H437" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rdnarede</t>
-        </is>
-      </c>
+          <t>dep.robertaroma@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr"/>
+      <c r="H437" s="2" t="inlineStr"/>
       <c r="I437" s="2" t="inlineStr"/>
       <c r="J437" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220693</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>220613</v>
+        <v>220588</v>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>Roberto Monteiro Pai</t>
+          <t>Roberto Duarte</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
+          <t>ROBERTO DUARTE JUNIOR</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>dep.robertomonteiropai@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr"/>
-      <c r="H438" s="2" t="inlineStr"/>
+          <t>dep.robertoduarte@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>@rdnarede</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rdnarede</t>
+        </is>
+      </c>
       <c r="I438" s="2" t="inlineStr"/>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220588</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>220624</v>
+        <v>220613</v>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>Robinson Faria</t>
+          <t>Roberto Monteiro Pai</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>ROBINSON MESQUITA DE FARIA</t>
+          <t>ROBERTO LUIZ RODRIGUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>dep.robinsonfaria@camara.leg.br</t>
+          <t>dep.robertomonteiropai@camara.leg.br</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr"/>
@@ -19750,72 +19758,60 @@
       <c r="I439" s="2" t="inlineStr"/>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220613</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>220546</v>
+        <v>220624</v>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>Rodolfo Nogueira</t>
+          <t>Robinson Faria</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
+          <t>ROBINSON MESQUITA DE FARIA</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>dep.rodolfonogueira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G440" s="2" t="inlineStr">
-        <is>
-          <t>@rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="H440" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodolfonogueirams</t>
-        </is>
-      </c>
-      <c r="I440" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/RodolfoNogueirams</t>
-        </is>
-      </c>
+          <t>dep.robinsonfaria@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr"/>
+      <c r="H440" s="2" t="inlineStr"/>
+      <c r="I440" s="2" t="inlineStr"/>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220624</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>230767</v>
+        <v>220546</v>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo da Zaeli</t>
+          <t>Rodolfo Nogueira</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO LUGLI</t>
+          <t>RODOLFO OLIVEIRA NOGUEIRA</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
@@ -19825,445 +19821,457 @@
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodazaeli@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G441" s="2" t="inlineStr"/>
-      <c r="H441" s="2" t="inlineStr"/>
-      <c r="I441" s="2" t="inlineStr"/>
+          <t>dep.rodolfonogueira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>@rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodolfonogueirams</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/RodolfoNogueirams</t>
+        </is>
+      </c>
       <c r="J441" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220546</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>141531</v>
+        <v>230767</v>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo de Castro</t>
+          <t>Rodrigo da Zaeli</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO BATISTA DE CASTRO</t>
+          <t>RODRIGO LUGLI</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigodecastro@camara.leg.br</t>
+          <t>dep.rodrigodazaeli@camara.leg.br</t>
         </is>
       </c>
       <c r="G442" s="2" t="inlineStr"/>
       <c r="H442" s="2" t="inlineStr"/>
-      <c r="I442" s="2" t="inlineStr">
-        <is>
-          <t>http://www.youtube.com/rodrigocastro45</t>
-        </is>
-      </c>
+      <c r="I442" s="2" t="inlineStr"/>
       <c r="J442" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230767</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>220641</v>
+        <v>141531</v>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Gambale</t>
+          <t>Rodrigo de Castro</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO GAMBALE VIEIRA</t>
+          <t>RODRIGO BATISTA DE CASTRO</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigogambale@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G443" s="2" t="inlineStr">
-        <is>
-          <t>@rodrigogambale</t>
-        </is>
-      </c>
-      <c r="H443" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodrigogambale</t>
-        </is>
-      </c>
-      <c r="I443" s="2" t="inlineStr"/>
+          <t>dep.rodrigodecastro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr"/>
+      <c r="H443" s="2" t="inlineStr"/>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>http://www.youtube.com/rodrigocastro45</t>
+        </is>
+      </c>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141531</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>141533</v>
+        <v>220641</v>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Rollemberg</t>
+          <t>Rodrigo Gambale</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SOBRAL ROLLEMBERG</t>
+          <t>RODRIGO GAMBALE VIEIRA</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigorollemberg@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G444" s="2" t="inlineStr"/>
-      <c r="H444" s="2" t="inlineStr"/>
+          <t>dep.rodrigogambale@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>@rodrigogambale</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rodrigogambale</t>
+        </is>
+      </c>
       <c r="I444" s="2" t="inlineStr"/>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220641</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>165470</v>
+        <v>141533</v>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Valadares</t>
+          <t>Rodrigo Rollemberg</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>RODRIGO SANTANA VALADARES</t>
+          <t>RODRIGO SOBRAL ROLLEMBERG</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>dep.rodrigovaladares@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G445" s="2" t="inlineStr">
-        <is>
-          <t>@rodrigovaladares_</t>
-        </is>
-      </c>
-      <c r="H445" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rodrigovaladares_</t>
-        </is>
-      </c>
-      <c r="I445" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadorodrigovaladares1954</t>
-        </is>
-      </c>
+          <t>dep.rodrigorollemberg@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr"/>
+      <c r="H445" s="2" t="inlineStr"/>
+      <c r="I445" s="2" t="inlineStr"/>
       <c r="J445" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141533</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>220695</v>
+        <v>165470</v>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>Rogéria Santos</t>
+          <t>Rodrigo Valadares</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
+          <t>RODRIGO SANTANA VALADARES</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriasantos@camara.leg.br</t>
+          <t>dep.rodrigovaladares@camara.leg.br</t>
         </is>
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>@rogeriasantosoficial</t>
+          <t>@rodrigovaladares_</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriasantosoficial</t>
+          <t>https://instagram.com/rodrigovaladares_</t>
         </is>
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
+          <t>https://youtube.com/deputadorodrigovaladares1954</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/165470</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>204480</v>
+        <v>220695</v>
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>Rogério Correia</t>
+          <t>Rogéria Santos</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
+          <t>ROGÉRIA DE ALMEIDA PEREIRA DOS SANTOS</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>dep.rogeriocorreia@camara.leg.br</t>
+          <t>dep.rogeriasantos@camara.leg.br</t>
         </is>
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>@rogeriocorreia_</t>
+          <t>@rogeriasantosoficial</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rogeriocorreia_</t>
+          <t>https://instagram.com/rogeriasantosoficial</t>
         </is>
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
+          <t>https://youtube.com/channel/UCWe-7aMx_Q87rZIbh7ccbyw</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220695</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>204525</v>
+        <v>204480</v>
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>Rosana Valle</t>
+          <t>Rogério Correia</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>ROSANA DE OLIVEIRA VALLE</t>
+          <t>ROGÉRIO CORREIA DE MOURA BAPTISTA</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>dep.rosanavalle@camara.leg.br</t>
+          <t>dep.rogeriocorreia@camara.leg.br</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>@rosanavalleoficial</t>
+          <t>@rogeriocorreia_</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosanavalleoficial</t>
+          <t>https://instagram.com/rogeriocorreia_</t>
         </is>
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
+          <t>https://youtube.com/channel/UC6AVYYHC-GswIhS2xlYUb5g</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204480</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>178945</v>
+        <v>204525</v>
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Gomes</t>
+          <t>Rosana Valle</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE SOUZA GOMES</t>
+          <t>ROSANA DE OLIVEIRA VALLE</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelagomes@camara.leg.br</t>
+          <t>dep.rosanavalle@camara.leg.br</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>@rosangelasgomes</t>
+          <t>@rosanavalleoficial</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rosangelasgomes</t>
-        </is>
-      </c>
-      <c r="I449" s="2" t="inlineStr"/>
+          <t>https://instagram.com/rosanavalleoficial</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCoiIg7-jlQtJX3CCgOceQbA</t>
+        </is>
+      </c>
       <c r="J449" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204525</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>220644</v>
+        <v>178945</v>
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>Rosangela Moro</t>
+          <t>Rosangela Gomes</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
+          <t>ROSANGELA DE SOUZA GOMES</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelamoro@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G450" s="2" t="inlineStr"/>
-      <c r="H450" s="2" t="inlineStr"/>
+          <t>dep.rosangelagomes@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>@rosangelasgomes</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rosangelasgomes</t>
+        </is>
+      </c>
       <c r="I450" s="2" t="inlineStr"/>
       <c r="J450" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178945</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>220620</v>
+        <v>220644</v>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>Rosângela Reis</t>
+          <t>Rosangela Moro</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
+          <t>ROSANGELA MARIA WOLFF DE QUADROS MORO</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
@@ -20273,127 +20281,127 @@
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>dep.rosangelareis@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G451" s="2" t="inlineStr">
-        <is>
-          <t>@rosangelareis.mg</t>
-        </is>
-      </c>
-      <c r="H451" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rosangelareis.mg</t>
-        </is>
-      </c>
+          <t>dep.rosangelamoro@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr"/>
+      <c r="H451" s="2" t="inlineStr"/>
       <c r="I451" s="2" t="inlineStr"/>
       <c r="J451" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220644</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>73806</v>
+        <v>220620</v>
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>Roseana Sarney</t>
+          <t>Rosângela Reis</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Roseana Sarney Murad</t>
+          <t>ROSANGELA DE OLIVEIRA CAMPOS REIS</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>dep.roseanasarney@camara.leg.br</t>
+          <t>dep.rosangelareis@camara.leg.br</t>
         </is>
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>@roseanasarney</t>
+          <t>@rosangelareis.mg</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/roseanasarney</t>
+          <t>https://instagram.com/rosangelareis.mg</t>
         </is>
       </c>
       <c r="I452" s="2" t="inlineStr"/>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73806</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220620</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>74371</v>
+        <v>73806</v>
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>Rubens Otoni</t>
+          <t>Roseana Sarney</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>RUBENS OTONI GOMIDE</t>
+          <t>Roseana Sarney Murad</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>dep.rubensotoni@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G453" s="2" t="inlineStr"/>
-      <c r="H453" s="2" t="inlineStr"/>
+          <t>dep.roseanasarney@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>@roseanasarney</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/roseanasarney</t>
+        </is>
+      </c>
       <c r="I453" s="2" t="inlineStr"/>
       <c r="J453" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73806</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>178887</v>
+        <v>74371</v>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>Rubens Pereira Júnior</t>
+          <t>Rubens Otoni</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
+          <t>RUBENS OTONI GOMIDE</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -20403,47 +20411,35 @@
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>dep.rubenspereirajunior@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G454" s="2" t="inlineStr">
-        <is>
-          <t>@rubenspereirajr</t>
-        </is>
-      </c>
-      <c r="H454" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/rubenspereirajr</t>
-        </is>
-      </c>
-      <c r="I454" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
-        </is>
-      </c>
+          <t>dep.rubensotoni@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr"/>
+      <c r="H454" s="2" t="inlineStr"/>
+      <c r="I454" s="2" t="inlineStr"/>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74371</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>73604</v>
+        <v>178887</v>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>Rui Falcão</t>
+          <t>Rubens Pereira Júnior</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>RUI GOETHE DA COSTA FALCÃO</t>
+          <t>RUBENS PEREIRA E SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -20453,286 +20449,298 @@
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>dep.ruifalcao@camara.leg.br</t>
+          <t>dep.rubenspereirajunior@camara.leg.br</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>@ruifalcao13</t>
+          <t>@rubenspereirajr</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruifalcao13</t>
+          <t>https://instagram.com/rubenspereirajr</t>
         </is>
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/rfalcao13</t>
+          <t>https://youtube.com/channel/UCovkVrGdzXbAHaV6ODAWbeA</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178887</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>160635</v>
+        <v>73604</v>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>Ruy Carneiro</t>
+          <t>Rui Falcão</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
+          <t>RUI GOETHE DA COSTA FALCÃO</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>dep.ruycarneiro@camara.leg.br</t>
+          <t>dep.ruifalcao@camara.leg.br</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>@ruy.carneiro</t>
+          <t>@ruifalcao13</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/ruy.carneiro</t>
-        </is>
-      </c>
-      <c r="I456" s="2" t="inlineStr"/>
+          <t>https://instagram.com/ruifalcao13</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/rfalcao13</t>
+        </is>
+      </c>
       <c r="J456" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73604</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>204535</v>
+        <v>160635</v>
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>Sâmia Bomfim</t>
+          <t>Ruy Carneiro</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>SAMIA DE SOUZA BOMFIM</t>
+          <t>RUY MANUEL CARNEIRO BARBOSA DE ACA BELCHIOR</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>dep.samiabomfim@camara.leg.br</t>
+          <t>dep.ruycarneiro@camara.leg.br</t>
         </is>
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>@samiabomfim</t>
+          <t>@ruy.carneiro</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/samiabomfim</t>
-        </is>
-      </c>
-      <c r="I457" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/samiabomfimpsol</t>
-        </is>
-      </c>
+          <t>https://instagram.com/ruy.carneiro</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr"/>
       <c r="J457" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160635</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>220631</v>
+        <v>204535</v>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Samuel Viana</t>
+          <t>Sâmia Bomfim</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
+          <t>SAMIA DE SOUZA BOMFIM</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>dep.samuelviana@camara.leg.br</t>
+          <t>dep.samiabomfim@camara.leg.br</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>@vianasamuel</t>
+          <t>@samiabomfim</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/vianasamuel</t>
+          <t>https://instagram.com/samiabomfim</t>
         </is>
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
+          <t>https://youtube.com/samiabomfimpsol</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204535</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>204416</v>
+        <v>220631</v>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Sanderson</t>
+          <t>Samuel Viana</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>UBIRATAN ANTUNES SANDERSON</t>
+          <t>SAMUEL JOSÉ RODRIGUES DE VIANA</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>dep.sanderson@camara.leg.br</t>
+          <t>dep.samuelviana@camara.leg.br</t>
         </is>
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>@sandersonrs</t>
+          <t>@vianasamuel</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sandersonrs</t>
+          <t>https://instagram.com/vianasamuel</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCR_FE7jk9lWQKLixmnf0_sA</t>
+          <t>https://youtube.com/channel/UCgXYsH9AH6hf3kRJ272lAoQ</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220631</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>160621</v>
+        <v>204416</v>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>Sandro Alex</t>
+          <t>Sanderson</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
+          <t>UBIRATAN ANTUNES SANDERSON</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>dep.sandroalex@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G460" s="2" t="inlineStr"/>
-      <c r="H460" s="2" t="inlineStr"/>
-      <c r="I460" s="2" t="inlineStr"/>
+          <t>dep.sanderson@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>@sandersonrs</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sandersonrs</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCR_FE7jk9lWQKLixmnf0_sA</t>
+        </is>
+      </c>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204416</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
-        <v>236518</v>
+        <v>160621</v>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>Santin Roveda</t>
+          <t>Sandro Alex</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>HILTON SANTIN ROVEDA</t>
+          <t>SANDRO ALEX CRUZ DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -20742,43 +20750,35 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>dep.santinroveda@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G461" s="2" t="inlineStr">
-        <is>
-          <t>@santinroveda</t>
-        </is>
-      </c>
-      <c r="H461" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/santinroveda</t>
-        </is>
-      </c>
+          <t>dep.sandroalex@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr"/>
+      <c r="H461" s="2" t="inlineStr"/>
       <c r="I461" s="2" t="inlineStr"/>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160621</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>204387</v>
+        <v>236518</v>
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>Sargento Fahur</t>
+          <t>Santin Roveda</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>GILSON CARDOSO FAHUR</t>
+          <t>HILTON SANTIN ROVEDA</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -20788,42 +20788,38 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentofahur@camara.leg.br</t>
+          <t>dep.santinroveda@camara.leg.br</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>@sargentofahurpr</t>
+          <t>@santinroveda</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sargentofahurpr</t>
-        </is>
-      </c>
-      <c r="I462" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCGtU73VeRj9hY1P3PtVUERw</t>
-        </is>
-      </c>
+          <t>https://instagram.com/santinroveda</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr"/>
       <c r="J462" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204387</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236518</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>220621</v>
+        <v>204387</v>
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>Sargento Gonçalves</t>
+          <t>Sargento Fahur</t>
         </is>
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>EVANDRO GONÇALVES DA SILVA JÚNIOR</t>
+          <t>GILSON CARDOSO FAHUR</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
@@ -20833,169 +20829,181 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentogoncalves@camara.leg.br</t>
+          <t>dep.sargentofahur@camara.leg.br</t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>@sargentogoncalves22</t>
+          <t>@sargentofahurpr</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sargentogoncalves22</t>
-        </is>
-      </c>
-      <c r="I463" s="2" t="inlineStr"/>
+          <t>https://instagram.com/sargentofahurpr</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCGtU73VeRj9hY1P3PtVUERw</t>
+        </is>
+      </c>
       <c r="J463" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220621</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204387</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>220618</v>
+        <v>220621</v>
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>Sargento Portugal</t>
+          <t>Sargento Gonçalves</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ PORTUGAL NETO</t>
+          <t>EVANDRO GONÇALVES DA SILVA JÚNIOR</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>dep.sargentoportugal@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G464" s="2" t="inlineStr"/>
-      <c r="H464" s="2" t="inlineStr"/>
+          <t>dep.sargentogoncalves@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>@sargentogoncalves22</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sargentogoncalves22</t>
+        </is>
+      </c>
       <c r="I464" s="2" t="inlineStr"/>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220618</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220621</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>220713</v>
+        <v>220618</v>
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>Saullo Vianna</t>
+          <t>Sargento Portugal</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>SAULLO VELAME VIANNA</t>
+          <t>JOSÉ PORTUGAL NETO</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>dep.saullovianna@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G465" s="2" t="inlineStr">
-        <is>
-          <t>@saullovianna</t>
-        </is>
-      </c>
-      <c r="H465" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/saullovianna</t>
-        </is>
-      </c>
-      <c r="I465" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/SaulloVianna</t>
-        </is>
-      </c>
+          <t>dep.sargentoportugal@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr"/>
+      <c r="H465" s="2" t="inlineStr"/>
+      <c r="I465" s="2" t="inlineStr"/>
       <c r="J465" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220713</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220618</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>226837</v>
+        <v>220713</v>
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>Saulo Pedroso</t>
+          <t>Saullo Vianna</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>SAULO PEDROSO DE SOUZA</t>
+          <t>SAULLO VELAME VIANNA</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>dep.saulopedroso@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G466" s="2" t="inlineStr"/>
-      <c r="H466" s="2" t="inlineStr"/>
-      <c r="I466" s="2" t="inlineStr"/>
+          <t>dep.saullovianna@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>@saullovianna</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/saullovianna</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/SaulloVianna</t>
+        </is>
+      </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226837</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220713</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>73808</v>
+        <v>226837</v>
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>Sérgio Brito</t>
+          <t>Saulo Pedroso</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>SÉRGIO LUÍS LACERDA BRITO</t>
+          <t>SAULO PEDROSO DE SOUZA</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
@@ -21005,12 +21013,12 @@
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>dep.sergiobrito@camara.leg.br</t>
+          <t>dep.saulopedroso@camara.leg.br</t>
         </is>
       </c>
       <c r="G467" s="2" t="inlineStr"/>
@@ -21018,125 +21026,125 @@
       <c r="I467" s="2" t="inlineStr"/>
       <c r="J467" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73808</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/226837</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>178933</v>
+        <v>73808</v>
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>Sergio Souza</t>
+          <t>Sérgio Brito</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>SERGIO DE SOUZA</t>
+          <t>SÉRGIO LUÍS LACERDA BRITO</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>dep.sergiosouza@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G468" s="2" t="inlineStr">
-        <is>
-          <t>@sergiosouzapr</t>
-        </is>
-      </c>
-      <c r="H468" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sergiosouzapr</t>
-        </is>
-      </c>
-      <c r="I468" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadofederalsergiosouza</t>
-        </is>
-      </c>
+          <t>dep.sergiobrito@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr"/>
+      <c r="H468" s="2" t="inlineStr"/>
+      <c r="I468" s="2" t="inlineStr"/>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178933</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/73808</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>204557</v>
+        <v>178933</v>
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>Sidney Leite</t>
+          <t>Sergio Souza</t>
         </is>
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>SIDNEY RICARDO DE OLIVEIRA LEITE</t>
+          <t>SERGIO DE SOUZA</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>dep.sidneyleite@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G469" s="2" t="inlineStr"/>
-      <c r="H469" s="2" t="inlineStr"/>
-      <c r="I469" s="2" t="inlineStr"/>
+          <t>dep.sergiosouza@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>@sergiosouzapr</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sergiosouzapr</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/deputadofederalsergiosouza</t>
+        </is>
+      </c>
       <c r="J469" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204557</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178933</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>204360</v>
+        <v>204557</v>
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>Silvia Cristina</t>
+          <t>Sidney Leite</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>SILVIA CRISTINA AMANCIO CHAGAS</t>
+          <t>SIDNEY RICARDO DE OLIVEIRA LEITE</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>dep.silviacristina@camara.leg.br</t>
+          <t>dep.sidneyleite@camara.leg.br</t>
         </is>
       </c>
       <c r="G470" s="2" t="inlineStr"/>
@@ -21144,156 +21152,156 @@
       <c r="I470" s="2" t="inlineStr"/>
       <c r="J470" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204360</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204557</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>204425</v>
+        <v>204360</v>
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>Silvio Costa Filho</t>
+          <t>Silvia Cristina</t>
         </is>
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>SILVIO SERAFIM COSTA FILHO</t>
+          <t>SILVIA CRISTINA AMANCIO CHAGAS</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>dep.silviocostafilho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G471" s="2" t="inlineStr">
-        <is>
-          <t>@silviocostafilho</t>
-        </is>
-      </c>
-      <c r="H471" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/silviocostafilho</t>
-        </is>
-      </c>
-      <c r="I471" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/SilvioCostaFilhooficial</t>
-        </is>
-      </c>
+          <t>dep.silviacristina@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr"/>
+      <c r="H471" s="2" t="inlineStr"/>
+      <c r="I471" s="2" t="inlineStr"/>
       <c r="J471" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204425</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204360</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>220569</v>
+        <v>204425</v>
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>Silvye Alves</t>
+          <t>Silvio Costa Filho</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>SILVYE ALVES DA SILVA</t>
+          <t>SILVIO SERAFIM COSTA FILHO</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>dep.silvyealves@camara.leg.br</t>
+          <t>dep.silviocostafilho@camara.leg.br</t>
         </is>
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t>@silvyealves</t>
+          <t>@silviocostafilho</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/silvyealves</t>
-        </is>
-      </c>
-      <c r="I472" s="2" t="inlineStr"/>
+          <t>https://instagram.com/silviocostafilho</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/SilvioCostaFilhooficial</t>
+        </is>
+      </c>
       <c r="J472" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220569</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204425</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>220651</v>
+        <v>220569</v>
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>Simone Marquetto</t>
+          <t>Silvye Alves</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>SIMONE APARECIDA MARQUETO CURRALADAS</t>
+          <t>SILVYE ALVES DA SILVA</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>dep.simonemarquetto@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G473" s="2" t="inlineStr"/>
-      <c r="H473" s="2" t="inlineStr"/>
+          <t>dep.silvyealves@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>@silvyealves</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/silvyealves</t>
+        </is>
+      </c>
       <c r="I473" s="2" t="inlineStr"/>
       <c r="J473" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220651</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220569</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>104552</v>
+        <v>220651</v>
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>Socorro Neri</t>
+          <t>Simone Marquetto</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>MARIA DO SOCORRO NERI MEDEIROS DE SOUZA</t>
+          <t>SIMONE APARECIDA MARQUETO CURRALADAS</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
@@ -21303,131 +21311,119 @@
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>dep.socorroneri@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G474" s="2" t="inlineStr">
-        <is>
-          <t>@socorroneri</t>
-        </is>
-      </c>
-      <c r="H474" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/socorroneri</t>
-        </is>
-      </c>
+          <t>dep.simonemarquetto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr"/>
+      <c r="H474" s="2" t="inlineStr"/>
       <c r="I474" s="2" t="inlineStr"/>
       <c r="J474" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/104552</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220651</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>220643</v>
+        <v>104552</v>
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>Sônia Guajajara</t>
+          <t>Socorro Neri</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>SONIA BONE DE SOUSA SILVA</t>
+          <t>MARIA DO SOCORRO NERI MEDEIROS DE SOUZA</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>dep.soniaguajajara@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G475" s="2" t="inlineStr"/>
-      <c r="H475" s="2" t="inlineStr"/>
+          <t>dep.socorroneri@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>@socorroneri</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/socorroneri</t>
+        </is>
+      </c>
       <c r="I475" s="2" t="inlineStr"/>
       <c r="J475" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220643</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/104552</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>178946</v>
+        <v>220643</v>
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>Soraya Santos</t>
+          <t>Sônia Guajajara</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>SORAYA ALENCAR DOS SANTOS</t>
+          <t>SONIA BONE DE SOUSA SILVA</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>dep.sorayasantos@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G476" s="2" t="inlineStr">
-        <is>
-          <t>@dep.sorayasantos</t>
-        </is>
-      </c>
-      <c r="H476" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/dep.sorayasantos</t>
-        </is>
-      </c>
-      <c r="I476" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCYJ_VrjZS7ISX0Ut0bU_AMA</t>
-        </is>
-      </c>
+          <t>dep.soniaguajajara@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr"/>
+      <c r="H476" s="2" t="inlineStr"/>
+      <c r="I476" s="2" t="inlineStr"/>
       <c r="J476" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178946</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220643</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>178947</v>
+        <v>178946</v>
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>Sóstenes Cavalcante</t>
+          <t>Soraya Santos</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>SOSTENES SILVA CAVALCANTE</t>
+          <t>SORAYA ALENCAR DOS SANTOS</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
@@ -21442,191 +21438,203 @@
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>dep.sostenescavalcante@camara.leg.br</t>
+          <t>dep.sorayasantos@camara.leg.br</t>
         </is>
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>@sostenescavalcante</t>
+          <t>@dep.sorayasantos</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/sostenescavalcante</t>
+          <t>https://instagram.com/dep.sorayasantos</t>
         </is>
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCI2j76o7JyLVSmooEcSvLxA</t>
+          <t>https://www.youtube.com/channel/UCYJ_VrjZS7ISX0Ut0bU_AMA</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178947</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178946</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>92776</v>
+        <v>178947</v>
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>Stefano Aguiar</t>
+          <t>Sóstenes Cavalcante</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>STEFANO AGUIAR DOS SANTOS</t>
+          <t>SOSTENES SILVA CAVALCANTE</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>dep.stefanoaguiar@camara.leg.br</t>
+          <t>dep.sostenescavalcante@camara.leg.br</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>@depstefano</t>
+          <t>@sostenescavalcante</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/depstefano</t>
-        </is>
-      </c>
-      <c r="I478" s="2" t="inlineStr"/>
+          <t>https://instagram.com/sostenescavalcante</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCI2j76o7JyLVSmooEcSvLxA</t>
+        </is>
+      </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92776</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178947</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>204534</v>
+        <v>92776</v>
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>Tabata Amaral</t>
+          <t>Stefano Aguiar</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>TABATA CLAUDIA AMARAL DE PONTES</t>
+          <t>STEFANO AGUIAR DOS SANTOS</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>PSB</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>dep.tabataamaral@camara.leg.br</t>
+          <t>dep.stefanoaguiar@camara.leg.br</t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>@tabataamaralsp</t>
+          <t>@depstefano</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/tabataamaralsp</t>
-        </is>
-      </c>
-      <c r="I479" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCWcx5M5negY_kqSawo2bjZQ</t>
-        </is>
-      </c>
+          <t>https://instagram.com/depstefano</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr"/>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204534</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/92776</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>220682</v>
+        <v>204534</v>
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>Tadeu Veneri</t>
+          <t>Tabata Amaral</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO TADEU VENERI</t>
+          <t>TABATA CLAUDIA AMARAL DE PONTES</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSB</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>dep.tadeuveneri@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G480" s="2" t="inlineStr"/>
-      <c r="H480" s="2" t="inlineStr"/>
-      <c r="I480" s="2" t="inlineStr"/>
+          <t>dep.tabataamaral@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>@tabataamaralsp</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tabataamaralsp</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCWcx5M5negY_kqSawo2bjZQ</t>
+        </is>
+      </c>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220682</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204534</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>204464</v>
+        <v>220682</v>
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>Talíria Petrone</t>
+          <t>Tadeu Veneri</t>
         </is>
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>TALIRIA PETRONE SOARES</t>
+          <t>ANTONIO TADEU VENERI</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>PSOL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>dep.taliriapetrone@camara.leg.br</t>
+          <t>dep.tadeuveneri@camara.leg.br</t>
         </is>
       </c>
       <c r="G481" s="2" t="inlineStr"/>
@@ -21634,22 +21642,22 @@
       <c r="I481" s="2" t="inlineStr"/>
       <c r="J481" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204464</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220682</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>220598</v>
+        <v>204464</v>
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>Tarcísio Motta</t>
+          <t>Talíria Petrone</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>TARCISIO MOTTA DE CARVALHO</t>
+          <t>TALIRIA PETRONE SOARES</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
@@ -21664,191 +21672,191 @@
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>dep.tarcisiomotta@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G482" s="2" t="inlineStr">
-        <is>
-          <t>@tarcisiomottapsol</t>
-        </is>
-      </c>
-      <c r="H482" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/tarcisiomottapsol</t>
-        </is>
-      </c>
-      <c r="I482" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/tarcisiomottapsol</t>
-        </is>
-      </c>
+          <t>dep.taliriapetrone@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr"/>
+      <c r="H482" s="2" t="inlineStr"/>
+      <c r="I482" s="2" t="inlineStr"/>
       <c r="J482" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220598</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204464</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>220560</v>
+        <v>220598</v>
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>Thiago de Joaldo</t>
+          <t>Tarcísio Motta</t>
         </is>
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>JOSE THIAGO ALVES DE CARVALHO</t>
+          <t>TARCISIO MOTTA DE CARVALHO</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSOL</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>dep.thiagodejoaldo@camara.leg.br</t>
+          <t>dep.tarcisiomotta@camara.leg.br</t>
         </is>
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>@thiagodejoaldo</t>
+          <t>@tarcisiomottapsol</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/thiagodejoaldo</t>
-        </is>
-      </c>
-      <c r="I483" s="2" t="inlineStr"/>
+          <t>https://instagram.com/tarcisiomottapsol</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/tarcisiomottapsol</t>
+        </is>
+      </c>
       <c r="J483" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220560</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220598</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>220597</v>
+        <v>220560</v>
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>Thiago Flores</t>
+          <t>Thiago de Joaldo</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>THIAGO LEITE FLORES PEREIRA</t>
+          <t>JOSE THIAGO ALVES DE CARVALHO</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>dep.thiagoflores@camara.leg.br</t>
+          <t>dep.thiagodejoaldo@camara.leg.br</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>@deputadothiagoflores</t>
+          <t>@thiagodejoaldo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputadothiagoflores</t>
-        </is>
-      </c>
-      <c r="I484" s="2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/channel/UCF6Ks4RTqfjqxPMqUTotKkg</t>
-        </is>
-      </c>
+          <t>https://instagram.com/thiagodejoaldo</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr"/>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220597</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220560</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>143084</v>
+        <v>220597</v>
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>Tiago Dimas</t>
+          <t>Thiago Flores</t>
         </is>
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>Tiago Dimas Braga Pereira</t>
+          <t>THIAGO LEITE FLORES PEREIRA</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>PODE</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>dep.tiagodimas@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G485" s="2" t="inlineStr"/>
-      <c r="H485" s="2" t="inlineStr"/>
-      <c r="I485" s="2" t="inlineStr"/>
+          <t>dep.thiagoflores@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>@deputadothiagoflores</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputadothiagoflores</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCF6Ks4RTqfjqxPMqUTotKkg</t>
+        </is>
+      </c>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/143084</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220597</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>220684</v>
+        <v>143084</v>
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>Tião Medeiros</t>
+          <t>Tiago Dimas</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>SEBASTIÃO HENRIQUE DE MEDEIROS</t>
+          <t>Tiago Dimas Braga Pereira</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PODE</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>dep.tiaomedeiros@camara.leg.br</t>
+          <t>dep.tiagodimas@camara.leg.br</t>
         </is>
       </c>
       <c r="G486" s="2" t="inlineStr"/>
@@ -21856,37 +21864,37 @@
       <c r="I486" s="2" t="inlineStr"/>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220684</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/143084</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>160976</v>
+        <v>220684</v>
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>Tiririca</t>
+          <t>Tião Medeiros</t>
         </is>
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO EVERARDO TIRIRICA OLIVEIRA SILVA</t>
+          <t>SEBASTIÃO HENRIQUE DE MEDEIROS</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>dep.tiririca@camara.leg.br</t>
+          <t>dep.tiaomedeiros@camara.leg.br</t>
         </is>
       </c>
       <c r="G487" s="2" t="inlineStr"/>
@@ -21894,37 +21902,37 @@
       <c r="I487" s="2" t="inlineStr"/>
       <c r="J487" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160976</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220684</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>178934</v>
+        <v>160976</v>
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>Toninho Wandscheer</t>
+          <t>Tiririca</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>ANTONIO WANDSCHEER</t>
+          <t>FRANCISCO EVERARDO TIRIRICA OLIVEIRA SILVA</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>dep.toninhowandscheer@camara.leg.br</t>
+          <t>dep.tiririca@camara.leg.br</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr"/>
@@ -21932,121 +21940,121 @@
       <c r="I488" s="2" t="inlineStr"/>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178934</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160976</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>157130</v>
+        <v>178934</v>
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>Túlio Gadêlha</t>
+          <t>Toninho Wandscheer</t>
         </is>
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>TÚLIO GADÊLHA SALES DE MELO</t>
+          <t>ANTONIO WANDSCHEER</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
-          <t>dep.tuliogadelha@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G489" s="2" t="inlineStr">
-        <is>
-          <t>@tulio.gadelha</t>
-        </is>
-      </c>
-      <c r="H489" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/tulio.gadelha</t>
-        </is>
-      </c>
+          <t>dep.toninhowandscheer@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr"/>
+      <c r="H489" s="2" t="inlineStr"/>
       <c r="I489" s="2" t="inlineStr"/>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/157130</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178934</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>236423</v>
+        <v>157130</v>
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>Valdir Trindade</t>
+          <t>Túlio Gadêlha</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>VALDIR TRINDADE DOS SANTOS</t>
+          <t>TÚLIO GADÊLHA SALES DE MELO</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>REPUBLICANOS</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>dep.valdirtrindade@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G490" s="2" t="inlineStr"/>
-      <c r="H490" s="2" t="inlineStr"/>
+          <t>dep.tuliogadelha@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>@tulio.gadelha</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tulio.gadelha</t>
+        </is>
+      </c>
       <c r="I490" s="2" t="inlineStr"/>
       <c r="J490" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236423</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/157130</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>160610</v>
+        <v>236423</v>
       </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
-          <t>Valmir Assunção</t>
+          <t>Valdir Trindade</t>
         </is>
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>VALMIR CARLOS DA ASSUNÇÃO</t>
+          <t>VALDIR TRINDADE DOS SANTOS</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>REPUBLICANOS</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
         <is>
-          <t>dep.valmirassuncao@camara.leg.br</t>
+          <t>dep.valdirtrindade@camara.leg.br</t>
         </is>
       </c>
       <c r="G491" s="2" t="inlineStr"/>
@@ -22054,22 +22062,22 @@
       <c r="I491" s="2" t="inlineStr"/>
       <c r="J491" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160610</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/236423</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
-        <v>74376</v>
+        <v>160610</v>
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>Vander Loubet</t>
+          <t>Valmir Assunção</t>
         </is>
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>VANDER LUIZ DOS SANTOS LOUBET</t>
+          <t>VALMIR CARLOS DA ASSUNÇÃO</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
@@ -22079,177 +22087,165 @@
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>dep.vanderloubet@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G492" s="2" t="inlineStr">
-        <is>
-          <t>@vanderloubet</t>
-        </is>
-      </c>
-      <c r="H492" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/vanderloubet</t>
-        </is>
-      </c>
+          <t>dep.valmirassuncao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr"/>
+      <c r="H492" s="2" t="inlineStr"/>
       <c r="I492" s="2" t="inlineStr"/>
       <c r="J492" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74376</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160610</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
-        <v>204396</v>
+        <v>74376</v>
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>Vermelho</t>
+          <t>Vander Loubet</t>
         </is>
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>NELSI COGUETTO MARIA</t>
+          <t>VANDER LUIZ DOS SANTOS LOUBET</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>dep.vermelho@camara.leg.br</t>
+          <t>dep.vanderloubet@camara.leg.br</t>
         </is>
       </c>
       <c r="G493" s="2" t="inlineStr">
         <is>
-          <t>@deputado_vermelho</t>
+          <t>@vanderloubet</t>
         </is>
       </c>
       <c r="H493" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/deputado_vermelho</t>
+          <t>https://instagram.com/vanderloubet</t>
         </is>
       </c>
       <c r="I493" s="2" t="inlineStr"/>
       <c r="J493" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204396</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74376</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
-        <v>137070</v>
+        <v>204396</v>
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>Vicentinho Júnior</t>
+          <t>Vermelho</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>VICENTE ALVES DE OLIVEIRA JUNIOR</t>
+          <t>NELSI COGUETTO MARIA</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>PSDB</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>dep.vicentinhojunior@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G494" s="2" t="inlineStr"/>
-      <c r="H494" s="2" t="inlineStr"/>
+          <t>dep.vermelho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>@deputado_vermelho</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/deputado_vermelho</t>
+        </is>
+      </c>
       <c r="I494" s="2" t="inlineStr"/>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/137070</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204396</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
-        <v>141555</v>
+        <v>137070</v>
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Carvalho</t>
+          <t>Vicentinho Júnior</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>VINICIUS RAPOZO DE CARVALHO</t>
+          <t>VICENTE ALVES DE OLIVEIRA JUNIOR</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PSDB</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>dep.viniciuscarvalho@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G495" s="2" t="inlineStr">
-        <is>
-          <t>@viniciuscarvalhooficial</t>
-        </is>
-      </c>
-      <c r="H495" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/viniciuscarvalhooficial</t>
-        </is>
-      </c>
-      <c r="I495" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC0jfgVGfyujPS4YeBjTdJpw</t>
-        </is>
-      </c>
+          <t>dep.vicentinhojunior@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G495" s="2" t="inlineStr"/>
+      <c r="H495" s="2" t="inlineStr"/>
+      <c r="I495" s="2" t="inlineStr"/>
       <c r="J495" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141555</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/137070</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
-        <v>160591</v>
+        <v>141555</v>
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Gurgel</t>
+          <t>Vinicius Carvalho</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>VINICIUS DE AZEVEDO GURGEL</t>
+          <t>VINICIUS RAPOZO DE CARVALHO</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
@@ -22259,211 +22255,215 @@
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>dep.viniciusgurgel@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G496" s="2" t="inlineStr"/>
-      <c r="H496" s="2" t="inlineStr"/>
-      <c r="I496" s="2" t="inlineStr"/>
+          <t>dep.viniciuscarvalho@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>@viniciuscarvalhooficial</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/viniciuscarvalhooficial</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC0jfgVGfyujPS4YeBjTdJpw</t>
+        </is>
+      </c>
       <c r="J496" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160591</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/141555</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
-        <v>178992</v>
+        <v>160591</v>
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>Vitor Lippi</t>
+          <t>Vinicius Gurgel</t>
         </is>
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>VITOR LIPPI</t>
+          <t>VINICIUS DE AZEVEDO GURGEL</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>dep.vitorlippi@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G497" s="2" t="inlineStr">
-        <is>
-          <t>@vitorlippi</t>
-        </is>
-      </c>
-      <c r="H497" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/vitorlippi</t>
-        </is>
-      </c>
+          <t>dep.viniciusgurgel@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G497" s="2" t="inlineStr"/>
+      <c r="H497" s="2" t="inlineStr"/>
       <c r="I497" s="2" t="inlineStr"/>
       <c r="J497" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178992</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160591</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
-        <v>91228</v>
+        <v>178992</v>
       </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
-          <t>Waldemar Oliveira</t>
+          <t>Vitor Lippi</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>WALDEMAR DE ANDRADA IGNÁCIO DE OLIVEIRA</t>
+          <t>VITOR LIPPI</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>AVANTE</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>dep.waldemaroliveira@camara.leg.br</t>
+          <t>dep.vitorlippi@camara.leg.br</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
         <is>
-          <t>@waldemaroliveiraoficial</t>
+          <t>@vitorlippi</t>
         </is>
       </c>
       <c r="H498" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/waldemaroliveiraoficial</t>
+          <t>https://instagram.com/vitorlippi</t>
         </is>
       </c>
       <c r="I498" s="2" t="inlineStr"/>
       <c r="J498" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/91228</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/178992</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
-        <v>160569</v>
+        <v>91228</v>
       </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
-          <t>Waldenor Pereira</t>
+          <t>Waldemar Oliveira</t>
         </is>
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>WALDENOR ALVES PEREIRA FILHO</t>
+          <t>WALDEMAR DE ANDRADA IGNÁCIO DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>AVANTE</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
-          <t>dep.waldenorpereira@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G499" s="2" t="inlineStr"/>
-      <c r="H499" s="2" t="inlineStr"/>
+          <t>dep.waldemaroliveira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>@waldemaroliveiraoficial</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/waldemaroliveiraoficial</t>
+        </is>
+      </c>
       <c r="I499" s="2" t="inlineStr"/>
       <c r="J499" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160569</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/91228</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
-        <v>160518</v>
+        <v>160569</v>
       </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
-          <t>Weliton Prado</t>
+          <t>Waldenor Pereira</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>WELITON FERNANDES PRADO</t>
+          <t>WALDENOR ALVES PEREIRA FILHO</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>dep.welitonprado@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G500" s="2" t="inlineStr">
-        <is>
-          <t>@weliton.prado</t>
-        </is>
-      </c>
-      <c r="H500" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/weliton.prado</t>
-        </is>
-      </c>
+          <t>dep.waldenorpereira@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G500" s="2" t="inlineStr"/>
+      <c r="H500" s="2" t="inlineStr"/>
       <c r="I500" s="2" t="inlineStr"/>
       <c r="J500" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160518</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160569</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
-        <v>74043</v>
+        <v>160518</v>
       </c>
       <c r="B501" s="2" t="inlineStr">
         <is>
-          <t>Wellington Roberto</t>
+          <t>Weliton Prado</t>
         </is>
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ WELLINGTON ROBERTO</t>
+          <t>WELITON FERNANDES PRADO</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
@@ -22473,238 +22473,246 @@
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>dep.wellingtonroberto@camara.leg.br</t>
+          <t>dep.welitonprado@camara.leg.br</t>
         </is>
       </c>
       <c r="G501" s="2" t="inlineStr">
         <is>
-          <t>@wellingtonroberto.pb</t>
+          <t>@weliton.prado</t>
         </is>
       </c>
       <c r="H501" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/wellingtonroberto.pb</t>
+          <t>https://instagram.com/weliton.prado</t>
         </is>
       </c>
       <c r="I501" s="2" t="inlineStr"/>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74043</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160518</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
-        <v>224333</v>
+        <v>74043</v>
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>Welter</t>
+          <t>Wellington Roberto</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>ELTON CARLOS WELTER</t>
+          <t>JOSÉ WELLINGTON ROBERTO</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>dep.welter@camara.leg.br</t>
+          <t>dep.wellingtonroberto@camara.leg.br</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>@eltonwelter</t>
+          <t>@wellingtonroberto.pb</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/eltonwelter</t>
+          <t>https://instagram.com/wellingtonroberto.pb</t>
         </is>
       </c>
       <c r="I502" s="2" t="inlineStr"/>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/224333</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/74043</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
-        <v>220564</v>
+        <v>224333</v>
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>Yandra Moura</t>
+          <t>Welter</t>
         </is>
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>YANDRA BARRETO FERREIRA</t>
+          <t>ELTON CARLOS WELTER</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>dep.yandramoura@camara.leg.br</t>
+          <t>dep.welter@camara.leg.br</t>
         </is>
       </c>
       <c r="G503" s="2" t="inlineStr">
         <is>
-          <t>@yandramourase</t>
+          <t>@eltonwelter</t>
         </is>
       </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/yandramourase</t>
-        </is>
-      </c>
-      <c r="I503" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/Yandramourase</t>
-        </is>
-      </c>
+          <t>https://instagram.com/eltonwelter</t>
+        </is>
+      </c>
+      <c r="I503" s="2" t="inlineStr"/>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220564</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/224333</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
-        <v>220660</v>
+        <v>220564</v>
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>Yury do Paredão</t>
+          <t>Yandra Moura</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>YURY BRUNO ALENCAR ARAUJO</t>
+          <t>YANDRA BARRETO FERREIRA</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>dep.yurydoparedao@camara.leg.br</t>
+          <t>dep.yandramoura@camara.leg.br</t>
         </is>
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>@yurydoparedao</t>
+          <t>@yandramourase</t>
         </is>
       </c>
       <c r="H504" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/yurydoparedao</t>
-        </is>
-      </c>
-      <c r="I504" s="2" t="inlineStr"/>
+          <t>https://instagram.com/yandramourase</t>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/Yandramourase</t>
+        </is>
+      </c>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220660</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220564</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
-        <v>230768</v>
+        <v>220660</v>
       </c>
       <c r="B505" s="2" t="inlineStr">
         <is>
-          <t>Zé Adriano</t>
+          <t>Yury do Paredão</t>
         </is>
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>JOSE ADRIANO RIBEIRO DA SILVA</t>
+          <t>YURY BRUNO ALENCAR ARAUJO</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
-          <t>dep.zeadriano@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G505" s="2" t="inlineStr"/>
-      <c r="H505" s="2" t="inlineStr"/>
+          <t>dep.yurydoparedao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>@yurydoparedao</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/yurydoparedao</t>
+        </is>
+      </c>
       <c r="I505" s="2" t="inlineStr"/>
       <c r="J505" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230768</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220660</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
-        <v>220536</v>
+        <v>230768</v>
       </c>
       <c r="B506" s="2" t="inlineStr">
         <is>
-          <t>Zé Haroldo Cathedral</t>
+          <t>Zé Adriano</t>
         </is>
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ HAROLDO FIGUEIREDO CAMPOS</t>
+          <t>JOSE ADRIANO RIBEIRO DA SILVA</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>dep.zeharoldocathedral@camara.leg.br</t>
+          <t>dep.zeadriano@camara.leg.br</t>
         </is>
       </c>
       <c r="G506" s="2" t="inlineStr"/>
@@ -22712,37 +22720,37 @@
       <c r="I506" s="2" t="inlineStr"/>
       <c r="J506" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220536</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/230768</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
-        <v>204559</v>
+        <v>220536</v>
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>Zé Neto</t>
+          <t>Zé Haroldo Cathedral</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ CERQUEIRA DE SANTANA NETO</t>
+          <t>JOSÉ HAROLDO FIGUEIREDO CAMPOS</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
-          <t>dep.zeneto@camara.leg.br</t>
+          <t>dep.zeharoldocathedral@camara.leg.br</t>
         </is>
       </c>
       <c r="G507" s="2" t="inlineStr"/>
@@ -22750,110 +22758,110 @@
       <c r="I507" s="2" t="inlineStr"/>
       <c r="J507" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204559</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220536</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
-        <v>160632</v>
+        <v>204559</v>
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>Zé Silva</t>
+          <t>Zé Neto</t>
         </is>
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ SILVA SOARES</t>
+          <t>JOSÉ CERQUEIRA DE SANTANA NETO</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>UNIÃO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>dep.zesilva@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G508" s="2" t="inlineStr">
-        <is>
-          <t>@depzesilva</t>
-        </is>
-      </c>
-      <c r="H508" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/depzesilva</t>
-        </is>
-      </c>
-      <c r="I508" s="2" t="inlineStr">
-        <is>
-          <t>https://youtube.com/deputadozesilva</t>
-        </is>
-      </c>
+          <t>dep.zeneto@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G508" s="2" t="inlineStr"/>
+      <c r="H508" s="2" t="inlineStr"/>
+      <c r="I508" s="2" t="inlineStr"/>
       <c r="J508" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160632</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204559</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
-        <v>220558</v>
+        <v>160632</v>
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>Zé Trovão</t>
+          <t>Zé Silva</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>MARCOS ANTONIO PEREIRA GOMES</t>
+          <t>JOSÉ SILVA SOARES</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>UNIÃO</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>dep.zetrovao@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G509" s="2" t="inlineStr"/>
-      <c r="H509" s="2" t="inlineStr"/>
-      <c r="I509" s="2" t="inlineStr"/>
+          <t>dep.zesilva@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>@depzesilva</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/depzesilva</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/deputadozesilva</t>
+        </is>
+      </c>
       <c r="J509" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220558</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160632</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
-        <v>204517</v>
+        <v>220558</v>
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>Zé Vitor</t>
+          <t>Zé Trovão</t>
         </is>
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>JOSE VITOR DE RESENDE AGUIAR</t>
+          <t>MARCOS ANTONIO PEREIRA GOMES</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
@@ -22863,142 +22871,142 @@
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>dep.zevitor@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G510" s="2" t="inlineStr">
-        <is>
-          <t>@zevitormg</t>
-        </is>
-      </c>
-      <c r="H510" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.com/zevitormg</t>
-        </is>
-      </c>
+          <t>dep.zetrovao@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G510" s="2" t="inlineStr"/>
+      <c r="H510" s="2" t="inlineStr"/>
       <c r="I510" s="2" t="inlineStr"/>
       <c r="J510" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204517</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220558</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
-        <v>160592</v>
+        <v>204517</v>
       </c>
       <c r="B511" s="2" t="inlineStr">
         <is>
-          <t>Zeca Dirceu</t>
+          <t>Zé Vitor</t>
         </is>
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ CARLOS BECKER DE OLIVEIRA E SILVA</t>
+          <t>JOSE VITOR DE RESENDE AGUIAR</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>dep.zecadirceu@camara.leg.br</t>
+          <t>dep.zevitor@camara.leg.br</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
         <is>
-          <t>@zecadirceuoficial</t>
+          <t>@zevitormg</t>
         </is>
       </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/zecadirceuoficial</t>
+          <t>https://instagram.com/zevitormg</t>
         </is>
       </c>
       <c r="I511" s="2" t="inlineStr"/>
       <c r="J511" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160592</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/204517</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
-        <v>220592</v>
+        <v>160592</v>
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>Zezinho Barbary</t>
+          <t>Zeca Dirceu</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>JOSÉ ESTEPHAN AMORIM BARBARY FILHO</t>
+          <t>JOSÉ CARLOS BECKER DE OLIVEIRA E SILVA</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>dep.zezinhobarbary@camara.leg.br</t>
-        </is>
-      </c>
-      <c r="G512" s="2" t="inlineStr"/>
-      <c r="H512" s="2" t="inlineStr"/>
+          <t>dep.zecadirceu@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>@zecadirceuoficial</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/zecadirceuoficial</t>
+        </is>
+      </c>
       <c r="I512" s="2" t="inlineStr"/>
       <c r="J512" s="2" t="inlineStr">
         <is>
-          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220592</t>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/160592</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
-        <v>220552</v>
+        <v>220592</v>
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
-          <t>Zucco</t>
+          <t>Zezinho Barbary</t>
         </is>
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>LUCIANO LORENZINI ZUCCO</t>
+          <t>JOSÉ ESTEPHAN AMORIM BARBARY FILHO</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>dep.zucco@camara.leg.br</t>
+          <t>dep.zezinhobarbary@camara.leg.br</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr"/>
@@ -23006,29 +23014,67 @@
       <c r="I513" s="2" t="inlineStr"/>
       <c r="J513" s="2" t="inlineStr">
         <is>
+          <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220592</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="n">
+        <v>220552</v>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>Zucco</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>LUCIANO LORENZINI ZUCCO</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>dep.zucco@camara.leg.br</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="inlineStr"/>
+      <c r="H514" s="2" t="inlineStr"/>
+      <c r="I514" s="2" t="inlineStr"/>
+      <c r="J514" s="2" t="inlineStr">
+        <is>
           <t>https://dadosabertos.camara.leg.br/api/v2/deputados/220552</t>
         </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" s="3" t="inlineStr">
-        <is>
-          <t>Total deputados:</t>
-        </is>
-      </c>
-      <c r="B515">
-        <f>COUNTA(B2:B513)</f>
-        <v/>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
         <is>
+          <t>Total deputados:</t>
+        </is>
+      </c>
+      <c r="B516">
+        <f>COUNTA(B2:B514)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="3" t="inlineStr">
+        <is>
           <t>Com Instagram:</t>
         </is>
       </c>
-      <c r="B516">
-        <f>COUNTIF(G2:G513,"&lt;&gt;""")</f>
+      <c r="B517">
+        <f>COUNTIF(G2:G514,"&lt;&gt;""")</f>
         <v/>
       </c>
     </row>

--- a/deputados_federais.xlsx
+++ b/deputados_federais.xlsx
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>MARIO S. M. NEGROMONTE JR.</t>
+          <t>MARIO SILVIO MENDES NEGROMONTE JÚNIOR</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
